--- a/Data/FlightPlan/FPL_09AUG26.xlsx
+++ b/Data/FlightPlan/FPL_09AUG26.xlsx
@@ -344,7 +344,7 @@
     <t>10:25</t>
   </si>
   <si>
-    <t>16:56</t>
+    <t>16:45</t>
   </si>
   <si>
     <t>17:30</t>
@@ -650,9 +650,6 @@
     <t>16:15</t>
   </si>
   <si>
-    <t>16:45</t>
-  </si>
-  <si>
     <t>18:55</t>
   </si>
   <si>
@@ -740,6 +737,9 @@
     <t>VN-A550</t>
   </si>
   <si>
+    <t>12:31</t>
+  </si>
+  <si>
     <t>22:20</t>
   </si>
   <si>
@@ -869,7 +869,7 @@
     <t>09:31</t>
   </si>
   <si>
-    <t>15:09</t>
+    <t>15:06</t>
   </si>
   <si>
     <t>18:20</t>
@@ -1061,6 +1061,15 @@
     <t>12:35</t>
   </si>
   <si>
+    <t>01:30</t>
+  </si>
+  <si>
+    <t>02:30</t>
+  </si>
+  <si>
+    <t>04:10</t>
+  </si>
+  <si>
     <t>VN-A641</t>
   </si>
   <si>
@@ -1088,9 +1097,6 @@
     <t>09:59</t>
   </si>
   <si>
-    <t>12:31</t>
-  </si>
-  <si>
     <t>PXU</t>
   </si>
   <si>
@@ -1112,7 +1118,7 @@
     <t>09:55</t>
   </si>
   <si>
-    <t>12:52</t>
+    <t>12:49</t>
   </si>
   <si>
     <t>VN-A646</t>
@@ -1127,7 +1133,7 @@
     <t>12:00</t>
   </si>
   <si>
-    <t>12:39</t>
+    <t>12:42</t>
   </si>
   <si>
     <t>MNL</t>
@@ -1154,6 +1160,9 @@
     <t>10:37</t>
   </si>
   <si>
+    <t>12:41</t>
+  </si>
+  <si>
     <t>13:40</t>
   </si>
   <si>
@@ -1205,6 +1214,9 @@
     <t>VN-A656</t>
   </si>
   <si>
+    <t>12:48</t>
+  </si>
+  <si>
     <t>VN-A657</t>
   </si>
   <si>
@@ -1361,15 +1373,6 @@
     <t>07:43</t>
   </si>
   <si>
-    <t>01:30</t>
-  </si>
-  <si>
-    <t>02:30</t>
-  </si>
-  <si>
-    <t>04:10</t>
-  </si>
-  <si>
     <t>VN-A687</t>
   </si>
   <si>
@@ -1457,7 +1460,7 @@
     <t>Total Record(s): 450</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Aug 09, 2026 10:55</t>
+    <t xml:space="preserve">Generated on  Aug 09, 2026 11:10</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -5207,10 +5210,10 @@
         <v>59</v>
       </c>
       <c t="s" r="I110" s="7">
+        <v>111</v>
+      </c>
+      <c t="s" r="J110" s="7">
         <v>213</v>
-      </c>
-      <c t="s" r="J110" s="7">
-        <v>214</v>
       </c>
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
@@ -5243,7 +5246,7 @@
         <v>175</v>
       </c>
       <c t="s" r="J111" s="7">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
@@ -5276,7 +5279,7 @@
         <v>147</v>
       </c>
       <c t="s" r="J112" s="7">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
@@ -5309,7 +5312,7 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
@@ -5324,7 +5327,7 @@
         <v>87</v>
       </c>
       <c t="s" r="J114" s="7">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
@@ -5344,7 +5347,7 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
@@ -5359,7 +5362,7 @@
         <v>171</v>
       </c>
       <c t="s" r="J115" s="7">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
@@ -5377,7 +5380,7 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
@@ -5389,7 +5392,7 @@
         <v>127</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c t="s" r="J116" s="7">
         <v>64</v>
@@ -5410,7 +5413,7 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -5443,7 +5446,7 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
@@ -5455,7 +5458,7 @@
         <v>59</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c t="s" r="J118" s="7">
         <v>67</v>
@@ -5465,7 +5468,7 @@
       </c>
       <c r="L118" s="7"/>
       <c t="s" r="M118" s="7">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="119" ht="14.25" customHeight="1">
@@ -5480,7 +5483,7 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
@@ -5492,10 +5495,10 @@
         <v>78</v>
       </c>
       <c t="s" r="I119" s="7">
+        <v>222</v>
+      </c>
+      <c t="s" r="J119" s="7">
         <v>223</v>
-      </c>
-      <c t="s" r="J119" s="7">
-        <v>224</v>
       </c>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
@@ -5528,7 +5531,7 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -5548,7 +5551,7 @@
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
       <c t="s" r="M121" s="7">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="122" ht="14.25" customHeight="1">
@@ -5563,7 +5566,7 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
@@ -5572,13 +5575,13 @@
         <v>49</v>
       </c>
       <c t="s" r="H122" s="8">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c t="s" r="I122" s="7">
         <v>62</v>
       </c>
       <c t="s" r="J122" s="7">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
@@ -5596,19 +5599,19 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G123" s="8">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c t="s" r="H123" s="8">
         <v>49</v>
       </c>
       <c t="s" r="I123" s="7">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c t="s" r="J123" s="7">
         <v>46</v>
@@ -5629,7 +5632,7 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
@@ -5641,10 +5644,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I124" s="7">
+        <v>229</v>
+      </c>
+      <c t="s" r="J124" s="7">
         <v>230</v>
-      </c>
-      <c t="s" r="J124" s="7">
-        <v>231</v>
       </c>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
@@ -5662,7 +5665,7 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
@@ -5674,7 +5677,7 @@
         <v>78</v>
       </c>
       <c t="s" r="I125" s="7">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c t="s" r="J125" s="7">
         <v>106</v>
@@ -5710,7 +5713,7 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
@@ -5722,7 +5725,7 @@
         <v>59</v>
       </c>
       <c t="s" r="I127" s="7">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c t="s" r="J127" s="7">
         <v>93</v>
@@ -5745,7 +5748,7 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
@@ -5754,13 +5757,13 @@
         <v>59</v>
       </c>
       <c t="s" r="H128" s="8">
+        <v>234</v>
+      </c>
+      <c t="s" r="I128" s="7">
         <v>235</v>
       </c>
-      <c t="s" r="I128" s="7">
-        <v>236</v>
-      </c>
       <c t="s" r="J128" s="7">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
@@ -5778,22 +5781,22 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G129" s="8">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c t="s" r="H129" s="8">
         <v>59</v>
       </c>
       <c t="s" r="I129" s="7">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c t="s" r="J129" s="7">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
@@ -5811,7 +5814,7 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -5823,7 +5826,7 @@
         <v>31</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c t="s" r="J130" s="7">
         <v>152</v>
@@ -5859,7 +5862,7 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
@@ -5894,7 +5897,7 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
@@ -5927,7 +5930,7 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
@@ -5960,7 +5963,7 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -5972,10 +5975,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I135" s="7">
+        <v>239</v>
+      </c>
+      <c t="s" r="J135" s="7">
         <v>240</v>
-      </c>
-      <c t="s" r="J135" s="7">
-        <v>241</v>
       </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
@@ -6008,7 +6011,7 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
@@ -6027,7 +6030,9 @@
       </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
-      <c r="M137" s="7"/>
+      <c t="s" r="M137" s="7">
+        <v>242</v>
+      </c>
     </row>
     <row r="138" ht="14.25" customHeight="1">
       <c t="s" r="A138" s="6">
@@ -6041,7 +6046,7 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -6074,7 +6079,7 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -6107,7 +6112,7 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -6140,7 +6145,7 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
@@ -6155,7 +6160,7 @@
         <v>243</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
@@ -6273,7 +6278,7 @@
         <v>36</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
@@ -6470,7 +6475,7 @@
         <v>31</v>
       </c>
       <c t="s" r="I151" s="7">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c t="s" r="J151" s="7">
         <v>160</v>
@@ -6555,7 +6560,7 @@
         <v>49</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c t="s" r="J154" s="7">
         <v>248</v>
@@ -6825,7 +6830,7 @@
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
       <c t="s" r="M162" s="7">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="163" ht="14.25" customHeight="1">
@@ -6929,7 +6934,7 @@
         <v>100</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
@@ -6959,7 +6964,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I166" s="7">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c t="s" r="J166" s="7">
         <v>265</v>
@@ -7539,7 +7544,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H185" s="8">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c t="s" r="I185" s="7">
         <v>184</v>
@@ -7571,7 +7576,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G186" s="8">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c t="s" r="H186" s="8">
         <v>16</v>
@@ -7613,7 +7618,7 @@
         <v>175</v>
       </c>
       <c t="s" r="J187" s="7">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c t="s" r="K187" s="7">
         <v>289</v>
@@ -8037,7 +8042,7 @@
         <v>284</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
@@ -8687,7 +8692,7 @@
         <v>318</v>
       </c>
       <c t="s" r="I222" s="7">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c t="s" r="J222" s="7">
         <v>98</v>
@@ -8720,10 +8725,10 @@
         <v>89</v>
       </c>
       <c t="s" r="I223" s="7">
+        <v>227</v>
+      </c>
+      <c t="s" r="J223" s="7">
         <v>228</v>
-      </c>
-      <c t="s" r="J223" s="7">
-        <v>229</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
@@ -9086,7 +9091,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I235" s="7">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c t="s" r="J235" s="7">
         <v>323</v>
@@ -9162,11 +9167,11 @@
         <v>56</v>
       </c>
       <c t="s" r="K237" s="7">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="L237" s="7"/>
       <c t="s" r="M237" s="7">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="238" ht="14.25" customHeight="1">
@@ -9384,7 +9389,7 @@
         <v>133</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
@@ -9851,7 +9856,7 @@
         <v>133</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
@@ -10114,7 +10119,7 @@
         <v>13</v>
       </c>
       <c r="B268" s="7">
-        <v>155</v>
+        <v>3908</v>
       </c>
       <c t="s" r="C268" s="7">
         <v>14</v>
@@ -10127,16 +10132,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G268" s="8">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c t="s" r="H268" s="8">
-        <v>16</v>
+        <v>312</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>190</v>
+        <v>55</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>280</v>
+        <v>350</v>
       </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
@@ -10144,10 +10149,10 @@
     </row>
     <row r="269" ht="14.25" customHeight="1">
       <c t="s" r="A269" s="6">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="B269" s="7">
-        <v>148</v>
+        <v>3909</v>
       </c>
       <c t="s" r="C269" s="7">
         <v>14</v>
@@ -10160,24 +10165,20 @@
         <v>321</v>
       </c>
       <c t="s" r="G269" s="8">
-        <v>16</v>
+        <v>312</v>
       </c>
       <c t="s" r="H269" s="8">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>257</v>
+        <v>351</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>270</v>
-      </c>
-      <c t="s" r="K269" s="7">
-        <v>176</v>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="K269" s="7"/>
       <c r="L269" s="7"/>
-      <c t="s" r="M269" s="7">
-        <v>77</v>
-      </c>
+      <c r="M269" s="7"/>
     </row>
     <row r="270" ht="15" customHeight="1">
       <c r="A270" s="6"/>
@@ -10206,7 +10207,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
@@ -10241,7 +10242,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
@@ -10274,7 +10275,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
@@ -10307,7 +10308,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
@@ -10340,7 +10341,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -10373,7 +10374,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
@@ -10388,7 +10389,7 @@
         <v>324</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
@@ -10421,7 +10422,7 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="F278" s="7">
         <v>321</v>
@@ -10436,12 +10437,12 @@
         <v>250</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
       <c t="s" r="M278" s="7">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="279" ht="14.25" customHeight="1">
@@ -10456,7 +10457,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="F279" s="7">
         <v>321</v>
@@ -10476,7 +10477,7 @@
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
       <c t="s" r="M279" s="7">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="280" ht="15" customHeight="1">
@@ -10491,7 +10492,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="F280" s="7">
         <v>321</v>
@@ -10500,13 +10501,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H280" s="8">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c t="s" r="I280" s="7">
         <v>40</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
@@ -10524,13 +10525,13 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="F281" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G281" s="8">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c t="s" r="H281" s="8">
         <v>16</v>
@@ -10572,7 +10573,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="F283" s="7">
         <v>321</v>
@@ -10592,7 +10593,7 @@
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
       <c t="s" r="M283" s="7">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="284" ht="14.25" customHeight="1">
@@ -10607,7 +10608,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="F284" s="7">
         <v>321</v>
@@ -10627,7 +10628,7 @@
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
       <c t="s" r="M284" s="7">
-        <v>359</v>
+        <v>242</v>
       </c>
     </row>
     <row r="285" ht="15" customHeight="1">
@@ -10642,7 +10643,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="F285" s="7">
         <v>321</v>
@@ -10657,7 +10658,7 @@
         <v>43</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
@@ -10675,7 +10676,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="F286" s="7">
         <v>321</v>
@@ -10708,7 +10709,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
@@ -10717,7 +10718,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H287" s="8">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c t="s" r="I287" s="7">
         <v>257</v>
@@ -10741,13 +10742,13 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="F288" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G288" s="8">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c t="s" r="H288" s="8">
         <v>16</v>
@@ -10774,7 +10775,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
@@ -10796,7 +10797,7 @@
       </c>
       <c r="L289" s="7"/>
       <c t="s" r="M289" s="7">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="290" ht="15" customHeight="1">
@@ -10811,7 +10812,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
@@ -10826,7 +10827,7 @@
         <v>56</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
@@ -10859,7 +10860,7 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F292" s="7">
         <v>321</v>
@@ -10871,7 +10872,7 @@
         <v>127</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c t="s" r="J292" s="7">
         <v>310</v>
@@ -10894,7 +10895,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F293" s="7">
         <v>321</v>
@@ -10914,7 +10915,7 @@
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
       <c t="s" r="M293" s="7">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="294" ht="14.25" customHeight="1">
@@ -10929,7 +10930,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F294" s="7">
         <v>321</v>
@@ -10941,7 +10942,7 @@
         <v>127</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c t="s" r="J294" s="7">
         <v>262</v>
@@ -10962,7 +10963,7 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F295" s="7">
         <v>321</v>
@@ -10977,7 +10978,7 @@
         <v>190</v>
       </c>
       <c t="s" r="J295" s="7">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
@@ -11010,7 +11011,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="F297" s="7">
         <v>321</v>
@@ -11025,12 +11026,12 @@
         <v>291</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
       <c t="s" r="M297" s="7">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="298" ht="14.25" customHeight="1">
@@ -11045,7 +11046,7 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="F298" s="7">
         <v>321</v>
@@ -11065,7 +11066,7 @@
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
       <c t="s" r="M298" s="7">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="299" ht="14.25" customHeight="1">
@@ -11080,7 +11081,7 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="F299" s="7">
         <v>321</v>
@@ -11113,7 +11114,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="F300" s="7">
         <v>321</v>
@@ -11146,7 +11147,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="F301" s="7">
         <v>321</v>
@@ -11179,7 +11180,7 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="F302" s="7">
         <v>321</v>
@@ -11227,7 +11228,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="F304" s="7">
         <v>321</v>
@@ -11262,7 +11263,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="F305" s="7">
         <v>321</v>
@@ -11295,7 +11296,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="F306" s="7">
         <v>321</v>
@@ -11328,7 +11329,7 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="F307" s="7">
         <v>321</v>
@@ -11340,7 +11341,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c t="s" r="J307" s="7">
         <v>66</v>
@@ -11376,7 +11377,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F309" s="7">
         <v>321</v>
@@ -11385,7 +11386,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H309" s="8">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c t="s" r="I309" s="7">
         <v>79</v>
@@ -11411,13 +11412,13 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F310" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G310" s="8">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c t="s" r="H310" s="8">
         <v>16</v>
@@ -11446,7 +11447,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F311" s="7">
         <v>321</v>
@@ -11461,14 +11462,14 @@
         <v>90</v>
       </c>
       <c t="s" r="J311" s="7">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c t="s" r="K311" s="7">
         <v>110</v>
       </c>
       <c r="L311" s="7"/>
       <c t="s" r="M311" s="7">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="312" ht="14.25" customHeight="1">
@@ -11483,7 +11484,7 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F312" s="7">
         <v>321</v>
@@ -11520,7 +11521,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F313" s="7">
         <v>321</v>
@@ -11532,7 +11533,7 @@
         <v>42</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c t="s" r="J313" s="7">
         <v>165</v>
@@ -11542,7 +11543,7 @@
       </c>
       <c r="L313" s="7"/>
       <c t="s" r="M313" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="314" ht="14.25" customHeight="1">
@@ -11557,7 +11558,7 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F314" s="7">
         <v>321</v>
@@ -11594,7 +11595,7 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F315" s="7">
         <v>321</v>
@@ -11603,7 +11604,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H315" s="8">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c t="s" r="I315" s="7">
         <v>159</v>
@@ -11627,13 +11628,13 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F316" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G316" s="8">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c t="s" r="H316" s="8">
         <v>16</v>
@@ -11642,7 +11643,7 @@
         <v>204</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
@@ -11675,7 +11676,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F318" s="7">
         <v>321</v>
@@ -11687,7 +11688,7 @@
         <v>156</v>
       </c>
       <c t="s" r="I318" s="7">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c t="s" r="J318" s="7">
         <v>43</v>
@@ -11695,7 +11696,7 @@
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
       <c t="s" r="M318" s="7">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="319" ht="14.25" customHeight="1">
@@ -11710,7 +11711,7 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F319" s="7">
         <v>321</v>
@@ -11743,7 +11744,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F320" s="7">
         <v>321</v>
@@ -11758,7 +11759,7 @@
         <v>190</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
@@ -11776,7 +11777,7 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F321" s="7">
         <v>321</v>
@@ -11809,7 +11810,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F322" s="7">
         <v>321</v>
@@ -11857,7 +11858,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F324" s="7">
         <v>321</v>
@@ -11877,7 +11878,7 @@
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
       <c t="s" r="M324" s="7">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="325" ht="15" customHeight="1">
@@ -11892,7 +11893,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F325" s="7">
         <v>321</v>
@@ -11927,7 +11928,7 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F326" s="7">
         <v>321</v>
@@ -11942,12 +11943,12 @@
         <v>334</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
       <c t="s" r="M326" s="7">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="327" ht="14.25" customHeight="1">
@@ -11962,7 +11963,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F327" s="7">
         <v>321</v>
@@ -11981,7 +11982,9 @@
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
-      <c r="M327" s="7"/>
+      <c t="s" r="M327" s="7">
+        <v>383</v>
+      </c>
     </row>
     <row r="328" ht="14.25" customHeight="1">
       <c t="s" r="A328" s="6">
@@ -11995,7 +11998,7 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F328" s="7">
         <v>321</v>
@@ -12007,7 +12010,7 @@
         <v>120</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c t="s" r="J328" s="7">
         <v>45</v>
@@ -12028,7 +12031,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F329" s="7">
         <v>321</v>
@@ -12061,7 +12064,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F330" s="7">
         <v>321</v>
@@ -12094,7 +12097,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F331" s="7">
         <v>321</v>
@@ -12106,10 +12109,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I331" s="7">
+        <v>214</v>
+      </c>
+      <c t="s" r="J331" s="7">
         <v>215</v>
-      </c>
-      <c t="s" r="J331" s="7">
-        <v>216</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
@@ -12142,7 +12145,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="F333" s="7">
         <v>320</v>
@@ -12154,7 +12157,7 @@
         <v>96</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c t="s" r="J333" s="7">
         <v>267</v>
@@ -12162,7 +12165,7 @@
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
       <c t="s" r="M333" s="7">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="334" ht="14.25" customHeight="1">
@@ -12177,7 +12180,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="F334" s="7">
         <v>320</v>
@@ -12197,7 +12200,7 @@
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
       <c t="s" r="M334" s="7">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="335" ht="15" customHeight="1">
@@ -12212,7 +12215,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="F335" s="7">
         <v>320</v>
@@ -12227,12 +12230,12 @@
         <v>18</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
       <c t="s" r="M335" s="7">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="336" ht="14.25" customHeight="1">
@@ -12247,7 +12250,7 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="F336" s="7">
         <v>320</v>
@@ -12262,12 +12265,12 @@
         <v>184</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
       <c t="s" r="M336" s="7">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="337" ht="14.25" customHeight="1">
@@ -12282,7 +12285,7 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="F337" s="7">
         <v>320</v>
@@ -12294,7 +12297,7 @@
         <v>59</v>
       </c>
       <c t="s" r="I337" s="7">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c t="s" r="J337" s="7">
         <v>343</v>
@@ -12315,7 +12318,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="F338" s="7">
         <v>320</v>
@@ -12348,7 +12351,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="F339" s="7">
         <v>320</v>
@@ -12357,13 +12360,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H339" s="8">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c t="s" r="I339" s="7">
         <v>131</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
@@ -12381,19 +12384,19 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="F340" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G340" s="8">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c t="s" r="H340" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c t="s" r="J340" s="7">
         <v>250</v>
@@ -12429,7 +12432,7 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="F342" s="7">
         <v>321</v>
@@ -12449,7 +12452,7 @@
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
       <c t="s" r="M342" s="7">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="343" ht="14.25" customHeight="1">
@@ -12464,7 +12467,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="F343" s="7">
         <v>321</v>
@@ -12476,7 +12479,7 @@
         <v>59</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c t="s" r="J343" s="7">
         <v>211</v>
@@ -12497,7 +12500,7 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="F344" s="7">
         <v>321</v>
@@ -12530,7 +12533,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="F345" s="7">
         <v>321</v>
@@ -12563,7 +12566,7 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="F346" s="7">
         <v>321</v>
@@ -12596,7 +12599,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="F347" s="7">
         <v>321</v>
@@ -12644,7 +12647,7 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="F349" s="7">
         <v>321</v>
@@ -12664,7 +12667,7 @@
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
       <c t="s" r="M349" s="7">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="350" ht="15" customHeight="1">
@@ -12679,7 +12682,7 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="F350" s="7">
         <v>321</v>
@@ -12688,7 +12691,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H350" s="8">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c t="s" r="I350" s="7">
         <v>83</v>
@@ -12712,22 +12715,22 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="F351" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G351" s="8">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c t="s" r="H351" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
@@ -12760,7 +12763,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F353" s="7">
         <v>320</v>
@@ -12795,7 +12798,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F354" s="7">
         <v>320</v>
@@ -12814,7 +12817,9 @@
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
-      <c r="M354" s="7"/>
+      <c t="s" r="M354" s="7">
+        <v>401</v>
+      </c>
     </row>
     <row r="355" ht="15" customHeight="1">
       <c t="s" r="A355" s="6">
@@ -12828,7 +12833,7 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F355" s="7">
         <v>320</v>
@@ -12843,7 +12848,7 @@
         <v>194</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
@@ -12861,7 +12866,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F356" s="7">
         <v>320</v>
@@ -12894,7 +12899,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F357" s="7">
         <v>320</v>
@@ -12927,7 +12932,7 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F358" s="7">
         <v>320</v>
@@ -12975,7 +12980,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
@@ -12984,7 +12989,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H360" s="8">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c t="s" r="I360" s="7">
         <v>90</v>
@@ -12995,7 +13000,7 @@
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
       <c t="s" r="M360" s="7">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
     <row r="361" ht="14.25" customHeight="1">
@@ -13010,13 +13015,13 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G361" s="8">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c t="s" r="H361" s="8">
         <v>16</v>
@@ -13043,7 +13048,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
@@ -13076,7 +13081,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
@@ -13109,7 +13114,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="F364" s="7">
         <v>321</v>
@@ -13142,7 +13147,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="F365" s="7">
         <v>321</v>
@@ -13190,7 +13195,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="F367" s="7">
         <v>320</v>
@@ -13225,7 +13230,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="F368" s="7">
         <v>320</v>
@@ -13260,7 +13265,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="F369" s="7">
         <v>320</v>
@@ -13269,10 +13274,10 @@
         <v>59</v>
       </c>
       <c t="s" r="H369" s="8">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c t="s" r="J369" s="7">
         <v>185</v>
@@ -13297,13 +13302,13 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="F370" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G370" s="8">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c t="s" r="H370" s="8">
         <v>59</v>
@@ -13312,7 +13317,7 @@
         <v>187</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c t="s" r="K370" s="7">
         <v>194</v>
@@ -13334,7 +13339,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="F371" s="7">
         <v>320</v>
@@ -13346,7 +13351,7 @@
         <v>311</v>
       </c>
       <c t="s" r="I371" s="7">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c t="s" r="J371" s="7">
         <v>32</v>
@@ -13367,7 +13372,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="F372" s="7">
         <v>320</v>
@@ -13382,7 +13387,7 @@
         <v>270</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
@@ -13415,7 +13420,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="F374" s="7">
         <v>321</v>
@@ -13448,7 +13453,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="F375" s="7">
         <v>321</v>
@@ -13481,7 +13486,7 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="F376" s="7">
         <v>321</v>
@@ -13514,7 +13519,7 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="F377" s="7">
         <v>321</v>
@@ -13529,7 +13534,7 @@
         <v>337</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
@@ -13562,7 +13567,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="F379" s="7">
         <v>320</v>
@@ -13597,7 +13602,7 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="F380" s="7">
         <v>320</v>
@@ -13632,7 +13637,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="F381" s="7">
         <v>320</v>
@@ -13669,7 +13674,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="F382" s="7">
         <v>320</v>
@@ -13678,7 +13683,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H382" s="8">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c t="s" r="I382" s="7">
         <v>45</v>
@@ -13702,13 +13707,13 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="F383" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G383" s="8">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c t="s" r="H383" s="8">
         <v>16</v>
@@ -13735,7 +13740,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="F384" s="7">
         <v>320</v>
@@ -13750,7 +13755,7 @@
         <v>289</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
@@ -13783,13 +13788,13 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="F386" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G386" s="8">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c t="s" r="H386" s="8">
         <v>59</v>
@@ -13803,7 +13808,7 @@
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
       <c t="s" r="M386" s="7">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="387" ht="14.25" customHeight="1">
@@ -13818,7 +13823,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="F387" s="7">
         <v>320</v>
@@ -13827,7 +13832,7 @@
         <v>59</v>
       </c>
       <c t="s" r="H387" s="8">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c t="s" r="I387" s="7">
         <v>44</v>
@@ -13851,13 +13856,13 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="F388" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G388" s="8">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c t="s" r="H388" s="8">
         <v>59</v>
@@ -13884,7 +13889,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="F389" s="7">
         <v>320</v>
@@ -13917,7 +13922,7 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="F390" s="7">
         <v>320</v>
@@ -13929,7 +13934,7 @@
         <v>59</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c t="s" r="J390" s="7">
         <v>177</v>
@@ -13965,7 +13970,7 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="F392" s="7">
         <v>320</v>
@@ -14000,7 +14005,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="F393" s="7">
         <v>320</v>
@@ -14012,7 +14017,7 @@
         <v>59</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c t="s" r="J393" s="7">
         <v>335</v>
@@ -14020,7 +14025,7 @@
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
       <c t="s" r="M393" s="7">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="394" ht="14.25" customHeight="1">
@@ -14035,7 +14040,7 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="F394" s="7">
         <v>320</v>
@@ -14044,7 +14049,7 @@
         <v>59</v>
       </c>
       <c t="s" r="H394" s="8">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c t="s" r="I394" s="7">
         <v>321</v>
@@ -14068,13 +14073,13 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="F395" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G395" s="8">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c t="s" r="H395" s="8">
         <v>59</v>
@@ -14083,7 +14088,7 @@
         <v>98</v>
       </c>
       <c t="s" r="J395" s="7">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
@@ -14101,7 +14106,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="F396" s="7">
         <v>320</v>
@@ -14110,7 +14115,7 @@
         <v>59</v>
       </c>
       <c t="s" r="H396" s="8">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c t="s" r="I396" s="7">
         <v>146</v>
@@ -14134,13 +14139,13 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="F397" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G397" s="8">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c t="s" r="H397" s="8">
         <v>59</v>
@@ -14149,7 +14154,7 @@
         <v>114</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
@@ -14182,7 +14187,7 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="F399" s="7">
         <v>321</v>
@@ -14217,7 +14222,7 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="F400" s="7">
         <v>321</v>
@@ -14237,7 +14242,7 @@
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
       <c t="s" r="M400" s="7">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="401" ht="14.25" customHeight="1">
@@ -14252,7 +14257,7 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="F401" s="7">
         <v>321</v>
@@ -14285,7 +14290,7 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="F402" s="7">
         <v>321</v>
@@ -14318,7 +14323,7 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="F403" s="7">
         <v>321</v>
@@ -14351,7 +14356,7 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="F404" s="7">
         <v>321</v>
@@ -14366,7 +14371,7 @@
         <v>257</v>
       </c>
       <c t="s" r="J404" s="7">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
@@ -14384,7 +14389,7 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="F405" s="7">
         <v>321</v>
@@ -14406,7 +14411,7 @@
       </c>
       <c r="L405" s="7"/>
       <c t="s" r="M405" s="7">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="406" ht="14.25" customHeight="1">
@@ -14421,7 +14426,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="F406" s="7">
         <v>321</v>
@@ -14443,7 +14448,7 @@
       </c>
       <c r="L406" s="7"/>
       <c t="s" r="M406" s="7">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="407" ht="14.25" customHeight="1">
@@ -14473,7 +14478,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="F408" s="7">
         <v>320</v>
@@ -14485,7 +14490,7 @@
         <v>311</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c t="s" r="J408" s="7">
         <v>208</v>
@@ -14493,7 +14498,7 @@
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
       <c t="s" r="M408" s="7">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="409" ht="14.25" customHeight="1">
@@ -14508,7 +14513,7 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="F409" s="7">
         <v>320</v>
@@ -14520,7 +14525,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I409" s="7">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c t="s" r="J409" s="7">
         <v>43</v>
@@ -14541,7 +14546,7 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="F410" s="7">
         <v>320</v>
@@ -14574,7 +14579,7 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="F411" s="7">
         <v>320</v>
@@ -14586,7 +14591,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I411" s="7">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c t="s" r="J411" s="7">
         <v>197</v>
@@ -14607,7 +14612,7 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="F412" s="7">
         <v>320</v>
@@ -14622,7 +14627,7 @@
         <v>323</v>
       </c>
       <c t="s" r="J412" s="7">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
@@ -14640,7 +14645,7 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="F413" s="7">
         <v>320</v>
@@ -14655,7 +14660,7 @@
         <v>100</v>
       </c>
       <c t="s" r="J413" s="7">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="K413" s="7"/>
       <c r="L413" s="7"/>
@@ -14673,7 +14678,7 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="F414" s="7">
         <v>320</v>
@@ -14688,7 +14693,7 @@
         <v>280</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
@@ -14706,7 +14711,7 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="F415" s="7">
         <v>320</v>
@@ -14721,7 +14726,7 @@
         <v>271</v>
       </c>
       <c t="s" r="J415" s="7">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>
@@ -14754,7 +14759,7 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="F417" s="7">
         <v>320</v>
@@ -14766,7 +14771,7 @@
         <v>49</v>
       </c>
       <c t="s" r="I417" s="7">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c t="s" r="J417" s="7">
         <v>52</v>
@@ -14789,7 +14794,7 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="F418" s="7">
         <v>320</v>
@@ -14804,12 +14809,12 @@
         <v>251</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
       <c t="s" r="M418" s="7">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="419" ht="14.25" customHeight="1">
@@ -14824,7 +14829,7 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="F419" s="7">
         <v>320</v>
@@ -14844,7 +14849,7 @@
       <c r="K419" s="7"/>
       <c r="L419" s="7"/>
       <c t="s" r="M419" s="7">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="420" ht="15" customHeight="1">
@@ -14859,7 +14864,7 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="F420" s="7">
         <v>320</v>
@@ -14892,7 +14897,7 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="F421" s="7">
         <v>320</v>
@@ -14925,7 +14930,7 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="F422" s="7">
         <v>320</v>
@@ -14973,7 +14978,7 @@
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="F424" s="7">
         <v>320</v>
@@ -14993,7 +14998,7 @@
       <c r="K424" s="7"/>
       <c r="L424" s="7"/>
       <c t="s" r="M424" s="7">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="425" ht="15" customHeight="1">
@@ -15008,7 +15013,7 @@
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="F425" s="7">
         <v>320</v>
@@ -15045,7 +15050,7 @@
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="F426" s="7">
         <v>320</v>
@@ -15082,7 +15087,7 @@
       </c>
       <c r="D427" s="7"/>
       <c t="s" r="E427" s="7">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="F427" s="7">
         <v>320</v>
@@ -15094,7 +15099,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I427" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c t="s" r="J427" s="7">
         <v>212</v>
@@ -15119,7 +15124,7 @@
       </c>
       <c r="D428" s="7"/>
       <c t="s" r="E428" s="7">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="F428" s="7">
         <v>320</v>
@@ -15152,7 +15157,7 @@
       </c>
       <c r="D429" s="7"/>
       <c t="s" r="E429" s="7">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="F429" s="7">
         <v>320</v>
@@ -15200,7 +15205,7 @@
       </c>
       <c r="D431" s="7"/>
       <c t="s" r="E431" s="7">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="F431" s="7">
         <v>320</v>
@@ -15209,7 +15214,7 @@
         <v>59</v>
       </c>
       <c t="s" r="H431" s="8">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c t="s" r="I431" s="7">
         <v>275</v>
@@ -15220,7 +15225,7 @@
       <c r="K431" s="7"/>
       <c r="L431" s="7"/>
       <c t="s" r="M431" s="7">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="432" ht="14.25" customHeight="1">
@@ -15235,13 +15240,13 @@
       </c>
       <c r="D432" s="7"/>
       <c t="s" r="E432" s="7">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="F432" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G432" s="8">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c t="s" r="H432" s="8">
         <v>59</v>
@@ -15268,7 +15273,7 @@
       </c>
       <c r="D433" s="7"/>
       <c t="s" r="E433" s="7">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="F433" s="7">
         <v>320</v>
@@ -15277,7 +15282,7 @@
         <v>59</v>
       </c>
       <c t="s" r="H433" s="8">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c t="s" r="I433" s="7">
         <v>130</v>
@@ -15301,13 +15306,13 @@
       </c>
       <c r="D434" s="7"/>
       <c t="s" r="E434" s="7">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="F434" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G434" s="8">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c t="s" r="H434" s="8">
         <v>59</v>
@@ -15349,7 +15354,7 @@
       </c>
       <c r="D436" s="7"/>
       <c t="s" r="E436" s="7">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="F436" s="7">
         <v>321</v>
@@ -15361,7 +15366,7 @@
         <v>49</v>
       </c>
       <c t="s" r="I436" s="7">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c t="s" r="J436" s="7">
         <v>79</v>
@@ -15369,7 +15374,7 @@
       <c r="K436" s="7"/>
       <c r="L436" s="7"/>
       <c t="s" r="M436" s="7">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="437" ht="14.25" customHeight="1">
@@ -15384,7 +15389,7 @@
       </c>
       <c r="D437" s="7"/>
       <c t="s" r="E437" s="7">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="F437" s="7">
         <v>321</v>
@@ -15396,7 +15401,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I437" s="7">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c t="s" r="J437" s="7">
         <v>149</v>
@@ -15404,7 +15409,7 @@
       <c r="K437" s="7"/>
       <c r="L437" s="7"/>
       <c t="s" r="M437" s="7">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="438" ht="14.25" customHeight="1">
@@ -15419,7 +15424,7 @@
       </c>
       <c r="D438" s="7"/>
       <c t="s" r="E438" s="7">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="F438" s="7">
         <v>321</v>
@@ -15441,7 +15446,7 @@
       </c>
       <c r="L438" s="7"/>
       <c t="s" r="M438" s="7">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="439" ht="14.25" customHeight="1">
@@ -15456,7 +15461,7 @@
       </c>
       <c r="D439" s="7"/>
       <c t="s" r="E439" s="7">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="F439" s="7">
         <v>321</v>
@@ -15493,7 +15498,7 @@
       </c>
       <c r="D440" s="7"/>
       <c t="s" r="E440" s="7">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="F440" s="7">
         <v>321</v>
@@ -15502,13 +15507,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H440" s="8">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c t="s" r="I440" s="7">
         <v>211</v>
       </c>
       <c t="s" r="J440" s="7">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c t="s" r="K440" s="7">
         <v>343</v>
@@ -15530,19 +15535,19 @@
       </c>
       <c r="D441" s="7"/>
       <c t="s" r="E441" s="7">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="F441" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G441" s="8">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c t="s" r="H441" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I441" s="7">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c t="s" r="J441" s="7">
         <v>332</v>
@@ -15582,7 +15587,7 @@
       </c>
       <c r="D443" s="7"/>
       <c t="s" r="E443" s="7">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="F443" s="7">
         <v>321</v>
@@ -15602,7 +15607,7 @@
       <c r="K443" s="7"/>
       <c r="L443" s="7"/>
       <c t="s" r="M443" s="7">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="444" ht="14.25" customHeight="1">
@@ -15617,7 +15622,7 @@
       </c>
       <c r="D444" s="7"/>
       <c t="s" r="E444" s="7">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="F444" s="7">
         <v>321</v>
@@ -15626,7 +15631,7 @@
         <v>89</v>
       </c>
       <c t="s" r="H444" s="8">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c t="s" r="I444" s="7">
         <v>93</v>
@@ -15650,19 +15655,19 @@
       </c>
       <c r="D445" s="7"/>
       <c t="s" r="E445" s="7">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="F445" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G445" s="8">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c t="s" r="H445" s="8">
         <v>89</v>
       </c>
       <c t="s" r="I445" s="7">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c t="s" r="J445" s="7">
         <v>203</v>
@@ -15683,7 +15688,7 @@
       </c>
       <c r="D446" s="7"/>
       <c t="s" r="E446" s="7">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="F446" s="7">
         <v>321</v>
@@ -15698,7 +15703,7 @@
         <v>124</v>
       </c>
       <c t="s" r="J446" s="7">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="K446" s="7"/>
       <c r="L446" s="7"/>
@@ -15731,7 +15736,7 @@
       </c>
       <c r="D448" s="7"/>
       <c t="s" r="E448" s="7">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="F448" s="7">
         <v>320</v>
@@ -15746,12 +15751,12 @@
         <v>245</v>
       </c>
       <c t="s" r="J448" s="7">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="K448" s="7"/>
       <c r="L448" s="7"/>
       <c t="s" r="M448" s="7">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="449" ht="14.25" customHeight="1">
@@ -15766,7 +15771,7 @@
       </c>
       <c r="D449" s="7"/>
       <c t="s" r="E449" s="7">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="F449" s="7">
         <v>320</v>
@@ -15786,7 +15791,7 @@
       <c r="K449" s="7"/>
       <c r="L449" s="7"/>
       <c t="s" r="M449" s="7">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="450" ht="15" customHeight="1">
@@ -15801,7 +15806,7 @@
       </c>
       <c r="D450" s="7"/>
       <c t="s" r="E450" s="7">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="F450" s="7">
         <v>320</v>
@@ -15834,7 +15839,7 @@
       </c>
       <c r="D451" s="7"/>
       <c t="s" r="E451" s="7">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="F451" s="7">
         <v>320</v>
@@ -15867,7 +15872,7 @@
       </c>
       <c r="D452" s="7"/>
       <c t="s" r="E452" s="7">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="F452" s="7">
         <v>320</v>
@@ -15900,7 +15905,7 @@
       </c>
       <c r="D453" s="7"/>
       <c t="s" r="E453" s="7">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="F453" s="7">
         <v>320</v>
@@ -15912,10 +15917,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I453" s="7">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c t="s" r="J453" s="7">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K453" s="7"/>
       <c r="L453" s="7"/>
@@ -15948,7 +15953,7 @@
       </c>
       <c r="D455" s="7"/>
       <c t="s" r="E455" s="7">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="F455" s="7">
         <v>320</v>
@@ -15957,18 +15962,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H455" s="8">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c t="s" r="I455" s="7">
         <v>36</v>
       </c>
       <c t="s" r="J455" s="7">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K455" s="7"/>
       <c r="L455" s="7"/>
       <c t="s" r="M455" s="7">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="456" ht="14.25" customHeight="1">
@@ -15983,13 +15988,13 @@
       </c>
       <c r="D456" s="7"/>
       <c t="s" r="E456" s="7">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="F456" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G456" s="8">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c t="s" r="H456" s="8">
         <v>16</v>
@@ -16016,7 +16021,7 @@
       </c>
       <c r="D457" s="7"/>
       <c t="s" r="E457" s="7">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="F457" s="7">
         <v>320</v>
@@ -16025,13 +16030,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H457" s="8">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c t="s" r="I457" s="7">
         <v>277</v>
       </c>
       <c t="s" r="J457" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="K457" s="7"/>
       <c r="L457" s="7"/>
@@ -16049,13 +16054,13 @@
       </c>
       <c r="D458" s="7"/>
       <c t="s" r="E458" s="7">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="F458" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G458" s="8">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c t="s" r="H458" s="8">
         <v>16</v>
@@ -16082,7 +16087,7 @@
       </c>
       <c r="D459" s="7"/>
       <c t="s" r="E459" s="7">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="F459" s="7">
         <v>320</v>
@@ -16115,7 +16120,7 @@
       </c>
       <c r="D460" s="7"/>
       <c t="s" r="E460" s="7">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="F460" s="7">
         <v>320</v>
@@ -16148,7 +16153,7 @@
       </c>
       <c r="D461" s="7"/>
       <c t="s" r="E461" s="7">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="F461" s="7">
         <v>320</v>
@@ -16181,7 +16186,7 @@
       </c>
       <c r="D462" s="7"/>
       <c t="s" r="E462" s="7">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="F462" s="7">
         <v>320</v>
@@ -16196,7 +16201,7 @@
         <v>337</v>
       </c>
       <c t="s" r="J462" s="7">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="K462" s="7"/>
       <c r="L462" s="7"/>
@@ -16229,7 +16234,7 @@
       </c>
       <c r="D464" s="7"/>
       <c t="s" r="E464" s="7">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="F464" s="7">
         <v>321</v>
@@ -16264,7 +16269,7 @@
       </c>
       <c r="D465" s="7"/>
       <c t="s" r="E465" s="7">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="F465" s="7">
         <v>321</v>
@@ -16276,7 +16281,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I465" s="7">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c t="s" r="J465" s="7">
         <v>310</v>
@@ -16284,7 +16289,7 @@
       <c r="K465" s="7"/>
       <c r="L465" s="7"/>
       <c t="s" r="M465" s="7">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="466" ht="14.25" customHeight="1">
@@ -16299,7 +16304,7 @@
       </c>
       <c r="D466" s="7"/>
       <c t="s" r="E466" s="7">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="F466" s="7">
         <v>321</v>
@@ -16332,7 +16337,7 @@
       </c>
       <c r="D467" s="7"/>
       <c t="s" r="E467" s="7">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="F467" s="7">
         <v>321</v>
@@ -16365,7 +16370,7 @@
       </c>
       <c r="D468" s="7"/>
       <c t="s" r="E468" s="7">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="F468" s="7">
         <v>321</v>
@@ -16413,7 +16418,7 @@
       </c>
       <c r="D470" s="7"/>
       <c t="s" r="E470" s="7">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="F470" s="7">
         <v>321</v>
@@ -16422,18 +16427,18 @@
         <v>59</v>
       </c>
       <c t="s" r="H470" s="8">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c t="s" r="I470" s="7">
         <v>154</v>
       </c>
       <c t="s" r="J470" s="7">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="K470" s="7"/>
       <c r="L470" s="7"/>
       <c t="s" r="M470" s="7">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="471" ht="14.25" customHeight="1">
@@ -16448,13 +16453,13 @@
       </c>
       <c r="D471" s="7"/>
       <c t="s" r="E471" s="7">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="F471" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G471" s="8">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c t="s" r="H471" s="8">
         <v>59</v>
@@ -16481,7 +16486,7 @@
       </c>
       <c r="D472" s="7"/>
       <c t="s" r="E472" s="7">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="F472" s="7">
         <v>321</v>
@@ -16514,7 +16519,7 @@
       </c>
       <c r="D473" s="7"/>
       <c t="s" r="E473" s="7">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="F473" s="7">
         <v>321</v>
@@ -16529,7 +16534,7 @@
         <v>144</v>
       </c>
       <c t="s" r="J473" s="7">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="K473" s="7"/>
       <c r="L473" s="7"/>
@@ -16547,7 +16552,7 @@
       </c>
       <c r="D474" s="7"/>
       <c t="s" r="E474" s="7">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="F474" s="7">
         <v>321</v>
@@ -16562,7 +16567,7 @@
         <v>133</v>
       </c>
       <c t="s" r="J474" s="7">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K474" s="7"/>
       <c r="L474" s="7"/>
@@ -16580,7 +16585,7 @@
       </c>
       <c r="D475" s="7"/>
       <c t="s" r="E475" s="7">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="F475" s="7">
         <v>321</v>
@@ -16628,7 +16633,7 @@
       </c>
       <c r="D477" s="7"/>
       <c t="s" r="E477" s="7">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="F477" s="7">
         <v>321</v>
@@ -16643,12 +16648,12 @@
         <v>152</v>
       </c>
       <c t="s" r="J477" s="7">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="K477" s="7"/>
       <c r="L477" s="7"/>
       <c t="s" r="M477" s="7">
-        <v>449</v>
+        <v>453</v>
       </c>
     </row>
     <row r="478" ht="14.25" customHeight="1">
@@ -16663,7 +16668,7 @@
       </c>
       <c r="D478" s="7"/>
       <c t="s" r="E478" s="7">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="F478" s="7">
         <v>321</v>
@@ -16675,7 +16680,7 @@
         <v>59</v>
       </c>
       <c t="s" r="I478" s="7">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c t="s" r="J478" s="7">
         <v>38</v>
@@ -16698,7 +16703,7 @@
       </c>
       <c r="D479" s="7"/>
       <c t="s" r="E479" s="7">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="F479" s="7">
         <v>321</v>
@@ -16731,7 +16736,7 @@
       </c>
       <c r="D480" s="7"/>
       <c t="s" r="E480" s="7">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="F480" s="7">
         <v>321</v>
@@ -16743,7 +16748,7 @@
         <v>59</v>
       </c>
       <c t="s" r="I480" s="7">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c t="s" r="J480" s="7">
         <v>83</v>
@@ -16764,7 +16769,7 @@
       </c>
       <c r="D481" s="7"/>
       <c t="s" r="E481" s="7">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="F481" s="7">
         <v>321</v>
@@ -16790,14 +16795,14 @@
         <v>13</v>
       </c>
       <c r="B482" s="7">
-        <v>3908</v>
+        <v>148</v>
       </c>
       <c t="s" r="C482" s="7">
         <v>14</v>
       </c>
       <c r="D482" s="7"/>
       <c t="s" r="E482" s="7">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="F482" s="7">
         <v>321</v>
@@ -16806,50 +16811,58 @@
         <v>16</v>
       </c>
       <c t="s" r="H482" s="8">
-        <v>312</v>
+        <v>59</v>
       </c>
       <c t="s" r="I482" s="7">
-        <v>55</v>
+        <v>257</v>
       </c>
       <c t="s" r="J482" s="7">
-        <v>450</v>
-      </c>
-      <c r="K482" s="7"/>
+        <v>270</v>
+      </c>
+      <c t="s" r="K482" s="7">
+        <v>203</v>
+      </c>
       <c r="L482" s="7"/>
-      <c r="M482" s="7"/>
+      <c t="s" r="M482" s="7">
+        <v>124</v>
+      </c>
     </row>
     <row r="483" ht="14.25" customHeight="1">
       <c t="s" r="A483" s="6">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="B483" s="7">
-        <v>3909</v>
+        <v>155</v>
       </c>
       <c t="s" r="C483" s="7">
         <v>14</v>
       </c>
       <c r="D483" s="7"/>
       <c t="s" r="E483" s="7">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="F483" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G483" s="8">
-        <v>312</v>
+        <v>59</v>
       </c>
       <c t="s" r="H483" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I483" s="7">
-        <v>451</v>
+        <v>190</v>
       </c>
       <c t="s" r="J483" s="7">
-        <v>452</v>
-      </c>
-      <c r="K483" s="7"/>
+        <v>280</v>
+      </c>
+      <c t="s" r="K483" s="7">
+        <v>305</v>
+      </c>
       <c r="L483" s="7"/>
-      <c r="M483" s="7"/>
+      <c t="s" r="M483" s="7">
+        <v>84</v>
+      </c>
     </row>
     <row r="484" ht="14.25" customHeight="1">
       <c r="A484" s="6"/>
@@ -16878,7 +16891,7 @@
       </c>
       <c r="D485" s="7"/>
       <c t="s" r="E485" s="7">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F485" s="7">
         <v>321</v>
@@ -16890,7 +16903,7 @@
         <v>183</v>
       </c>
       <c t="s" r="I485" s="7">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c t="s" r="J485" s="7">
         <v>246</v>
@@ -16898,7 +16911,7 @@
       <c r="K485" s="7"/>
       <c r="L485" s="7"/>
       <c t="s" r="M485" s="7">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="486" ht="14.25" customHeight="1">
@@ -16913,7 +16926,7 @@
       </c>
       <c r="D486" s="7"/>
       <c t="s" r="E486" s="7">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F486" s="7">
         <v>321</v>
@@ -16933,7 +16946,7 @@
       <c r="K486" s="7"/>
       <c r="L486" s="7"/>
       <c t="s" r="M486" s="7">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="487" ht="14.25" customHeight="1">
@@ -16948,7 +16961,7 @@
       </c>
       <c r="D487" s="7"/>
       <c t="s" r="E487" s="7">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F487" s="7">
         <v>321</v>
@@ -16968,7 +16981,7 @@
       <c r="K487" s="7"/>
       <c r="L487" s="7"/>
       <c t="s" r="M487" s="7">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="488" ht="14.25" customHeight="1">
@@ -16983,7 +16996,7 @@
       </c>
       <c r="D488" s="7"/>
       <c t="s" r="E488" s="7">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F488" s="7">
         <v>321</v>
@@ -16998,7 +17011,7 @@
         <v>91</v>
       </c>
       <c t="s" r="J488" s="7">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="K488" s="7"/>
       <c r="L488" s="7"/>
@@ -17016,7 +17029,7 @@
       </c>
       <c r="D489" s="7"/>
       <c t="s" r="E489" s="7">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F489" s="7">
         <v>321</v>
@@ -17049,7 +17062,7 @@
       </c>
       <c r="D490" s="7"/>
       <c t="s" r="E490" s="7">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F490" s="7">
         <v>321</v>
@@ -17061,7 +17074,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I490" s="7">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c t="s" r="J490" s="7">
         <v>97</v>
@@ -17082,7 +17095,7 @@
       </c>
       <c r="D491" s="7"/>
       <c t="s" r="E491" s="7">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F491" s="7">
         <v>321</v>
@@ -17115,7 +17128,7 @@
       </c>
       <c r="D492" s="7"/>
       <c t="s" r="E492" s="7">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F492" s="7">
         <v>321</v>
@@ -17148,7 +17161,7 @@
       </c>
       <c r="D493" s="7"/>
       <c t="s" r="E493" s="7">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F493" s="7">
         <v>321</v>
@@ -17163,7 +17176,7 @@
         <v>124</v>
       </c>
       <c t="s" r="J493" s="7">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="K493" s="7"/>
       <c r="L493" s="7"/>
@@ -17181,7 +17194,7 @@
       </c>
       <c r="D494" s="7"/>
       <c t="s" r="E494" s="7">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F494" s="7">
         <v>321</v>
@@ -17193,7 +17206,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I494" s="7">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c t="s" r="J494" s="7">
         <v>33</v>
@@ -17229,7 +17242,7 @@
       </c>
       <c r="D496" s="7"/>
       <c t="s" r="E496" s="7">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F496" s="7">
         <v>320</v>
@@ -17244,12 +17257,12 @@
         <v>326</v>
       </c>
       <c t="s" r="J496" s="7">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="K496" s="7"/>
       <c r="L496" s="7"/>
       <c t="s" r="M496" s="7">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="497" ht="14.25" customHeight="1">
@@ -17264,7 +17277,7 @@
       </c>
       <c r="D497" s="7"/>
       <c t="s" r="E497" s="7">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F497" s="7">
         <v>320</v>
@@ -17284,7 +17297,7 @@
       <c r="K497" s="7"/>
       <c r="L497" s="7"/>
       <c t="s" r="M497" s="7">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="498" ht="14.25" customHeight="1">
@@ -17299,7 +17312,7 @@
       </c>
       <c r="D498" s="7"/>
       <c t="s" r="E498" s="7">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F498" s="7">
         <v>320</v>
@@ -17314,12 +17327,12 @@
         <v>110</v>
       </c>
       <c t="s" r="J498" s="7">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="K498" s="7"/>
       <c r="L498" s="7"/>
       <c t="s" r="M498" s="7">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="499" ht="14.25" customHeight="1">
@@ -17334,7 +17347,7 @@
       </c>
       <c r="D499" s="7"/>
       <c t="s" r="E499" s="7">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F499" s="7">
         <v>320</v>
@@ -17367,7 +17380,7 @@
       </c>
       <c r="D500" s="7"/>
       <c t="s" r="E500" s="7">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F500" s="7">
         <v>320</v>
@@ -17400,7 +17413,7 @@
       </c>
       <c r="D501" s="7"/>
       <c t="s" r="E501" s="7">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F501" s="7">
         <v>320</v>
@@ -17433,7 +17446,7 @@
       </c>
       <c r="D502" s="7"/>
       <c t="s" r="E502" s="7">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F502" s="7">
         <v>320</v>
@@ -17445,7 +17458,7 @@
         <v>89</v>
       </c>
       <c t="s" r="I502" s="7">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c t="s" r="J502" s="7">
         <v>177</v>
@@ -17466,7 +17479,7 @@
       </c>
       <c r="D503" s="7"/>
       <c t="s" r="E503" s="7">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F503" s="7">
         <v>320</v>
@@ -17478,10 +17491,10 @@
         <v>59</v>
       </c>
       <c t="s" r="I503" s="7">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c t="s" r="J503" s="7">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="K503" s="7"/>
       <c r="L503" s="7"/>
@@ -17514,7 +17527,7 @@
       </c>
       <c r="D505" s="7"/>
       <c t="s" r="E505" s="7">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="F505" s="7">
         <v>321</v>
@@ -17532,11 +17545,11 @@
         <v>172</v>
       </c>
       <c t="s" r="K505" s="7">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="L505" s="7"/>
       <c t="s" r="M505" s="7">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="506" ht="14.25" customHeight="1">
@@ -17551,7 +17564,7 @@
       </c>
       <c r="D506" s="7"/>
       <c t="s" r="E506" s="7">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="F506" s="7">
         <v>321</v>
@@ -17584,7 +17597,7 @@
       </c>
       <c r="D507" s="7"/>
       <c t="s" r="E507" s="7">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="F507" s="7">
         <v>321</v>
@@ -17599,7 +17612,7 @@
         <v>270</v>
       </c>
       <c t="s" r="J507" s="7">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="K507" s="7"/>
       <c r="L507" s="7"/>
@@ -17632,7 +17645,7 @@
       </c>
       <c r="D509" s="7"/>
       <c t="s" r="E509" s="7">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="F509" s="7">
         <v>321</v>
@@ -17667,7 +17680,7 @@
       </c>
       <c r="D510" s="7"/>
       <c t="s" r="E510" s="7">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="F510" s="7">
         <v>321</v>
@@ -17687,7 +17700,7 @@
       <c r="K510" s="7"/>
       <c r="L510" s="7"/>
       <c t="s" r="M510" s="7">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="511" ht="14.25" customHeight="1">
@@ -17702,7 +17715,7 @@
       </c>
       <c r="D511" s="7"/>
       <c t="s" r="E511" s="7">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="F511" s="7">
         <v>321</v>
@@ -17711,7 +17724,7 @@
         <v>59</v>
       </c>
       <c t="s" r="H511" s="8">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c t="s" r="I511" s="7">
         <v>211</v>
@@ -17735,19 +17748,19 @@
       </c>
       <c r="D512" s="7"/>
       <c t="s" r="E512" s="7">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="F512" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G512" s="8">
+        <v>226</v>
+      </c>
+      <c t="s" r="H512" s="8">
+        <v>59</v>
+      </c>
+      <c t="s" r="I512" s="7">
         <v>227</v>
-      </c>
-      <c t="s" r="H512" s="8">
-        <v>59</v>
-      </c>
-      <c t="s" r="I512" s="7">
-        <v>228</v>
       </c>
       <c t="s" r="J512" s="7">
         <v>123</v>
@@ -17768,7 +17781,7 @@
       </c>
       <c r="D513" s="7"/>
       <c t="s" r="E513" s="7">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="F513" s="7">
         <v>321</v>
@@ -17816,7 +17829,7 @@
       </c>
       <c r="D515" s="7"/>
       <c t="s" r="E515" s="7">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F515" s="7">
         <v>320</v>
@@ -17825,10 +17838,10 @@
         <v>59</v>
       </c>
       <c t="s" r="H515" s="8">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c t="s" r="I515" s="7">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c t="s" r="J515" s="7">
         <v>328</v>
@@ -17836,7 +17849,7 @@
       <c r="K515" s="7"/>
       <c r="L515" s="7"/>
       <c t="s" r="M515" s="7">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="516" ht="14.25" customHeight="1">
@@ -17851,13 +17864,13 @@
       </c>
       <c r="D516" s="7"/>
       <c t="s" r="E516" s="7">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F516" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G516" s="8">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c t="s" r="H516" s="8">
         <v>59</v>
@@ -17871,7 +17884,7 @@
       <c r="K516" s="7"/>
       <c r="L516" s="7"/>
       <c t="s" r="M516" s="7">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="517" ht="14.25" customHeight="1">
@@ -17886,7 +17899,7 @@
       </c>
       <c r="D517" s="7"/>
       <c t="s" r="E517" s="7">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F517" s="7">
         <v>320</v>
@@ -17901,7 +17914,7 @@
         <v>209</v>
       </c>
       <c t="s" r="J517" s="7">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K517" s="7"/>
       <c r="L517" s="7"/>
@@ -17919,7 +17932,7 @@
       </c>
       <c r="D518" s="7"/>
       <c t="s" r="E518" s="7">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F518" s="7">
         <v>320</v>
@@ -17934,7 +17947,7 @@
         <v>25</v>
       </c>
       <c t="s" r="J518" s="7">
-        <v>213</v>
+        <v>111</v>
       </c>
       <c r="K518" s="7"/>
       <c r="L518" s="7"/>
@@ -17952,7 +17965,7 @@
       </c>
       <c r="D519" s="7"/>
       <c t="s" r="E519" s="7">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F519" s="7">
         <v>320</v>
@@ -17985,7 +17998,7 @@
       </c>
       <c r="D520" s="7"/>
       <c t="s" r="E520" s="7">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F520" s="7">
         <v>320</v>
@@ -18033,7 +18046,7 @@
       </c>
       <c r="D522" s="7"/>
       <c t="s" r="E522" s="7">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F522" s="7">
         <v>330</v>
@@ -18045,7 +18058,7 @@
         <v>89</v>
       </c>
       <c t="s" r="I522" s="7">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c t="s" r="J522" s="7">
         <v>72</v>
@@ -18066,7 +18079,7 @@
       </c>
       <c r="D523" s="7"/>
       <c t="s" r="E523" s="7">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F523" s="7">
         <v>330</v>
@@ -18075,13 +18088,13 @@
         <v>89</v>
       </c>
       <c t="s" r="H523" s="8">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c t="s" r="I523" s="7">
         <v>172</v>
       </c>
       <c t="s" r="J523" s="7">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="K523" s="7"/>
       <c r="L523" s="7"/>
@@ -18099,13 +18112,13 @@
       </c>
       <c r="D524" s="7"/>
       <c t="s" r="E524" s="7">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F524" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G524" s="8">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c t="s" r="H524" s="8">
         <v>89</v>
@@ -18140,14 +18153,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B526" s="7">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c t="s" r="C526" s="7">
         <v>14</v>
       </c>
       <c r="D526" s="7"/>
       <c t="s" r="E526" s="7">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F526" s="7">
         <v>330</v>
@@ -18159,17 +18172,17 @@
         <v>16</v>
       </c>
       <c t="s" r="I526" s="7">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c t="s" r="J526" s="7">
         <v>181</v>
       </c>
       <c t="s" r="K526" s="7">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="L526" s="7"/>
       <c t="s" r="M526" s="7">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="527" ht="14.25" customHeight="1">
@@ -18184,7 +18197,7 @@
       </c>
       <c r="D527" s="7"/>
       <c t="s" r="E527" s="7">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F527" s="7">
         <v>330</v>
@@ -18193,7 +18206,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H527" s="8">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c t="s" r="I527" s="7">
         <v>203</v>
@@ -18232,7 +18245,7 @@
       </c>
       <c r="D529" s="7"/>
       <c t="s" r="E529" s="7">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F529" s="7">
         <v>330</v>
@@ -18247,11 +18260,13 @@
         <v>38</v>
       </c>
       <c t="s" r="J529" s="7">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="K529" s="7"/>
       <c r="L529" s="7"/>
-      <c r="M529" s="7"/>
+      <c t="s" r="M529" s="7">
+        <v>460</v>
+      </c>
     </row>
     <row r="530" ht="15" customHeight="1">
       <c t="s" r="A530" s="6">
@@ -18265,7 +18280,7 @@
       </c>
       <c r="D530" s="7"/>
       <c t="s" r="E530" s="7">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F530" s="7">
         <v>330</v>
@@ -18274,7 +18289,7 @@
         <v>89</v>
       </c>
       <c t="s" r="H530" s="8">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c t="s" r="I530" s="7">
         <v>195</v>
@@ -18298,13 +18313,13 @@
       </c>
       <c r="D531" s="7"/>
       <c t="s" r="E531" s="7">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F531" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G531" s="8">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c t="s" r="H531" s="8">
         <v>89</v>
@@ -18313,7 +18328,7 @@
         <v>134</v>
       </c>
       <c t="s" r="J531" s="7">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="K531" s="7"/>
       <c r="L531" s="7"/>
@@ -18346,13 +18361,13 @@
       </c>
       <c r="D533" s="7"/>
       <c t="s" r="E533" s="7">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F533" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G533" s="8">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c t="s" r="H533" s="8">
         <v>16</v>
@@ -18366,7 +18381,7 @@
       <c r="K533" s="7"/>
       <c r="L533" s="7"/>
       <c t="s" r="M533" s="7">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="534" ht="14.25" customHeight="1">
@@ -18396,7 +18411,7 @@
       </c>
       <c r="D535" s="7"/>
       <c t="s" r="E535" s="7">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F535" s="7">
         <v>330</v>
@@ -18411,12 +18426,12 @@
         <v>251</v>
       </c>
       <c t="s" r="J535" s="7">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="K535" s="7"/>
       <c r="L535" s="7"/>
       <c t="s" r="M535" s="7">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="536" ht="14.25" customHeight="1">
@@ -18446,7 +18461,7 @@
       </c>
       <c r="D537" s="7"/>
       <c t="s" r="E537" s="7">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="F537" s="7">
         <v>330</v>
@@ -18455,7 +18470,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H537" s="8">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c t="s" r="I537" s="7">
         <v>248</v>
@@ -18479,13 +18494,13 @@
       </c>
       <c r="D538" s="7"/>
       <c t="s" r="E538" s="7">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="F538" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G538" s="8">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c t="s" r="H538" s="8">
         <v>16</v>
@@ -18502,7 +18517,7 @@
     </row>
     <row r="539" ht="15.75" customHeight="1">
       <c t="s" r="A539" s="9">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B539" s="9"/>
       <c r="C539" s="9"/>
@@ -18522,7 +18537,7 @@
     <row r="540" ht="66" customHeight="1"/>
     <row r="541" ht="16.5" customHeight="1">
       <c t="s" r="A541" s="10">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B541" s="10"/>
       <c r="C541" s="10"/>
@@ -18535,7 +18550,7 @@
       <c r="J541" s="10"/>
       <c r="K541" s="10"/>
       <c t="s" r="L541" s="11">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M541" s="11"/>
       <c r="N541" s="11"/>

--- a/Data/FlightPlan/FPL_09AUG26.xlsx
+++ b/Data/FlightPlan/FPL_09AUG26.xlsx
@@ -482,768 +482,777 @@
     <t>22:00</t>
   </si>
   <si>
+    <t>00:38</t>
+  </si>
+  <si>
+    <t>00:45</t>
+  </si>
+  <si>
+    <t>00:35</t>
+  </si>
+  <si>
+    <t>02:35</t>
+  </si>
+  <si>
+    <t>VN-A525</t>
+  </si>
+  <si>
+    <t>07:45</t>
+  </si>
+  <si>
+    <t>10:10</t>
+  </si>
+  <si>
+    <t>VCA</t>
+  </si>
+  <si>
+    <t>14:47</t>
+  </si>
+  <si>
+    <t>VII</t>
+  </si>
+  <si>
+    <t>17:10</t>
+  </si>
+  <si>
+    <t>17:40</t>
+  </si>
+  <si>
+    <t>19:30</t>
+  </si>
+  <si>
+    <t>19:31</t>
+  </si>
+  <si>
+    <t>20:00</t>
+  </si>
+  <si>
+    <t>21:30</t>
+  </si>
+  <si>
+    <t>01:00</t>
+  </si>
+  <si>
+    <t>08:30</t>
+  </si>
+  <si>
+    <t>VN-A526</t>
+  </si>
+  <si>
+    <t>HUI</t>
+  </si>
+  <si>
+    <t>05:30</t>
+  </si>
+  <si>
+    <t>06:49</t>
+  </si>
+  <si>
+    <t>07:25</t>
+  </si>
+  <si>
+    <t>09:03</t>
+  </si>
+  <si>
+    <t>CGK</t>
+  </si>
+  <si>
+    <t>13:22</t>
+  </si>
+  <si>
+    <t>17:37</t>
+  </si>
+  <si>
+    <t>15:55</t>
+  </si>
+  <si>
+    <t>18:40</t>
+  </si>
+  <si>
+    <t>20:44</t>
+  </si>
+  <si>
+    <t>VN-A529</t>
+  </si>
+  <si>
+    <t>11:40</t>
+  </si>
+  <si>
+    <t>14:55</t>
+  </si>
+  <si>
+    <t>15:25</t>
+  </si>
+  <si>
+    <t>VN-A534</t>
+  </si>
+  <si>
+    <t>06:50</t>
+  </si>
+  <si>
+    <t>08:48</t>
+  </si>
+  <si>
+    <t>11:50</t>
+  </si>
+  <si>
+    <t>13:35</t>
+  </si>
+  <si>
+    <t>13:55</t>
+  </si>
+  <si>
+    <t>14:05</t>
+  </si>
+  <si>
+    <t>16:42</t>
+  </si>
+  <si>
+    <t>16:20</t>
+  </si>
+  <si>
+    <t>19:32</t>
+  </si>
+  <si>
+    <t>18:15</t>
+  </si>
+  <si>
+    <t>19:40</t>
+  </si>
+  <si>
+    <t>21:44</t>
+  </si>
+  <si>
+    <t>21:10</t>
+  </si>
+  <si>
+    <t>22:30</t>
+  </si>
+  <si>
+    <t>22:20</t>
+  </si>
+  <si>
+    <t>00:07</t>
+  </si>
+  <si>
+    <t>23:00</t>
+  </si>
+  <si>
+    <t>00:20</t>
+  </si>
+  <si>
+    <t>00:15</t>
+  </si>
+  <si>
+    <t>VN-A535</t>
+  </si>
+  <si>
+    <t>06:25</t>
+  </si>
+  <si>
+    <t>08:55</t>
+  </si>
+  <si>
+    <t>08:37</t>
+  </si>
+  <si>
+    <t>BMV</t>
+  </si>
+  <si>
+    <t>10:30</t>
+  </si>
+  <si>
+    <t>12:15</t>
+  </si>
+  <si>
+    <t>12:24</t>
+  </si>
+  <si>
+    <t>12:45</t>
+  </si>
+  <si>
+    <t>14:42</t>
+  </si>
+  <si>
+    <t>TBB</t>
+  </si>
+  <si>
+    <t>15:10</t>
+  </si>
+  <si>
+    <t>16:55</t>
+  </si>
+  <si>
+    <t>19:15</t>
+  </si>
+  <si>
+    <t>19:00</t>
+  </si>
+  <si>
+    <t>NGO</t>
+  </si>
+  <si>
+    <t>01:40</t>
+  </si>
+  <si>
+    <t>VN-A536</t>
+  </si>
+  <si>
+    <t>13:05</t>
+  </si>
+  <si>
+    <t>13:15</t>
+  </si>
+  <si>
+    <t>16:28</t>
+  </si>
+  <si>
+    <t>VTE</t>
+  </si>
+  <si>
+    <t>16:50</t>
+  </si>
+  <si>
+    <t>18:50</t>
+  </si>
+  <si>
+    <t>19:44</t>
+  </si>
+  <si>
+    <t>22:25</t>
+  </si>
+  <si>
+    <t>21:05</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>VN-A537</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>19:17</t>
+  </si>
+  <si>
+    <t>BQS</t>
+  </si>
+  <si>
+    <t>19:55</t>
+  </si>
+  <si>
+    <t>03:10</t>
+  </si>
+  <si>
+    <t>03:50</t>
+  </si>
+  <si>
+    <t>VN-A539</t>
+  </si>
+  <si>
+    <t>06:00</t>
+  </si>
+  <si>
+    <t>07:34</t>
+  </si>
+  <si>
+    <t>08:15</t>
+  </si>
+  <si>
+    <t>10:05</t>
+  </si>
+  <si>
+    <t>11:45</t>
+  </si>
+  <si>
+    <t>12:13</t>
+  </si>
+  <si>
+    <t>13:30</t>
+  </si>
+  <si>
+    <t>14:25</t>
+  </si>
+  <si>
+    <t>17:02</t>
+  </si>
+  <si>
+    <t>18:55</t>
+  </si>
+  <si>
+    <t>18:58</t>
+  </si>
+  <si>
+    <t>21:40</t>
+  </si>
+  <si>
+    <t>00:25</t>
+  </si>
+  <si>
+    <t>VN-A542</t>
+  </si>
+  <si>
+    <t>10:40</t>
+  </si>
+  <si>
+    <t>14:11</t>
+  </si>
+  <si>
+    <t>15:45</t>
+  </si>
+  <si>
+    <t>20:24</t>
+  </si>
+  <si>
+    <t>18:45</t>
+  </si>
+  <si>
+    <t>20:55</t>
+  </si>
+  <si>
+    <t>21:15</t>
+  </si>
+  <si>
+    <t>23:46</t>
+  </si>
+  <si>
+    <t>VN-A543</t>
+  </si>
+  <si>
+    <t>13:33</t>
+  </si>
+  <si>
+    <t>RMQ</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t>17:56</t>
+  </si>
+  <si>
+    <t>20:19</t>
+  </si>
+  <si>
+    <t>23:05</t>
+  </si>
+  <si>
+    <t>00:05</t>
+  </si>
+  <si>
+    <t>VN-A544</t>
+  </si>
+  <si>
+    <t>09:25</t>
+  </si>
+  <si>
+    <t>TPE</t>
+  </si>
+  <si>
+    <t>22:12</t>
+  </si>
+  <si>
+    <t>23:15</t>
+  </si>
+  <si>
+    <t>VN-A547</t>
+  </si>
+  <si>
+    <t>19:10</t>
+  </si>
+  <si>
+    <t>20:40</t>
+  </si>
+  <si>
+    <t>22:55</t>
+  </si>
+  <si>
+    <t>05:35</t>
+  </si>
+  <si>
+    <t>VN-A550</t>
+  </si>
+  <si>
+    <t>12:35</t>
+  </si>
+  <si>
+    <t>15:08</t>
+  </si>
+  <si>
+    <t>20:09</t>
+  </si>
+  <si>
+    <t>20:45</t>
+  </si>
+  <si>
+    <t>23:45</t>
+  </si>
+  <si>
+    <t>00:50</t>
+  </si>
+  <si>
+    <t>02:15</t>
+  </si>
+  <si>
+    <t>VN-A551</t>
+  </si>
+  <si>
+    <t>05:40</t>
+  </si>
+  <si>
+    <t>07:30</t>
+  </si>
+  <si>
+    <t>10:57</t>
+  </si>
+  <si>
+    <t>11:10</t>
+  </si>
+  <si>
+    <t>15:43</t>
+  </si>
+  <si>
+    <t>17:35</t>
+  </si>
+  <si>
+    <t>19:57</t>
+  </si>
+  <si>
+    <t>22:13</t>
+  </si>
+  <si>
+    <t>VN-A552</t>
+  </si>
+  <si>
+    <t>05:00</t>
+  </si>
+  <si>
+    <t>08:25</t>
+  </si>
+  <si>
+    <t>05:50</t>
+  </si>
+  <si>
+    <t>12:17</t>
+  </si>
+  <si>
+    <t>13:25</t>
+  </si>
+  <si>
+    <t>12:25</t>
+  </si>
+  <si>
+    <t>14:35</t>
+  </si>
+  <si>
+    <t>16:05</t>
+  </si>
+  <si>
+    <t>17:28</t>
+  </si>
+  <si>
+    <t>21:02</t>
+  </si>
+  <si>
+    <t>21:20</t>
+  </si>
+  <si>
+    <t>01:15</t>
+  </si>
+  <si>
+    <t>03:20</t>
+  </si>
+  <si>
+    <t>VN-A553</t>
+  </si>
+  <si>
+    <t>16:46</t>
+  </si>
+  <si>
+    <t>18:10</t>
+  </si>
+  <si>
+    <t>19:18</t>
+  </si>
+  <si>
+    <t>DEL</t>
+  </si>
+  <si>
+    <t>00:33</t>
+  </si>
+  <si>
+    <t>06:35</t>
+  </si>
+  <si>
+    <t>VN-A554</t>
+  </si>
+  <si>
+    <t>06:45</t>
+  </si>
+  <si>
+    <t>08:05</t>
+  </si>
+  <si>
+    <t>08:06</t>
+  </si>
+  <si>
+    <t>18:46</t>
+  </si>
+  <si>
+    <t>20:43</t>
+  </si>
+  <si>
+    <t>22:35</t>
+  </si>
+  <si>
+    <t>23:50</t>
+  </si>
+  <si>
+    <t>VVO</t>
+  </si>
+  <si>
+    <t>VN-A575</t>
+  </si>
+  <si>
+    <t>06:15</t>
+  </si>
+  <si>
+    <t>12:16</t>
+  </si>
+  <si>
+    <t>12:55</t>
+  </si>
+  <si>
+    <t>14:45</t>
+  </si>
+  <si>
+    <t>14:34</t>
+  </si>
+  <si>
+    <t>18:47</t>
+  </si>
+  <si>
+    <t>VDH</t>
+  </si>
+  <si>
+    <t>21:47</t>
+  </si>
+  <si>
+    <t>00:03</t>
+  </si>
+  <si>
+    <t>VN-A578</t>
+  </si>
+  <si>
+    <t>04:05</t>
+  </si>
+  <si>
+    <t>07:35</t>
+  </si>
+  <si>
+    <t>09:35</t>
+  </si>
+  <si>
+    <t>09:31</t>
+  </si>
+  <si>
+    <t>15:06</t>
+  </si>
+  <si>
+    <t>18:20</t>
+  </si>
+  <si>
+    <t>18:11</t>
+  </si>
+  <si>
+    <t>BOM</t>
+  </si>
+  <si>
+    <t>01:14</t>
+  </si>
+  <si>
+    <t>07:15</t>
+  </si>
+  <si>
+    <t>VN-A580</t>
+  </si>
+  <si>
+    <t>09:48</t>
+  </si>
+  <si>
+    <t>10:20</t>
+  </si>
+  <si>
+    <t>12:08</t>
+  </si>
+  <si>
+    <t>VN-A607</t>
+  </si>
+  <si>
+    <t>KHH</t>
+  </si>
+  <si>
+    <t>HKG</t>
+  </si>
+  <si>
+    <t>22:11</t>
+  </si>
+  <si>
+    <t>VN-A629</t>
+  </si>
+  <si>
+    <t>13:51</t>
+  </si>
+  <si>
+    <t>17:53</t>
+  </si>
+  <si>
+    <t>20:07</t>
+  </si>
+  <si>
+    <t>01:05</t>
+  </si>
+  <si>
+    <t>07:10</t>
+  </si>
+  <si>
+    <t>VN-A630</t>
+  </si>
+  <si>
+    <t>13:10</t>
+  </si>
+  <si>
+    <t>16:15</t>
+  </si>
+  <si>
+    <t>16:32</t>
+  </si>
+  <si>
+    <t>21:00</t>
+  </si>
+  <si>
+    <t>20:25</t>
+  </si>
+  <si>
+    <t>22:50</t>
+  </si>
+  <si>
+    <t>VN-A632</t>
+  </si>
+  <si>
+    <t>07:24</t>
+  </si>
+  <si>
+    <t>10:15</t>
+  </si>
+  <si>
+    <t>BKK</t>
+  </si>
+  <si>
+    <t>13:37</t>
+  </si>
+  <si>
+    <t>16:53</t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>19:38</t>
+  </si>
+  <si>
+    <t>20:20</t>
+  </si>
+  <si>
+    <t>22:40</t>
+  </si>
+  <si>
+    <t>VN-A633</t>
+  </si>
+  <si>
+    <t>06:56</t>
+  </si>
+  <si>
+    <t>08:56</t>
+  </si>
+  <si>
+    <t>MFM</t>
+  </si>
+  <si>
+    <t>16:56</t>
+  </si>
+  <si>
+    <t>19:11</t>
+  </si>
+  <si>
+    <t>VN-A634</t>
+  </si>
+  <si>
+    <t>16:07</t>
+  </si>
+  <si>
+    <t>21:23</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>01:04</t>
+  </si>
+  <si>
+    <t>02:10</t>
+  </si>
+  <si>
+    <t>03:05</t>
+  </si>
+  <si>
+    <t>VN-A635</t>
+  </si>
+  <si>
+    <t>12:10</t>
+  </si>
+  <si>
+    <t>12:42</t>
+  </si>
+  <si>
+    <t>15:15</t>
+  </si>
+  <si>
+    <t>16:38</t>
+  </si>
+  <si>
+    <t>17:55</t>
+  </si>
+  <si>
+    <t>22:48</t>
+  </si>
+  <si>
+    <t>VN-A636</t>
+  </si>
+  <si>
+    <t>06:05</t>
+  </si>
+  <si>
+    <t>08:07</t>
+  </si>
+  <si>
+    <t>08:45</t>
+  </si>
+  <si>
+    <t>11:52</t>
+  </si>
+  <si>
+    <t>12:05</t>
+  </si>
+  <si>
+    <t>17:09</t>
+  </si>
+  <si>
     <t>00:00</t>
   </si>
   <si>
-    <t>00:45</t>
-  </si>
-  <si>
-    <t>00:35</t>
-  </si>
-  <si>
-    <t>02:35</t>
-  </si>
-  <si>
-    <t>VN-A525</t>
-  </si>
-  <si>
-    <t>07:45</t>
-  </si>
-  <si>
-    <t>10:10</t>
-  </si>
-  <si>
-    <t>VCA</t>
-  </si>
-  <si>
-    <t>14:47</t>
-  </si>
-  <si>
-    <t>VII</t>
-  </si>
-  <si>
-    <t>17:10</t>
-  </si>
-  <si>
-    <t>17:40</t>
-  </si>
-  <si>
-    <t>19:30</t>
-  </si>
-  <si>
-    <t>19:31</t>
-  </si>
-  <si>
-    <t>20:00</t>
-  </si>
-  <si>
-    <t>21:30</t>
-  </si>
-  <si>
-    <t>01:00</t>
-  </si>
-  <si>
-    <t>08:30</t>
-  </si>
-  <si>
-    <t>VN-A526</t>
-  </si>
-  <si>
-    <t>HUI</t>
-  </si>
-  <si>
-    <t>05:30</t>
-  </si>
-  <si>
-    <t>06:49</t>
-  </si>
-  <si>
-    <t>07:25</t>
-  </si>
-  <si>
-    <t>09:03</t>
-  </si>
-  <si>
-    <t>CGK</t>
-  </si>
-  <si>
-    <t>13:22</t>
-  </si>
-  <si>
-    <t>17:37</t>
-  </si>
-  <si>
-    <t>15:55</t>
-  </si>
-  <si>
-    <t>18:40</t>
-  </si>
-  <si>
-    <t>20:44</t>
-  </si>
-  <si>
-    <t>VN-A529</t>
-  </si>
-  <si>
-    <t>11:40</t>
-  </si>
-  <si>
-    <t>14:55</t>
-  </si>
-  <si>
-    <t>15:25</t>
-  </si>
-  <si>
-    <t>VN-A534</t>
-  </si>
-  <si>
-    <t>06:50</t>
-  </si>
-  <si>
-    <t>08:48</t>
-  </si>
-  <si>
-    <t>11:50</t>
-  </si>
-  <si>
-    <t>13:35</t>
-  </si>
-  <si>
-    <t>13:55</t>
-  </si>
-  <si>
-    <t>14:05</t>
-  </si>
-  <si>
-    <t>16:42</t>
-  </si>
-  <si>
-    <t>16:20</t>
-  </si>
-  <si>
-    <t>19:32</t>
-  </si>
-  <si>
-    <t>18:15</t>
-  </si>
-  <si>
-    <t>19:40</t>
-  </si>
-  <si>
-    <t>21:44</t>
-  </si>
-  <si>
-    <t>21:10</t>
-  </si>
-  <si>
-    <t>22:30</t>
-  </si>
-  <si>
-    <t>22:20</t>
-  </si>
-  <si>
-    <t>23:40</t>
-  </si>
-  <si>
-    <t>23:00</t>
-  </si>
-  <si>
-    <t>00:20</t>
-  </si>
-  <si>
-    <t>00:15</t>
-  </si>
-  <si>
-    <t>VN-A535</t>
-  </si>
-  <si>
-    <t>06:25</t>
-  </si>
-  <si>
-    <t>08:55</t>
-  </si>
-  <si>
-    <t>08:37</t>
-  </si>
-  <si>
-    <t>BMV</t>
-  </si>
-  <si>
-    <t>10:30</t>
-  </si>
-  <si>
-    <t>12:15</t>
-  </si>
-  <si>
-    <t>12:24</t>
-  </si>
-  <si>
-    <t>12:45</t>
-  </si>
-  <si>
-    <t>14:42</t>
-  </si>
-  <si>
-    <t>TBB</t>
-  </si>
-  <si>
-    <t>15:10</t>
-  </si>
-  <si>
-    <t>16:55</t>
-  </si>
-  <si>
-    <t>19:15</t>
-  </si>
-  <si>
-    <t>19:00</t>
-  </si>
-  <si>
-    <t>NGO</t>
-  </si>
-  <si>
-    <t>01:40</t>
-  </si>
-  <si>
-    <t>VN-A536</t>
-  </si>
-  <si>
-    <t>13:05</t>
-  </si>
-  <si>
-    <t>13:15</t>
-  </si>
-  <si>
-    <t>16:28</t>
-  </si>
-  <si>
-    <t>VTE</t>
-  </si>
-  <si>
-    <t>16:50</t>
-  </si>
-  <si>
-    <t>18:50</t>
-  </si>
-  <si>
-    <t>19:44</t>
-  </si>
-  <si>
-    <t>22:25</t>
-  </si>
-  <si>
-    <t>21:05</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>VN-A537</t>
-  </si>
-  <si>
-    <t>09:00</t>
-  </si>
-  <si>
-    <t>19:17</t>
-  </si>
-  <si>
-    <t>BQS</t>
-  </si>
-  <si>
-    <t>19:55</t>
-  </si>
-  <si>
-    <t>03:10</t>
-  </si>
-  <si>
-    <t>03:50</t>
-  </si>
-  <si>
-    <t>VN-A539</t>
-  </si>
-  <si>
-    <t>06:00</t>
-  </si>
-  <si>
-    <t>07:34</t>
-  </si>
-  <si>
-    <t>08:15</t>
-  </si>
-  <si>
-    <t>10:05</t>
-  </si>
-  <si>
-    <t>11:45</t>
-  </si>
-  <si>
-    <t>12:13</t>
-  </si>
-  <si>
-    <t>13:30</t>
-  </si>
-  <si>
-    <t>14:25</t>
-  </si>
-  <si>
-    <t>17:02</t>
-  </si>
-  <si>
-    <t>18:55</t>
-  </si>
-  <si>
-    <t>18:58</t>
-  </si>
-  <si>
-    <t>21:40</t>
-  </si>
-  <si>
-    <t>00:25</t>
-  </si>
-  <si>
-    <t>VN-A542</t>
-  </si>
-  <si>
-    <t>10:40</t>
-  </si>
-  <si>
-    <t>14:11</t>
-  </si>
-  <si>
-    <t>15:45</t>
-  </si>
-  <si>
-    <t>20:24</t>
-  </si>
-  <si>
-    <t>18:45</t>
-  </si>
-  <si>
-    <t>20:55</t>
-  </si>
-  <si>
-    <t>21:15</t>
-  </si>
-  <si>
-    <t>23:28</t>
-  </si>
-  <si>
-    <t>VN-A543</t>
-  </si>
-  <si>
-    <t>13:33</t>
-  </si>
-  <si>
-    <t>RMQ</t>
-  </si>
-  <si>
-    <t>18:00</t>
-  </si>
-  <si>
-    <t>17:56</t>
-  </si>
-  <si>
-    <t>20:19</t>
-  </si>
-  <si>
-    <t>23:05</t>
-  </si>
-  <si>
-    <t>00:05</t>
-  </si>
-  <si>
-    <t>VN-A544</t>
-  </si>
-  <si>
-    <t>09:25</t>
-  </si>
-  <si>
-    <t>TPE</t>
-  </si>
-  <si>
-    <t>22:12</t>
-  </si>
-  <si>
-    <t>23:15</t>
-  </si>
-  <si>
-    <t>VN-A547</t>
-  </si>
-  <si>
-    <t>19:10</t>
-  </si>
-  <si>
-    <t>20:40</t>
-  </si>
-  <si>
-    <t>22:55</t>
-  </si>
-  <si>
-    <t>05:35</t>
-  </si>
-  <si>
-    <t>VN-A550</t>
-  </si>
-  <si>
-    <t>12:35</t>
-  </si>
-  <si>
-    <t>15:08</t>
-  </si>
-  <si>
-    <t>20:09</t>
-  </si>
-  <si>
-    <t>20:45</t>
-  </si>
-  <si>
-    <t>23:45</t>
-  </si>
-  <si>
-    <t>00:50</t>
-  </si>
-  <si>
-    <t>02:15</t>
-  </si>
-  <si>
-    <t>VN-A551</t>
-  </si>
-  <si>
-    <t>05:40</t>
-  </si>
-  <si>
-    <t>07:30</t>
-  </si>
-  <si>
-    <t>10:57</t>
-  </si>
-  <si>
-    <t>11:10</t>
-  </si>
-  <si>
-    <t>15:43</t>
-  </si>
-  <si>
-    <t>17:35</t>
-  </si>
-  <si>
-    <t>19:57</t>
-  </si>
-  <si>
-    <t>22:13</t>
-  </si>
-  <si>
-    <t>VN-A552</t>
-  </si>
-  <si>
-    <t>05:00</t>
-  </si>
-  <si>
-    <t>08:25</t>
-  </si>
-  <si>
-    <t>05:50</t>
-  </si>
-  <si>
-    <t>12:17</t>
-  </si>
-  <si>
-    <t>13:25</t>
-  </si>
-  <si>
-    <t>12:25</t>
-  </si>
-  <si>
-    <t>14:35</t>
-  </si>
-  <si>
-    <t>16:05</t>
-  </si>
-  <si>
-    <t>17:28</t>
-  </si>
-  <si>
-    <t>21:02</t>
-  </si>
-  <si>
-    <t>21:20</t>
-  </si>
-  <si>
-    <t>02:05</t>
-  </si>
-  <si>
-    <t>VN-A553</t>
-  </si>
-  <si>
-    <t>16:46</t>
-  </si>
-  <si>
-    <t>18:10</t>
-  </si>
-  <si>
-    <t>19:18</t>
-  </si>
-  <si>
-    <t>DEL</t>
-  </si>
-  <si>
-    <t>00:33</t>
-  </si>
-  <si>
-    <t>06:35</t>
-  </si>
-  <si>
-    <t>VN-A554</t>
-  </si>
-  <si>
-    <t>06:45</t>
-  </si>
-  <si>
-    <t>08:05</t>
-  </si>
-  <si>
-    <t>08:06</t>
-  </si>
-  <si>
-    <t>18:46</t>
-  </si>
-  <si>
-    <t>20:43</t>
-  </si>
-  <si>
-    <t>22:35</t>
-  </si>
-  <si>
-    <t>23:50</t>
-  </si>
-  <si>
-    <t>VVO</t>
-  </si>
-  <si>
-    <t>VN-A575</t>
-  </si>
-  <si>
-    <t>06:15</t>
-  </si>
-  <si>
-    <t>12:16</t>
-  </si>
-  <si>
-    <t>12:55</t>
-  </si>
-  <si>
-    <t>14:45</t>
-  </si>
-  <si>
-    <t>14:34</t>
-  </si>
-  <si>
-    <t>18:47</t>
-  </si>
-  <si>
-    <t>VDH</t>
-  </si>
-  <si>
-    <t>21:47</t>
-  </si>
-  <si>
-    <t>VN-A578</t>
-  </si>
-  <si>
-    <t>04:05</t>
-  </si>
-  <si>
-    <t>07:35</t>
-  </si>
-  <si>
-    <t>09:35</t>
-  </si>
-  <si>
-    <t>09:31</t>
-  </si>
-  <si>
-    <t>15:06</t>
-  </si>
-  <si>
-    <t>18:20</t>
-  </si>
-  <si>
-    <t>18:11</t>
-  </si>
-  <si>
-    <t>BOM</t>
-  </si>
-  <si>
-    <t>01:14</t>
-  </si>
-  <si>
-    <t>07:15</t>
-  </si>
-  <si>
-    <t>01:15</t>
-  </si>
-  <si>
-    <t>VN-A580</t>
-  </si>
-  <si>
-    <t>09:48</t>
-  </si>
-  <si>
-    <t>10:20</t>
-  </si>
-  <si>
-    <t>12:08</t>
-  </si>
-  <si>
-    <t>VN-A607</t>
-  </si>
-  <si>
-    <t>KHH</t>
-  </si>
-  <si>
-    <t>HKG</t>
-  </si>
-  <si>
-    <t>22:11</t>
-  </si>
-  <si>
-    <t>VN-A629</t>
-  </si>
-  <si>
-    <t>13:51</t>
-  </si>
-  <si>
-    <t>17:53</t>
-  </si>
-  <si>
-    <t>20:07</t>
-  </si>
-  <si>
-    <t>01:05</t>
-  </si>
-  <si>
-    <t>07:10</t>
-  </si>
-  <si>
-    <t>VN-A630</t>
-  </si>
-  <si>
-    <t>13:10</t>
-  </si>
-  <si>
-    <t>16:15</t>
-  </si>
-  <si>
-    <t>16:32</t>
-  </si>
-  <si>
-    <t>21:00</t>
-  </si>
-  <si>
-    <t>20:25</t>
-  </si>
-  <si>
-    <t>22:50</t>
-  </si>
-  <si>
-    <t>VN-A632</t>
-  </si>
-  <si>
-    <t>07:24</t>
-  </si>
-  <si>
-    <t>10:15</t>
-  </si>
-  <si>
-    <t>BKK</t>
-  </si>
-  <si>
-    <t>13:37</t>
-  </si>
-  <si>
-    <t>16:53</t>
-  </si>
-  <si>
-    <t>17:00</t>
-  </si>
-  <si>
-    <t>19:38</t>
-  </si>
-  <si>
-    <t>20:20</t>
-  </si>
-  <si>
-    <t>22:40</t>
-  </si>
-  <si>
-    <t>VN-A633</t>
-  </si>
-  <si>
-    <t>06:56</t>
-  </si>
-  <si>
-    <t>08:56</t>
-  </si>
-  <si>
-    <t>MFM</t>
-  </si>
-  <si>
-    <t>16:56</t>
-  </si>
-  <si>
-    <t>19:11</t>
-  </si>
-  <si>
-    <t>VN-A634</t>
-  </si>
-  <si>
-    <t>16:07</t>
-  </si>
-  <si>
-    <t>21:23</t>
-  </si>
-  <si>
-    <t>CAN</t>
-  </si>
-  <si>
-    <t>02:10</t>
-  </si>
-  <si>
-    <t>03:05</t>
-  </si>
-  <si>
-    <t>VN-A635</t>
-  </si>
-  <si>
-    <t>12:10</t>
-  </si>
-  <si>
-    <t>12:42</t>
-  </si>
-  <si>
-    <t>15:15</t>
-  </si>
-  <si>
-    <t>16:38</t>
-  </si>
-  <si>
-    <t>17:55</t>
-  </si>
-  <si>
-    <t>22:48</t>
-  </si>
-  <si>
-    <t>VN-A636</t>
-  </si>
-  <si>
-    <t>06:05</t>
-  </si>
-  <si>
-    <t>08:07</t>
-  </si>
-  <si>
-    <t>08:45</t>
-  </si>
-  <si>
-    <t>11:52</t>
-  </si>
-  <si>
-    <t>12:05</t>
-  </si>
-  <si>
-    <t>17:09</t>
-  </si>
-  <si>
     <t>21:25</t>
   </si>
   <si>
@@ -1268,6 +1277,9 @@
     <t>22:05</t>
   </si>
   <si>
+    <t>00:12</t>
+  </si>
+  <si>
     <t>00:55</t>
   </si>
   <si>
@@ -1325,6 +1337,9 @@
     <t>22:23</t>
   </si>
   <si>
+    <t>00:22</t>
+  </si>
+  <si>
     <t>VN-A641</t>
   </si>
   <si>
@@ -1442,6 +1457,9 @@
     <t>MNL</t>
   </si>
   <si>
+    <t>02:27</t>
+  </si>
+  <si>
     <t>04:45</t>
   </si>
   <si>
@@ -1469,6 +1487,9 @@
     <t>13:40</t>
   </si>
   <si>
+    <t>00:32</t>
+  </si>
+  <si>
     <t>VN-A650</t>
   </si>
   <si>
@@ -1769,7 +1790,7 @@
     <t>04:30</t>
   </si>
   <si>
-    <t>04:33</t>
+    <t>04:50</t>
   </si>
   <si>
     <t>VN-A675</t>
@@ -1949,7 +1970,7 @@
     <t>Total Record(s): 451</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Aug 09, 2026 21:50</t>
+    <t xml:space="preserve">Generated on  Aug 09, 2026 23:08</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -5857,7 +5878,9 @@
       </c>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
-      <c r="M111" s="7"/>
+      <c t="s" r="M111" s="7">
+        <v>158</v>
+      </c>
     </row>
     <row r="112" ht="14.25" customHeight="1">
       <c r="A112" s="6"/>
@@ -6203,7 +6226,7 @@
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
       <c t="s" r="M122" s="7">
-        <v>208</v>
+        <v>77</v>
       </c>
     </row>
     <row r="123" ht="14.25" customHeight="1">
@@ -7307,7 +7330,7 @@
       </c>
       <c r="L156" s="7"/>
       <c t="s" r="M156" s="7">
-        <v>117</v>
+        <v>157</v>
       </c>
     </row>
     <row r="157" ht="14.25" customHeight="1">
@@ -7340,94 +7363,98 @@
         <v>315</v>
       </c>
       <c t="s" r="K157" s="7">
-        <v>157</v>
+        <v>316</v>
       </c>
       <c r="L157" s="7"/>
       <c t="s" r="M157" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="158" ht="14.25" customHeight="1">
-      <c t="s" r="A158" s="6">
-        <v>79</v>
-      </c>
-      <c r="B158" s="7">
-        <v>862</v>
-      </c>
-      <c t="s" r="C158" s="7">
-        <v>14</v>
-      </c>
+      <c r="A158" s="6"/>
+      <c r="B158" s="7"/>
+      <c r="C158" s="7"/>
       <c r="D158" s="7"/>
-      <c t="s" r="E158" s="7">
-        <v>304</v>
-      </c>
-      <c r="F158" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G158" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H158" s="8">
-        <v>31</v>
-      </c>
-      <c t="s" r="I158" s="7">
-        <v>160</v>
-      </c>
-      <c t="s" r="J158" s="7">
-        <v>58</v>
-      </c>
+      <c r="E158" s="7"/>
+      <c r="F158" s="7"/>
+      <c r="G158" s="8"/>
+      <c r="H158" s="8"/>
+      <c r="I158" s="7"/>
+      <c r="J158" s="7"/>
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
       <c r="M158" s="7"/>
     </row>
     <row r="159" ht="14.25" customHeight="1">
-      <c r="A159" s="6"/>
-      <c r="B159" s="7"/>
-      <c r="C159" s="7"/>
+      <c t="s" r="A159" s="6">
+        <v>13</v>
+      </c>
+      <c r="B159" s="7">
+        <v>829</v>
+      </c>
+      <c t="s" r="C159" s="7">
+        <v>14</v>
+      </c>
       <c r="D159" s="7"/>
-      <c r="E159" s="7"/>
-      <c r="F159" s="7"/>
-      <c r="G159" s="8"/>
-      <c r="H159" s="8"/>
-      <c r="I159" s="7"/>
-      <c r="J159" s="7"/>
+      <c t="s" r="E159" s="7">
+        <v>318</v>
+      </c>
+      <c r="F159" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G159" s="8">
+        <v>69</v>
+      </c>
+      <c t="s" r="H159" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I159" s="7">
+        <v>38</v>
+      </c>
+      <c t="s" r="J159" s="7">
+        <v>45</v>
+      </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
-      <c r="M159" s="7"/>
+      <c t="s" r="M159" s="7">
+        <v>196</v>
+      </c>
     </row>
     <row r="160" ht="15" customHeight="1">
       <c t="s" r="A160" s="6">
         <v>13</v>
       </c>
       <c r="B160" s="7">
-        <v>829</v>
+        <v>214</v>
       </c>
       <c t="s" r="C160" s="7">
         <v>14</v>
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G160" s="8">
-        <v>69</v>
+        <v>16</v>
       </c>
       <c t="s" r="H160" s="8">
-        <v>16</v>
+        <v>166</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>45</v>
-      </c>
-      <c r="K160" s="7"/>
+        <v>28</v>
+      </c>
+      <c t="s" r="K160" s="7">
+        <v>109</v>
+      </c>
       <c r="L160" s="7"/>
       <c t="s" r="M160" s="7">
-        <v>196</v>
+        <v>319</v>
       </c>
     </row>
     <row r="161" ht="14.25" customHeight="1">
@@ -7435,36 +7462,36 @@
         <v>13</v>
       </c>
       <c r="B161" s="7">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c t="s" r="C161" s="7">
         <v>14</v>
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G161" s="8">
-        <v>16</v>
+        <v>166</v>
       </c>
       <c t="s" r="H161" s="8">
-        <v>166</v>
+        <v>16</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>47</v>
+        <v>199</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>28</v>
+        <v>320</v>
       </c>
       <c t="s" r="K161" s="7">
-        <v>109</v>
+        <v>233</v>
       </c>
       <c r="L161" s="7"/>
       <c t="s" r="M161" s="7">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="162" ht="14.25" customHeight="1">
@@ -7472,156 +7499,154 @@
         <v>13</v>
       </c>
       <c r="B162" s="7">
-        <v>213</v>
+        <v>895</v>
       </c>
       <c t="s" r="C162" s="7">
         <v>14</v>
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G162" s="8">
-        <v>166</v>
+        <v>16</v>
       </c>
       <c t="s" r="H162" s="8">
-        <v>16</v>
+        <v>322</v>
       </c>
       <c t="s" r="I162" s="7">
-        <v>199</v>
+        <v>115</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>319</v>
+        <v>285</v>
       </c>
       <c t="s" r="K162" s="7">
-        <v>233</v>
+        <v>154</v>
       </c>
       <c r="L162" s="7"/>
       <c t="s" r="M162" s="7">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="163" ht="14.25" customHeight="1">
       <c t="s" r="A163" s="6">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="B163" s="7">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c t="s" r="C163" s="7">
         <v>14</v>
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G163" s="8">
-        <v>16</v>
+        <v>322</v>
       </c>
       <c t="s" r="H163" s="8">
-        <v>321</v>
+        <v>16</v>
       </c>
       <c t="s" r="I163" s="7">
-        <v>115</v>
+        <v>276</v>
       </c>
       <c t="s" r="J163" s="7">
-        <v>285</v>
-      </c>
-      <c t="s" r="K163" s="7">
-        <v>154</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="K163" s="7"/>
       <c r="L163" s="7"/>
-      <c t="s" r="M163" s="7">
-        <v>322</v>
-      </c>
+      <c r="M163" s="7"/>
     </row>
     <row r="164" ht="14.25" customHeight="1">
-      <c t="s" r="A164" s="6">
-        <v>79</v>
-      </c>
-      <c r="B164" s="7">
-        <v>896</v>
-      </c>
-      <c t="s" r="C164" s="7">
-        <v>14</v>
-      </c>
+      <c r="A164" s="6"/>
+      <c r="B164" s="7"/>
+      <c r="C164" s="7"/>
       <c r="D164" s="7"/>
-      <c t="s" r="E164" s="7">
-        <v>317</v>
-      </c>
-      <c r="F164" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G164" s="8">
-        <v>321</v>
-      </c>
-      <c t="s" r="H164" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I164" s="7">
-        <v>276</v>
-      </c>
-      <c t="s" r="J164" s="7">
-        <v>323</v>
-      </c>
+      <c r="E164" s="7"/>
+      <c r="F164" s="7"/>
+      <c r="G164" s="8"/>
+      <c r="H164" s="8"/>
+      <c r="I164" s="7"/>
+      <c r="J164" s="7"/>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
       <c r="M164" s="7"/>
     </row>
     <row r="165" ht="15" customHeight="1">
-      <c r="A165" s="6"/>
-      <c r="B165" s="7"/>
-      <c r="C165" s="7"/>
+      <c t="s" r="A165" s="6">
+        <v>13</v>
+      </c>
+      <c r="B165" s="7">
+        <v>2987</v>
+      </c>
+      <c t="s" r="C165" s="7">
+        <v>238</v>
+      </c>
       <c r="D165" s="7"/>
-      <c r="E165" s="7"/>
-      <c r="F165" s="7"/>
-      <c r="G165" s="8"/>
-      <c r="H165" s="8"/>
-      <c r="I165" s="7"/>
-      <c r="J165" s="7"/>
+      <c t="s" r="E165" s="7">
+        <v>325</v>
+      </c>
+      <c r="F165" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G165" s="8">
+        <v>68</v>
+      </c>
+      <c t="s" r="H165" s="8">
+        <v>56</v>
+      </c>
+      <c t="s" r="I165" s="7">
+        <v>326</v>
+      </c>
+      <c t="s" r="J165" s="7">
+        <v>327</v>
+      </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
-      <c r="M165" s="7"/>
+      <c t="s" r="M165" s="7">
+        <v>328</v>
+      </c>
     </row>
     <row r="166" ht="14.25" customHeight="1">
       <c t="s" r="A166" s="6">
         <v>13</v>
       </c>
       <c r="B166" s="7">
-        <v>2987</v>
+        <v>510</v>
       </c>
       <c t="s" r="C166" s="7">
-        <v>238</v>
+        <v>14</v>
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G166" s="8">
+        <v>56</v>
+      </c>
+      <c t="s" r="H166" s="8">
         <v>68</v>
       </c>
-      <c t="s" r="H166" s="8">
-        <v>56</v>
-      </c>
       <c t="s" r="I166" s="7">
-        <v>325</v>
+        <v>230</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>326</v>
+        <v>311</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
       <c t="s" r="M166" s="7">
-        <v>327</v>
+        <v>110</v>
       </c>
     </row>
     <row r="167" ht="14.25" customHeight="1">
@@ -7629,34 +7654,34 @@
         <v>13</v>
       </c>
       <c r="B167" s="7">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c t="s" r="C167" s="7">
         <v>14</v>
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G167" s="8">
+        <v>68</v>
+      </c>
+      <c t="s" r="H167" s="8">
         <v>56</v>
       </c>
-      <c t="s" r="H167" s="8">
-        <v>68</v>
-      </c>
       <c t="s" r="I167" s="7">
-        <v>230</v>
+        <v>46</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>311</v>
+        <v>30</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
       <c t="s" r="M167" s="7">
-        <v>110</v>
+        <v>198</v>
       </c>
     </row>
     <row r="168" ht="14.25" customHeight="1">
@@ -7664,34 +7689,34 @@
         <v>13</v>
       </c>
       <c r="B168" s="7">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c t="s" r="C168" s="7">
         <v>14</v>
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G168" s="8">
+        <v>56</v>
+      </c>
+      <c t="s" r="H168" s="8">
         <v>68</v>
       </c>
-      <c t="s" r="H168" s="8">
-        <v>56</v>
-      </c>
       <c t="s" r="I168" s="7">
-        <v>46</v>
+        <v>223</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>30</v>
+        <v>201</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
       <c t="s" r="M168" s="7">
-        <v>198</v>
+        <v>329</v>
       </c>
     </row>
     <row r="169" ht="14.25" customHeight="1">
@@ -7699,34 +7724,36 @@
         <v>13</v>
       </c>
       <c r="B169" s="7">
-        <v>512</v>
+        <v>521</v>
       </c>
       <c t="s" r="C169" s="7">
         <v>14</v>
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G169" s="8">
+        <v>68</v>
+      </c>
+      <c t="s" r="H169" s="8">
         <v>56</v>
       </c>
-      <c t="s" r="H169" s="8">
-        <v>68</v>
-      </c>
       <c t="s" r="I169" s="7">
-        <v>223</v>
+        <v>265</v>
       </c>
       <c t="s" r="J169" s="7">
-        <v>201</v>
-      </c>
-      <c r="K169" s="7"/>
+        <v>89</v>
+      </c>
+      <c t="s" r="K169" s="7">
+        <v>225</v>
+      </c>
       <c r="L169" s="7"/>
       <c t="s" r="M169" s="7">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="170" ht="15" customHeight="1">
@@ -7734,41 +7761,39 @@
         <v>13</v>
       </c>
       <c r="B170" s="7">
-        <v>521</v>
+        <v>7988</v>
       </c>
       <c t="s" r="C170" s="7">
         <v>14</v>
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G170" s="8">
+        <v>56</v>
+      </c>
+      <c t="s" r="H170" s="8">
         <v>68</v>
       </c>
-      <c t="s" r="H170" s="8">
-        <v>56</v>
-      </c>
       <c t="s" r="I170" s="7">
-        <v>265</v>
+        <v>331</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>89</v>
-      </c>
-      <c t="s" r="K170" s="7">
-        <v>225</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="K170" s="7"/>
       <c r="L170" s="7"/>
       <c t="s" r="M170" s="7">
-        <v>329</v>
+        <v>276</v>
       </c>
     </row>
     <row r="171" ht="14.25" customHeight="1">
       <c t="s" r="A171" s="6">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="B171" s="7">
         <v>7988</v>
@@ -7778,108 +7803,110 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G171" s="8">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c t="s" r="H171" s="8">
-        <v>68</v>
+        <v>333</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>330</v>
+        <v>259</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>331</v>
+        <v>174</v>
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
       <c r="M171" s="7"/>
     </row>
     <row r="172" ht="14.25" customHeight="1">
-      <c t="s" r="A172" s="6">
-        <v>79</v>
-      </c>
-      <c r="B172" s="7">
-        <v>7988</v>
-      </c>
-      <c t="s" r="C172" s="7">
-        <v>14</v>
-      </c>
+      <c r="A172" s="6"/>
+      <c r="B172" s="7"/>
+      <c r="C172" s="7"/>
       <c r="D172" s="7"/>
-      <c t="s" r="E172" s="7">
-        <v>324</v>
-      </c>
-      <c r="F172" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G172" s="8">
-        <v>68</v>
-      </c>
-      <c t="s" r="H172" s="8">
-        <v>332</v>
-      </c>
-      <c t="s" r="I172" s="7">
-        <v>259</v>
-      </c>
-      <c t="s" r="J172" s="7">
-        <v>174</v>
-      </c>
+      <c r="E172" s="7"/>
+      <c r="F172" s="7"/>
+      <c r="G172" s="8"/>
+      <c r="H172" s="8"/>
+      <c r="I172" s="7"/>
+      <c r="J172" s="7"/>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
       <c r="M172" s="7"/>
     </row>
     <row r="173" ht="14.25" customHeight="1">
-      <c r="A173" s="6"/>
-      <c r="B173" s="7"/>
-      <c r="C173" s="7"/>
+      <c t="s" r="A173" s="6">
+        <v>13</v>
+      </c>
+      <c r="B173" s="7">
+        <v>837</v>
+      </c>
+      <c t="s" r="C173" s="7">
+        <v>14</v>
+      </c>
       <c r="D173" s="7"/>
-      <c r="E173" s="7"/>
-      <c r="F173" s="7"/>
-      <c r="G173" s="8"/>
-      <c r="H173" s="8"/>
-      <c r="I173" s="7"/>
-      <c r="J173" s="7"/>
+      <c t="s" r="E173" s="7">
+        <v>334</v>
+      </c>
+      <c r="F173" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G173" s="8">
+        <v>31</v>
+      </c>
+      <c t="s" r="H173" s="8">
+        <v>104</v>
+      </c>
+      <c t="s" r="I173" s="7">
+        <v>335</v>
+      </c>
+      <c t="s" r="J173" s="7">
+        <v>121</v>
+      </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
-      <c r="M173" s="7"/>
+      <c t="s" r="M173" s="7">
+        <v>122</v>
+      </c>
     </row>
     <row r="174" ht="14.25" customHeight="1">
       <c t="s" r="A174" s="6">
         <v>13</v>
       </c>
       <c r="B174" s="7">
-        <v>837</v>
+        <v>730</v>
       </c>
       <c t="s" r="C174" s="7">
         <v>14</v>
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G174" s="8">
-        <v>31</v>
+        <v>104</v>
       </c>
       <c t="s" r="H174" s="8">
-        <v>104</v>
+        <v>44</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>334</v>
+        <v>132</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>121</v>
+        <v>310</v>
       </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
       <c t="s" r="M174" s="7">
-        <v>122</v>
+        <v>336</v>
       </c>
     </row>
     <row r="175" ht="15" customHeight="1">
@@ -7887,34 +7914,34 @@
         <v>13</v>
       </c>
       <c r="B175" s="7">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c t="s" r="C175" s="7">
         <v>14</v>
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G175" s="8">
+        <v>44</v>
+      </c>
+      <c t="s" r="H175" s="8">
         <v>104</v>
       </c>
-      <c t="s" r="H175" s="8">
-        <v>44</v>
-      </c>
       <c t="s" r="I175" s="7">
-        <v>132</v>
+        <v>337</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>310</v>
+        <v>338</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
       <c t="s" r="M175" s="7">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="176" ht="14.25" customHeight="1">
@@ -7922,34 +7949,36 @@
         <v>13</v>
       </c>
       <c r="B176" s="7">
-        <v>731</v>
+        <v>601</v>
       </c>
       <c t="s" r="C176" s="7">
         <v>14</v>
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G176" s="8">
-        <v>44</v>
+        <v>104</v>
       </c>
       <c t="s" r="H176" s="8">
-        <v>104</v>
+        <v>16</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>336</v>
+        <v>199</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>337</v>
-      </c>
-      <c r="K176" s="7"/>
+        <v>136</v>
+      </c>
+      <c t="s" r="K176" s="7">
+        <v>125</v>
+      </c>
       <c r="L176" s="7"/>
       <c t="s" r="M176" s="7">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="177" ht="14.25" customHeight="1">
@@ -7957,36 +7986,36 @@
         <v>13</v>
       </c>
       <c r="B177" s="7">
-        <v>601</v>
+        <v>262</v>
       </c>
       <c t="s" r="C177" s="7">
         <v>14</v>
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G177" s="8">
-        <v>104</v>
+        <v>16</v>
       </c>
       <c t="s" r="H177" s="8">
-        <v>16</v>
+        <v>341</v>
       </c>
       <c t="s" r="I177" s="7">
-        <v>199</v>
+        <v>87</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c t="s" r="K177" s="7">
-        <v>125</v>
+        <v>225</v>
       </c>
       <c r="L177" s="7"/>
       <c t="s" r="M177" s="7">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="178" ht="14.25" customHeight="1">
@@ -7994,123 +8023,121 @@
         <v>13</v>
       </c>
       <c r="B178" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c t="s" r="C178" s="7">
         <v>14</v>
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G178" s="8">
-        <v>16</v>
+        <v>341</v>
       </c>
       <c t="s" r="H178" s="8">
-        <v>340</v>
+        <v>16</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>87</v>
+        <v>139</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>137</v>
+        <v>315</v>
       </c>
       <c t="s" r="K178" s="7">
-        <v>225</v>
+        <v>155</v>
       </c>
       <c r="L178" s="7"/>
       <c t="s" r="M178" s="7">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="179" ht="14.25" customHeight="1">
-      <c t="s" r="A179" s="6">
-        <v>13</v>
-      </c>
-      <c r="B179" s="7">
-        <v>263</v>
-      </c>
-      <c t="s" r="C179" s="7">
-        <v>14</v>
-      </c>
+      <c r="A179" s="6"/>
+      <c r="B179" s="7"/>
+      <c r="C179" s="7"/>
       <c r="D179" s="7"/>
-      <c t="s" r="E179" s="7">
-        <v>333</v>
-      </c>
-      <c r="F179" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G179" s="8">
-        <v>340</v>
-      </c>
-      <c t="s" r="H179" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I179" s="7">
-        <v>139</v>
-      </c>
-      <c t="s" r="J179" s="7">
-        <v>315</v>
-      </c>
-      <c t="s" r="K179" s="7">
-        <v>155</v>
-      </c>
+      <c r="E179" s="7"/>
+      <c r="F179" s="7"/>
+      <c r="G179" s="8"/>
+      <c r="H179" s="8"/>
+      <c r="I179" s="7"/>
+      <c r="J179" s="7"/>
+      <c r="K179" s="7"/>
       <c r="L179" s="7"/>
-      <c t="s" r="M179" s="7">
-        <v>292</v>
-      </c>
+      <c r="M179" s="7"/>
     </row>
     <row r="180" ht="15" customHeight="1">
-      <c r="A180" s="6"/>
-      <c r="B180" s="7"/>
-      <c r="C180" s="7"/>
+      <c t="s" r="A180" s="6">
+        <v>13</v>
+      </c>
+      <c r="B180" s="7">
+        <v>979</v>
+      </c>
+      <c t="s" r="C180" s="7">
+        <v>14</v>
+      </c>
       <c r="D180" s="7"/>
-      <c r="E180" s="7"/>
-      <c r="F180" s="7"/>
-      <c r="G180" s="8"/>
-      <c r="H180" s="8"/>
-      <c r="I180" s="7"/>
-      <c r="J180" s="7"/>
+      <c t="s" r="E180" s="7">
+        <v>344</v>
+      </c>
+      <c r="F180" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G180" s="8">
+        <v>31</v>
+      </c>
+      <c t="s" r="H180" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="I180" s="7">
+        <v>345</v>
+      </c>
+      <c t="s" r="J180" s="7">
+        <v>346</v>
+      </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
-      <c r="M180" s="7"/>
+      <c t="s" r="M180" s="7">
+        <v>70</v>
+      </c>
     </row>
     <row r="181" ht="14.25" customHeight="1">
       <c t="s" r="A181" s="6">
         <v>13</v>
       </c>
       <c r="B181" s="7">
-        <v>979</v>
+        <v>336</v>
       </c>
       <c t="s" r="C181" s="7">
         <v>14</v>
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G181" s="8">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c t="s" r="H181" s="8">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>343</v>
+        <v>174</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
       <c t="s" r="M181" s="7">
-        <v>70</v>
+        <v>348</v>
       </c>
     </row>
     <row r="182" ht="14.25" customHeight="1">
@@ -8118,34 +8145,34 @@
         <v>13</v>
       </c>
       <c r="B182" s="7">
-        <v>336</v>
+        <v>852</v>
       </c>
       <c t="s" r="C182" s="7">
         <v>14</v>
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G182" s="8">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c t="s" r="H182" s="8">
-        <v>16</v>
+        <v>271</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>174</v>
+        <v>216</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>345</v>
+        <v>27</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
       <c t="s" r="M182" s="7">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="183" ht="14.25" customHeight="1">
@@ -8153,34 +8180,34 @@
         <v>13</v>
       </c>
       <c r="B183" s="7">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c t="s" r="C183" s="7">
         <v>14</v>
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G183" s="8">
-        <v>16</v>
+        <v>271</v>
       </c>
       <c t="s" r="H183" s="8">
-        <v>271</v>
+        <v>16</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>216</v>
+        <v>28</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>27</v>
+        <v>350</v>
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
       <c t="s" r="M183" s="7">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="184" ht="14.25" customHeight="1">
@@ -8188,158 +8215,160 @@
         <v>13</v>
       </c>
       <c r="B184" s="7">
-        <v>853</v>
+        <v>883</v>
       </c>
       <c t="s" r="C184" s="7">
         <v>14</v>
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G184" s="8">
-        <v>271</v>
+        <v>16</v>
       </c>
       <c t="s" r="H184" s="8">
-        <v>16</v>
+        <v>352</v>
       </c>
       <c t="s" r="I184" s="7">
-        <v>28</v>
+        <v>202</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>348</v>
-      </c>
-      <c r="K184" s="7"/>
+        <v>281</v>
+      </c>
+      <c t="s" r="K184" s="7">
+        <v>284</v>
+      </c>
       <c r="L184" s="7"/>
       <c t="s" r="M184" s="7">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="185" ht="15" customHeight="1">
       <c t="s" r="A185" s="6">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="B185" s="7">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c t="s" r="C185" s="7">
         <v>14</v>
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G185" s="8">
-        <v>16</v>
+        <v>352</v>
       </c>
       <c t="s" r="H185" s="8">
-        <v>350</v>
+        <v>16</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c t="s" r="J185" s="7">
-        <v>281</v>
+        <v>354</v>
       </c>
       <c t="s" r="K185" s="7">
-        <v>284</v>
+        <v>316</v>
       </c>
       <c r="L185" s="7"/>
       <c t="s" r="M185" s="7">
-        <v>351</v>
+        <v>249</v>
       </c>
     </row>
     <row r="186" ht="14.25" customHeight="1">
-      <c t="s" r="A186" s="6">
-        <v>79</v>
-      </c>
-      <c r="B186" s="7">
-        <v>884</v>
-      </c>
-      <c t="s" r="C186" s="7">
-        <v>14</v>
-      </c>
+      <c r="A186" s="6"/>
+      <c r="B186" s="7"/>
+      <c r="C186" s="7"/>
       <c r="D186" s="7"/>
-      <c t="s" r="E186" s="7">
-        <v>342</v>
-      </c>
-      <c r="F186" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G186" s="8">
-        <v>350</v>
-      </c>
-      <c t="s" r="H186" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I186" s="7">
-        <v>210</v>
-      </c>
-      <c t="s" r="J186" s="7">
-        <v>352</v>
-      </c>
-      <c t="s" r="K186" s="7">
-        <v>353</v>
-      </c>
+      <c r="E186" s="7"/>
+      <c r="F186" s="7"/>
+      <c r="G186" s="8"/>
+      <c r="H186" s="8"/>
+      <c r="I186" s="7"/>
+      <c r="J186" s="7"/>
+      <c r="K186" s="7"/>
       <c r="L186" s="7"/>
-      <c t="s" r="M186" s="7">
-        <v>249</v>
-      </c>
+      <c r="M186" s="7"/>
     </row>
     <row r="187" ht="14.25" customHeight="1">
-      <c r="A187" s="6"/>
-      <c r="B187" s="7"/>
-      <c r="C187" s="7"/>
+      <c t="s" r="A187" s="6">
+        <v>13</v>
+      </c>
+      <c r="B187" s="7">
+        <v>632</v>
+      </c>
+      <c t="s" r="C187" s="7">
+        <v>14</v>
+      </c>
       <c r="D187" s="7"/>
-      <c r="E187" s="7"/>
-      <c r="F187" s="7"/>
-      <c r="G187" s="8"/>
-      <c r="H187" s="8"/>
-      <c r="I187" s="7"/>
-      <c r="J187" s="7"/>
+      <c t="s" r="E187" s="7">
+        <v>355</v>
+      </c>
+      <c r="F187" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G187" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H187" s="8">
+        <v>56</v>
+      </c>
+      <c t="s" r="I187" s="7">
+        <v>297</v>
+      </c>
+      <c t="s" r="J187" s="7">
+        <v>18</v>
+      </c>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
-      <c r="M187" s="7"/>
+      <c t="s" r="M187" s="7">
+        <v>356</v>
+      </c>
     </row>
     <row r="188" ht="14.25" customHeight="1">
       <c t="s" r="A188" s="6">
         <v>13</v>
       </c>
       <c r="B188" s="7">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c t="s" r="C188" s="7">
         <v>14</v>
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G188" s="8">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c t="s" r="H188" s="8">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>297</v>
+        <v>38</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>18</v>
-      </c>
-      <c r="K188" s="7"/>
+        <v>19</v>
+      </c>
+      <c t="s" r="K188" s="7">
+        <v>357</v>
+      </c>
       <c r="L188" s="7"/>
       <c t="s" r="M188" s="7">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="189" ht="14.25" customHeight="1">
@@ -8347,36 +8376,34 @@
         <v>13</v>
       </c>
       <c r="B189" s="7">
-        <v>627</v>
+        <v>860</v>
       </c>
       <c t="s" r="C189" s="7">
         <v>14</v>
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G189" s="8">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c t="s" r="H189" s="8">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>19</v>
-      </c>
-      <c t="s" r="K189" s="7">
-        <v>356</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="K189" s="7"/>
       <c r="L189" s="7"/>
       <c t="s" r="M189" s="7">
-        <v>357</v>
+        <v>52</v>
       </c>
     </row>
     <row r="190" ht="15" customHeight="1">
@@ -8384,70 +8411,68 @@
         <v>13</v>
       </c>
       <c r="B190" s="7">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c t="s" r="C190" s="7">
         <v>14</v>
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G190" s="8">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c t="s" r="H190" s="8">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c t="s" r="I190" s="7">
-        <v>42</v>
+        <v>267</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
       <c t="s" r="M190" s="7">
-        <v>52</v>
+        <v>118</v>
       </c>
     </row>
     <row r="191" ht="14.25" customHeight="1">
       <c t="s" r="A191" s="6">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="B191" s="7">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c t="s" r="C191" s="7">
         <v>14</v>
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G191" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H191" s="8">
         <v>31</v>
       </c>
-      <c t="s" r="H191" s="8">
-        <v>16</v>
-      </c>
       <c t="s" r="I191" s="7">
-        <v>267</v>
+        <v>160</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>99</v>
+        <v>58</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
-      <c t="s" r="M191" s="7">
-        <v>118</v>
-      </c>
+      <c r="M191" s="7"/>
     </row>
     <row r="192" ht="14.25" customHeight="1">
       <c r="A192" s="6"/>
@@ -8476,7 +8501,7 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
@@ -8485,7 +8510,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H193" s="8">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c t="s" r="I193" s="7">
         <v>297</v>
@@ -8511,13 +8536,13 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G194" s="8">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c t="s" r="H194" s="8">
         <v>16</v>
@@ -8546,7 +8571,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -8555,7 +8580,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H195" s="8">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c t="s" r="I195" s="7">
         <v>61</v>
@@ -8581,13 +8606,13 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G196" s="8">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c t="s" r="H196" s="8">
         <v>16</v>
@@ -8601,7 +8626,7 @@
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
       <c t="s" r="M196" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="197" ht="14.25" customHeight="1">
@@ -8616,7 +8641,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -8664,7 +8689,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -8676,7 +8701,7 @@
         <v>143</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c t="s" r="J199" s="7">
         <v>196</v>
@@ -8684,7 +8709,7 @@
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
       <c t="s" r="M199" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="200" ht="15" customHeight="1">
@@ -8699,7 +8724,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -8719,7 +8744,7 @@
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
       <c t="s" r="M200" s="7">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="201" ht="14.25" customHeight="1">
@@ -8734,7 +8759,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -8754,7 +8779,7 @@
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
       <c t="s" r="M201" s="7">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="202" ht="14.25" customHeight="1">
@@ -8769,7 +8794,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -8804,7 +8829,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -8816,10 +8841,10 @@
         <v>92</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c t="s" r="J203" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
@@ -8852,7 +8877,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -8872,7 +8897,7 @@
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
       <c t="s" r="M205" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="206" ht="14.25" customHeight="1">
@@ -8887,7 +8912,7 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -8902,12 +8927,12 @@
         <v>197</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
       <c t="s" r="M206" s="7">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="207" ht="14.25" customHeight="1">
@@ -8922,7 +8947,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -8957,7 +8982,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -8972,10 +8997,10 @@
         <v>202</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c t="s" r="K208" s="7">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L208" s="7"/>
       <c t="s" r="M208" s="7">
@@ -8994,7 +9019,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -9009,14 +9034,14 @@
         <v>172</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c t="s" r="K209" s="7">
         <v>206</v>
       </c>
       <c r="L209" s="7"/>
       <c t="s" r="M209" s="7">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="210" ht="15" customHeight="1">
@@ -9046,7 +9071,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -9061,12 +9086,12 @@
         <v>177</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
       <c t="s" r="M211" s="7">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="212" ht="14.25" customHeight="1">
@@ -9081,7 +9106,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -9096,12 +9121,12 @@
         <v>102</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
       <c t="s" r="M212" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="213" ht="14.25" customHeight="1">
@@ -9116,7 +9141,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -9125,7 +9150,7 @@
         <v>68</v>
       </c>
       <c t="s" r="H213" s="8">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c t="s" r="I213" s="7">
         <v>299</v>
@@ -9136,7 +9161,7 @@
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
       <c t="s" r="M213" s="7">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="214" ht="14.25" customHeight="1">
@@ -9151,13 +9176,13 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G214" s="8">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c t="s" r="H214" s="8">
         <v>68</v>
@@ -9171,7 +9196,7 @@
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
       <c t="s" r="M214" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="215" ht="15" customHeight="1">
@@ -9186,7 +9211,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -9198,7 +9223,7 @@
         <v>164</v>
       </c>
       <c t="s" r="I215" s="7">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c t="s" r="J215" s="7">
         <v>283</v>
@@ -9206,7 +9231,7 @@
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
       <c t="s" r="M215" s="7">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="216" ht="14.25" customHeight="1">
@@ -9221,7 +9246,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -9239,11 +9264,11 @@
         <v>128</v>
       </c>
       <c t="s" r="K216" s="7">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L216" s="7"/>
       <c t="s" r="M216" s="7">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="217" ht="14.25" customHeight="1">
@@ -9273,7 +9298,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -9293,7 +9318,7 @@
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
       <c t="s" r="M218" s="7">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="219" ht="14.25" customHeight="1">
@@ -9308,7 +9333,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -9328,7 +9353,7 @@
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
       <c t="s" r="M219" s="7">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="220" ht="15" customHeight="1">
@@ -9343,7 +9368,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -9378,7 +9403,7 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
@@ -9387,18 +9412,18 @@
         <v>104</v>
       </c>
       <c t="s" r="H221" s="8">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c t="s" r="I221" s="7">
         <v>196</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
       <c t="s" r="M221" s="7">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="222" ht="14.25" customHeight="1">
@@ -9413,13 +9438,13 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G222" s="8">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c t="s" r="H222" s="8">
         <v>104</v>
@@ -9433,7 +9458,7 @@
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
       <c t="s" r="M222" s="7">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="223" ht="14.25" customHeight="1">
@@ -9463,7 +9488,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -9498,7 +9523,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -9518,7 +9543,7 @@
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
       <c t="s" r="M225" s="7">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="226" ht="14.25" customHeight="1">
@@ -9533,7 +9558,7 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -9570,7 +9595,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -9582,7 +9607,7 @@
         <v>68</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c t="s" r="J227" s="7">
         <v>152</v>
@@ -9592,7 +9617,7 @@
       </c>
       <c r="L227" s="7"/>
       <c t="s" r="M227" s="7">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="228" ht="14.25" customHeight="1">
@@ -9607,7 +9632,7 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
@@ -9616,7 +9641,7 @@
         <v>68</v>
       </c>
       <c t="s" r="H228" s="8">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c t="s" r="I228" s="7">
         <v>205</v>
@@ -9626,7 +9651,9 @@
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
-      <c r="M228" s="7"/>
+      <c t="s" r="M228" s="7">
+        <v>396</v>
+      </c>
     </row>
     <row r="229" ht="14.25" customHeight="1">
       <c t="s" r="A229" s="6">
@@ -9640,22 +9667,22 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G229" s="8">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c t="s" r="H229" s="8">
         <v>68</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
@@ -9688,7 +9715,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -9723,7 +9750,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -9738,7 +9765,7 @@
         <v>18</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
@@ -9758,7 +9785,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -9773,12 +9800,12 @@
         <v>60</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
       <c t="s" r="M233" s="7">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="234" ht="14.25" customHeight="1">
@@ -9793,7 +9820,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -9808,12 +9835,12 @@
         <v>229</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
       <c t="s" r="M234" s="7">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="235" ht="15" customHeight="1">
@@ -9828,7 +9855,7 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
@@ -9843,10 +9870,10 @@
         <v>263</v>
       </c>
       <c t="s" r="J235" s="7">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c t="s" r="K235" s="7">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L235" s="7"/>
       <c t="s" r="M235" s="7">
@@ -9865,7 +9892,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -9887,7 +9914,7 @@
       </c>
       <c r="L236" s="7"/>
       <c t="s" r="M236" s="7">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="237" ht="14.25" customHeight="1">
@@ -9902,7 +9929,7 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
@@ -9954,7 +9981,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -9966,7 +9993,7 @@
         <v>68</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c t="s" r="J239" s="7">
         <v>249</v>
@@ -9974,7 +10001,7 @@
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
       <c t="s" r="M239" s="7">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="240" ht="15" customHeight="1">
@@ -9989,7 +10016,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -10001,7 +10028,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c t="s" r="J240" s="7">
         <v>19</v>
@@ -10009,7 +10036,7 @@
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
       <c t="s" r="M240" s="7">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="241" ht="14.25" customHeight="1">
@@ -10024,7 +10051,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -10033,10 +10060,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H241" s="8">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c t="s" r="J241" s="7">
         <v>253</v>
@@ -10061,13 +10088,13 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G242" s="8">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c t="s" r="H242" s="8">
         <v>16</v>
@@ -10083,7 +10110,7 @@
       </c>
       <c r="L242" s="7"/>
       <c t="s" r="M242" s="7">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="243" ht="14.25" customHeight="1">
@@ -10098,7 +10125,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -10110,7 +10137,7 @@
         <v>68</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c t="s" r="J243" s="7">
         <v>149</v>
@@ -10135,7 +10162,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -10157,7 +10184,7 @@
       </c>
       <c r="L244" s="7"/>
       <c t="s" r="M244" s="7">
-        <v>141</v>
+        <v>413</v>
       </c>
     </row>
     <row r="245" ht="15" customHeight="1">
@@ -10172,7 +10199,7 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
@@ -10184,7 +10211,7 @@
         <v>68</v>
       </c>
       <c t="s" r="I245" s="7">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c t="s" r="J245" s="7">
         <v>64</v>
@@ -10194,7 +10221,7 @@
       </c>
       <c r="L245" s="7"/>
       <c t="s" r="M245" s="7">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="246" ht="14.25" customHeight="1">
@@ -10224,7 +10251,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -10236,15 +10263,15 @@
         <v>44</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
       <c t="s" r="M247" s="7">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="248" ht="14.25" customHeight="1">
@@ -10259,7 +10286,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -10268,7 +10295,7 @@
         <v>44</v>
       </c>
       <c t="s" r="H248" s="8">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c t="s" r="I248" s="7">
         <v>310</v>
@@ -10294,13 +10321,13 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G249" s="8">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c t="s" r="H249" s="8">
         <v>44</v>
@@ -10314,7 +10341,7 @@
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
       <c t="s" r="M249" s="7">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="250" ht="15" customHeight="1">
@@ -10329,7 +10356,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -10364,7 +10391,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -10382,11 +10409,11 @@
         <v>128</v>
       </c>
       <c t="s" r="K251" s="7">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="L251" s="7"/>
       <c t="s" r="M251" s="7">
-        <v>157</v>
+        <v>422</v>
       </c>
     </row>
     <row r="252" ht="14.25" customHeight="1">
@@ -10401,7 +10428,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
@@ -10416,7 +10443,7 @@
         <v>64</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c t="s" r="K252" s="7">
         <v>159</v>
@@ -10453,7 +10480,7 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
@@ -10468,12 +10495,12 @@
         <v>247</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
       <c t="s" r="M254" s="7">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="255" ht="15" customHeight="1">
@@ -10488,7 +10515,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
@@ -10503,12 +10530,12 @@
         <v>70</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
       <c t="s" r="M255" s="7">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="256" ht="14.25" customHeight="1">
@@ -10523,7 +10550,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
@@ -10543,7 +10570,7 @@
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
       <c t="s" r="M256" s="7">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="257" ht="14.25" customHeight="1">
@@ -10558,7 +10585,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
@@ -10578,7 +10605,7 @@
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
       <c t="s" r="M257" s="7">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="258" ht="14.25" customHeight="1">
@@ -10593,7 +10620,7 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
@@ -10605,7 +10632,7 @@
         <v>26</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c t="s" r="J258" s="7">
         <v>184</v>
@@ -10613,7 +10640,7 @@
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
       <c t="s" r="M258" s="7">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="259" ht="14.25" customHeight="1">
@@ -10628,7 +10655,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
@@ -10648,7 +10675,7 @@
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
       <c t="s" r="M259" s="7">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="260" ht="15" customHeight="1">
@@ -10663,7 +10690,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
@@ -10683,7 +10710,7 @@
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
       <c t="s" r="M260" s="7">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="261" ht="14.25" customHeight="1">
@@ -10698,7 +10725,7 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
@@ -10710,14 +10737,16 @@
         <v>56</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
-      <c r="M261" s="7"/>
+      <c t="s" r="M261" s="7">
+        <v>332</v>
+      </c>
     </row>
     <row r="262" ht="14.25" customHeight="1">
       <c r="A262" s="6"/>
@@ -10746,7 +10775,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
@@ -10758,7 +10787,7 @@
         <v>104</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c t="s" r="J263" s="7">
         <v>179</v>
@@ -10766,7 +10795,7 @@
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
       <c t="s" r="M263" s="7">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="264" ht="14.25" customHeight="1">
@@ -10781,7 +10810,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
@@ -10816,7 +10845,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
@@ -10836,7 +10865,7 @@
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
       <c t="s" r="M265" s="7">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="266" ht="14.25" customHeight="1">
@@ -10851,7 +10880,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
@@ -10871,7 +10900,7 @@
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
       <c t="s" r="M266" s="7">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="267" ht="14.25" customHeight="1">
@@ -10886,7 +10915,7 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
@@ -10921,7 +10950,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
@@ -10933,7 +10962,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c t="s" r="J268" s="7">
         <v>169</v>
@@ -10956,7 +10985,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
@@ -10968,7 +10997,7 @@
         <v>176</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c t="s" r="J269" s="7">
         <v>169</v>
@@ -10978,7 +11007,7 @@
       </c>
       <c r="L269" s="7"/>
       <c t="s" r="M269" s="7">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="270" ht="15" customHeight="1">
@@ -10993,7 +11022,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
@@ -11015,7 +11044,7 @@
       </c>
       <c r="L270" s="7"/>
       <c t="s" r="M270" s="7">
-        <v>209</v>
+        <v>442</v>
       </c>
     </row>
     <row r="271" ht="14.25" customHeight="1">
@@ -11045,7 +11074,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
@@ -11080,7 +11109,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
@@ -11100,7 +11129,7 @@
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
       <c t="s" r="M273" s="7">
-        <v>439</v>
+        <v>444</v>
       </c>
     </row>
     <row r="274" ht="14.25" customHeight="1">
@@ -11115,7 +11144,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
@@ -11127,7 +11156,7 @@
         <v>104</v>
       </c>
       <c t="s" r="I274" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c t="s" r="J274" s="7">
         <v>189</v>
@@ -11135,7 +11164,7 @@
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
       <c t="s" r="M274" s="7">
-        <v>440</v>
+        <v>445</v>
       </c>
     </row>
     <row r="275" ht="15" customHeight="1">
@@ -11150,7 +11179,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -11170,7 +11199,7 @@
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
       <c t="s" r="M275" s="7">
-        <v>441</v>
+        <v>446</v>
       </c>
     </row>
     <row r="276" ht="14.25" customHeight="1">
@@ -11185,7 +11214,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
@@ -11207,7 +11236,7 @@
       </c>
       <c r="L276" s="7"/>
       <c t="s" r="M276" s="7">
-        <v>442</v>
+        <v>447</v>
       </c>
     </row>
     <row r="277" ht="14.25" customHeight="1">
@@ -11222,7 +11251,7 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
@@ -11237,12 +11266,12 @@
         <v>291</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
       <c t="s" r="M277" s="7">
-        <v>443</v>
+        <v>448</v>
       </c>
     </row>
     <row r="278" ht="14.25" customHeight="1">
@@ -11272,7 +11301,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="F279" s="7">
         <v>321</v>
@@ -11287,12 +11316,12 @@
         <v>305</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
       <c t="s" r="M279" s="7">
-        <v>445</v>
+        <v>450</v>
       </c>
     </row>
     <row r="280" ht="15" customHeight="1">
@@ -11307,7 +11336,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="F280" s="7">
         <v>321</v>
@@ -11322,12 +11351,12 @@
         <v>102</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
       <c t="s" r="M280" s="7">
-        <v>446</v>
+        <v>451</v>
       </c>
     </row>
     <row r="281" ht="14.25" customHeight="1">
@@ -11342,7 +11371,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="F281" s="7">
         <v>321</v>
@@ -11351,18 +11380,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H281" s="8">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c t="s" r="I281" s="7">
         <v>41</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
       <c t="s" r="M281" s="7">
-        <v>449</v>
+        <v>454</v>
       </c>
     </row>
     <row r="282" ht="14.25" customHeight="1">
@@ -11377,13 +11406,13 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="F282" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G282" s="8">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c t="s" r="H282" s="8">
         <v>16</v>
@@ -11397,7 +11426,7 @@
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
       <c t="s" r="M282" s="7">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="283" ht="14.25" customHeight="1">
@@ -11412,7 +11441,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="F283" s="7">
         <v>321</v>
@@ -11434,7 +11463,7 @@
       </c>
       <c r="L283" s="7"/>
       <c t="s" r="M283" s="7">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="284" ht="14.25" customHeight="1">
@@ -11449,7 +11478,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="F284" s="7">
         <v>321</v>
@@ -11464,14 +11493,14 @@
         <v>30</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c t="s" r="K284" s="7">
         <v>89</v>
       </c>
       <c r="L284" s="7"/>
       <c t="s" r="M284" s="7">
-        <v>450</v>
+        <v>455</v>
       </c>
     </row>
     <row r="285" ht="15" customHeight="1">
@@ -11501,7 +11530,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="F286" s="7">
         <v>321</v>
@@ -11521,7 +11550,7 @@
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
       <c t="s" r="M286" s="7">
-        <v>452</v>
+        <v>457</v>
       </c>
     </row>
     <row r="287" ht="14.25" customHeight="1">
@@ -11536,7 +11565,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
@@ -11548,15 +11577,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
       <c t="s" r="M287" s="7">
-        <v>453</v>
+        <v>458</v>
       </c>
     </row>
     <row r="288" ht="14.25" customHeight="1">
@@ -11571,7 +11600,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="F288" s="7">
         <v>321</v>
@@ -11586,7 +11615,7 @@
         <v>45</v>
       </c>
       <c t="s" r="J288" s="7">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
@@ -11606,7 +11635,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
@@ -11636,14 +11665,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B290" s="7">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c t="s" r="C290" s="7">
         <v>14</v>
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
@@ -11680,7 +11709,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
@@ -11692,7 +11721,7 @@
         <v>166</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c t="s" r="J291" s="7">
         <v>155</v>
@@ -11700,7 +11729,7 @@
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
       <c t="s" r="M291" s="7">
-        <v>456</v>
+        <v>461</v>
       </c>
     </row>
     <row r="292" ht="14.25" customHeight="1">
@@ -11715,7 +11744,7 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="F292" s="7">
         <v>321</v>
@@ -11763,7 +11792,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="F294" s="7">
         <v>321</v>
@@ -11775,10 +11804,10 @@
         <v>143</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
@@ -11798,7 +11827,7 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="F295" s="7">
         <v>321</v>
@@ -11810,15 +11839,15 @@
         <v>56</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c t="s" r="J295" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
       <c t="s" r="M295" s="7">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="296" ht="14.25" customHeight="1">
@@ -11833,7 +11862,7 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="F296" s="7">
         <v>321</v>
@@ -11845,15 +11874,15 @@
         <v>143</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
       <c t="s" r="M296" s="7">
-        <v>460</v>
+        <v>465</v>
       </c>
     </row>
     <row r="297" ht="14.25" customHeight="1">
@@ -11868,7 +11897,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="F297" s="7">
         <v>321</v>
@@ -11918,7 +11947,7 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="F299" s="7">
         <v>321</v>
@@ -11930,10 +11959,10 @@
         <v>44</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
@@ -11953,7 +11982,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="F300" s="7">
         <v>321</v>
@@ -11973,7 +12002,7 @@
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
       <c t="s" r="M300" s="7">
-        <v>463</v>
+        <v>468</v>
       </c>
     </row>
     <row r="301" ht="14.25" customHeight="1">
@@ -11988,7 +12017,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="F301" s="7">
         <v>321</v>
@@ -12008,7 +12037,7 @@
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
       <c t="s" r="M301" s="7">
-        <v>464</v>
+        <v>469</v>
       </c>
     </row>
     <row r="302" ht="14.25" customHeight="1">
@@ -12023,7 +12052,7 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="F302" s="7">
         <v>321</v>
@@ -12043,7 +12072,7 @@
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
       <c t="s" r="M302" s="7">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="303" ht="14.25" customHeight="1">
@@ -12058,7 +12087,7 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="F303" s="7">
         <v>321</v>
@@ -12070,7 +12099,7 @@
         <v>44</v>
       </c>
       <c t="s" r="I303" s="7">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c t="s" r="J303" s="7">
         <v>171</v>
@@ -12080,7 +12109,7 @@
       </c>
       <c r="L303" s="7"/>
       <c t="s" r="M303" s="7">
-        <v>465</v>
+        <v>470</v>
       </c>
     </row>
     <row r="304" ht="14.25" customHeight="1">
@@ -12095,7 +12124,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="F304" s="7">
         <v>321</v>
@@ -12107,10 +12136,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c t="s" r="J304" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
@@ -12143,7 +12172,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="F306" s="7">
         <v>321</v>
@@ -12158,7 +12187,7 @@
         <v>240</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
@@ -12178,7 +12207,7 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="F307" s="7">
         <v>321</v>
@@ -12193,12 +12222,12 @@
         <v>229</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
       <c t="s" r="M307" s="7">
-        <v>468</v>
+        <v>473</v>
       </c>
     </row>
     <row r="308" ht="14.25" customHeight="1">
@@ -12213,7 +12242,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="F308" s="7">
         <v>321</v>
@@ -12228,12 +12257,12 @@
         <v>71</v>
       </c>
       <c t="s" r="J308" s="7">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
       <c t="s" r="M308" s="7">
-        <v>470</v>
+        <v>475</v>
       </c>
     </row>
     <row r="309" ht="14.25" customHeight="1">
@@ -12248,7 +12277,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="F309" s="7">
         <v>321</v>
@@ -12268,7 +12297,7 @@
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
       <c t="s" r="M309" s="7">
-        <v>471</v>
+        <v>476</v>
       </c>
     </row>
     <row r="310" ht="15" customHeight="1">
@@ -12298,7 +12327,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="F311" s="7">
         <v>321</v>
@@ -12307,7 +12336,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H311" s="8">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c t="s" r="I311" s="7">
         <v>93</v>
@@ -12333,13 +12362,13 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="F312" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G312" s="8">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c t="s" r="H312" s="8">
         <v>16</v>
@@ -12368,7 +12397,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="F313" s="7">
         <v>321</v>
@@ -12383,14 +12412,14 @@
         <v>105</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c t="s" r="K313" s="7">
         <v>124</v>
       </c>
       <c r="L313" s="7"/>
       <c t="s" r="M313" s="7">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="314" ht="14.25" customHeight="1">
@@ -12405,7 +12434,7 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="F314" s="7">
         <v>321</v>
@@ -12427,7 +12456,7 @@
       </c>
       <c r="L314" s="7"/>
       <c t="s" r="M314" s="7">
-        <v>475</v>
+        <v>480</v>
       </c>
     </row>
     <row r="315" ht="15" customHeight="1">
@@ -12442,7 +12471,7 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="F315" s="7">
         <v>321</v>
@@ -12451,17 +12480,19 @@
         <v>16</v>
       </c>
       <c t="s" r="H315" s="8">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c t="s" r="I315" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
-      <c r="M315" s="7"/>
+      <c t="s" r="M315" s="7">
+        <v>482</v>
+      </c>
     </row>
     <row r="316" ht="14.25" customHeight="1">
       <c t="s" r="A316" s="6">
@@ -12475,13 +12506,13 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="F316" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G316" s="8">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c t="s" r="H316" s="8">
         <v>16</v>
@@ -12490,7 +12521,7 @@
         <v>244</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
@@ -12523,7 +12554,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="F318" s="7">
         <v>321</v>
@@ -12535,7 +12566,7 @@
         <v>181</v>
       </c>
       <c t="s" r="I318" s="7">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c t="s" r="J318" s="7">
         <v>45</v>
@@ -12543,7 +12574,7 @@
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
       <c t="s" r="M318" s="7">
-        <v>480</v>
+        <v>486</v>
       </c>
     </row>
     <row r="319" ht="14.25" customHeight="1">
@@ -12558,7 +12589,7 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="F319" s="7">
         <v>321</v>
@@ -12593,7 +12624,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="F320" s="7">
         <v>321</v>
@@ -12613,7 +12644,7 @@
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
       <c t="s" r="M320" s="7">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="321" ht="14.25" customHeight="1">
@@ -12628,7 +12659,7 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="F321" s="7">
         <v>321</v>
@@ -12647,7 +12678,9 @@
       </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
-      <c r="M321" s="7"/>
+      <c t="s" r="M321" s="7">
+        <v>207</v>
+      </c>
     </row>
     <row r="322" ht="14.25" customHeight="1">
       <c t="s" r="A322" s="6">
@@ -12661,7 +12694,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="F322" s="7">
         <v>321</v>
@@ -12709,7 +12742,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="F324" s="7">
         <v>321</v>
@@ -12729,7 +12762,7 @@
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
       <c t="s" r="M324" s="7">
-        <v>482</v>
+        <v>488</v>
       </c>
     </row>
     <row r="325" ht="15" customHeight="1">
@@ -12744,7 +12777,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="F325" s="7">
         <v>321</v>
@@ -12756,10 +12789,10 @@
         <v>215</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
@@ -12779,7 +12812,7 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="F326" s="7">
         <v>321</v>
@@ -12791,7 +12824,7 @@
         <v>166</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c t="s" r="J326" s="7">
         <v>261</v>
@@ -12799,7 +12832,7 @@
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
       <c t="s" r="M326" s="7">
-        <v>483</v>
+        <v>489</v>
       </c>
     </row>
     <row r="327" ht="14.25" customHeight="1">
@@ -12814,7 +12847,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="F327" s="7">
         <v>321</v>
@@ -12834,7 +12867,7 @@
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
       <c t="s" r="M327" s="7">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="328" ht="14.25" customHeight="1">
@@ -12849,7 +12882,7 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="F328" s="7">
         <v>321</v>
@@ -12861,7 +12894,7 @@
         <v>135</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c t="s" r="J328" s="7">
         <v>49</v>
@@ -12884,7 +12917,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="F329" s="7">
         <v>321</v>
@@ -12899,7 +12932,7 @@
         <v>133</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c t="s" r="K329" s="7">
         <v>50</v>
@@ -12921,7 +12954,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="F330" s="7">
         <v>321</v>
@@ -12936,7 +12969,7 @@
         <v>185</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c t="s" r="K330" s="7">
         <v>137</v>
@@ -12958,7 +12991,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="F331" s="7">
         <v>321</v>
@@ -12970,17 +13003,17 @@
         <v>16</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c t="s" r="K331" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L331" s="7"/>
       <c t="s" r="M331" s="7">
-        <v>259</v>
+        <v>492</v>
       </c>
     </row>
     <row r="332" ht="14.25" customHeight="1">
@@ -13010,7 +13043,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="F333" s="7">
         <v>320</v>
@@ -13025,12 +13058,12 @@
         <v>286</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
       <c t="s" r="M333" s="7">
-        <v>487</v>
+        <v>494</v>
       </c>
     </row>
     <row r="334" ht="14.25" customHeight="1">
@@ -13045,7 +13078,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="F334" s="7">
         <v>320</v>
@@ -13057,7 +13090,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c t="s" r="J334" s="7">
         <v>36</v>
@@ -13065,7 +13098,7 @@
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
       <c t="s" r="M334" s="7">
-        <v>488</v>
+        <v>495</v>
       </c>
     </row>
     <row r="335" ht="15" customHeight="1">
@@ -13080,7 +13113,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="F335" s="7">
         <v>320</v>
@@ -13095,12 +13128,12 @@
         <v>18</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
       <c t="s" r="M335" s="7">
-        <v>489</v>
+        <v>496</v>
       </c>
     </row>
     <row r="336" ht="14.25" customHeight="1">
@@ -13115,7 +13148,7 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="F336" s="7">
         <v>320</v>
@@ -13130,12 +13163,12 @@
         <v>216</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
       <c t="s" r="M336" s="7">
-        <v>491</v>
+        <v>498</v>
       </c>
     </row>
     <row r="337" ht="14.25" customHeight="1">
@@ -13150,7 +13183,7 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="F337" s="7">
         <v>320</v>
@@ -13162,10 +13195,10 @@
         <v>68</v>
       </c>
       <c t="s" r="I337" s="7">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
@@ -13185,7 +13218,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="F338" s="7">
         <v>320</v>
@@ -13207,7 +13240,7 @@
       </c>
       <c r="L338" s="7"/>
       <c t="s" r="M338" s="7">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="339" ht="14.25" customHeight="1">
@@ -13222,7 +13255,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="F339" s="7">
         <v>320</v>
@@ -13231,7 +13264,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H339" s="8">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c t="s" r="I339" s="7">
         <v>148</v>
@@ -13244,7 +13277,7 @@
       </c>
       <c r="L339" s="7"/>
       <c t="s" r="M339" s="7">
-        <v>493</v>
+        <v>500</v>
       </c>
     </row>
     <row r="340" ht="15" customHeight="1">
@@ -13259,25 +13292,25 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="F340" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G340" s="8">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c t="s" r="H340" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c t="s" r="J340" s="7">
         <v>305</v>
       </c>
       <c t="s" r="K340" s="7">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="L340" s="7"/>
       <c t="s" r="M340" s="7">
@@ -13311,7 +13344,7 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>495</v>
+        <v>502</v>
       </c>
       <c r="F342" s="7">
         <v>321</v>
@@ -13323,7 +13356,7 @@
         <v>26</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c t="s" r="J342" s="7">
         <v>39</v>
@@ -13331,7 +13364,7 @@
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
       <c t="s" r="M342" s="7">
-        <v>496</v>
+        <v>503</v>
       </c>
     </row>
     <row r="343" ht="14.25" customHeight="1">
@@ -13346,7 +13379,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>495</v>
+        <v>502</v>
       </c>
       <c r="F343" s="7">
         <v>321</v>
@@ -13358,7 +13391,7 @@
         <v>68</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c t="s" r="J343" s="7">
         <v>253</v>
@@ -13366,7 +13399,7 @@
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
       <c t="s" r="M343" s="7">
-        <v>498</v>
+        <v>505</v>
       </c>
     </row>
     <row r="344" ht="14.25" customHeight="1">
@@ -13381,7 +13414,7 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>495</v>
+        <v>502</v>
       </c>
       <c r="F344" s="7">
         <v>321</v>
@@ -13401,7 +13434,7 @@
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
       <c t="s" r="M344" s="7">
-        <v>499</v>
+        <v>506</v>
       </c>
     </row>
     <row r="345" ht="15" customHeight="1">
@@ -13416,7 +13449,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>495</v>
+        <v>502</v>
       </c>
       <c r="F345" s="7">
         <v>321</v>
@@ -13428,7 +13461,7 @@
         <v>68</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c t="s" r="J345" s="7">
         <v>149</v>
@@ -13436,7 +13469,7 @@
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
       <c t="s" r="M345" s="7">
-        <v>500</v>
+        <v>507</v>
       </c>
     </row>
     <row r="346" ht="14.25" customHeight="1">
@@ -13451,7 +13484,7 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>495</v>
+        <v>502</v>
       </c>
       <c r="F346" s="7">
         <v>321</v>
@@ -13471,7 +13504,7 @@
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
       <c t="s" r="M346" s="7">
-        <v>501</v>
+        <v>508</v>
       </c>
     </row>
     <row r="347" ht="14.25" customHeight="1">
@@ -13486,7 +13519,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>495</v>
+        <v>502</v>
       </c>
       <c r="F347" s="7">
         <v>321</v>
@@ -13534,7 +13567,7 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="F349" s="7">
         <v>321</v>
@@ -13549,12 +13582,12 @@
         <v>213</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
       <c t="s" r="M349" s="7">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="350" ht="15" customHeight="1">
@@ -13569,7 +13602,7 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="F350" s="7">
         <v>321</v>
@@ -13578,7 +13611,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H350" s="8">
-        <v>503</v>
+        <v>510</v>
       </c>
       <c t="s" r="I350" s="7">
         <v>97</v>
@@ -13589,7 +13622,7 @@
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
       <c t="s" r="M350" s="7">
-        <v>504</v>
+        <v>511</v>
       </c>
     </row>
     <row r="351" ht="14.25" customHeight="1">
@@ -13604,22 +13637,22 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="F351" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G351" s="8">
-        <v>503</v>
+        <v>510</v>
       </c>
       <c t="s" r="H351" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
@@ -13652,7 +13685,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="F353" s="7">
         <v>320</v>
@@ -13687,7 +13720,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="F354" s="7">
         <v>320</v>
@@ -13707,7 +13740,7 @@
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
       <c t="s" r="M354" s="7">
-        <v>508</v>
+        <v>515</v>
       </c>
     </row>
     <row r="355" ht="15" customHeight="1">
@@ -13722,7 +13755,7 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="F355" s="7">
         <v>320</v>
@@ -13742,7 +13775,7 @@
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
       <c t="s" r="M355" s="7">
-        <v>509</v>
+        <v>516</v>
       </c>
     </row>
     <row r="356" ht="14.25" customHeight="1">
@@ -13757,7 +13790,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="F356" s="7">
         <v>320</v>
@@ -13772,12 +13805,12 @@
         <v>189</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
       <c t="s" r="M356" s="7">
-        <v>510</v>
+        <v>517</v>
       </c>
     </row>
     <row r="357" ht="14.25" customHeight="1">
@@ -13792,7 +13825,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="F357" s="7">
         <v>320</v>
@@ -13812,7 +13845,7 @@
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
       <c t="s" r="M357" s="7">
-        <v>511</v>
+        <v>518</v>
       </c>
     </row>
     <row r="358" ht="14.25" customHeight="1">
@@ -13827,7 +13860,7 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="F358" s="7">
         <v>320</v>
@@ -13842,12 +13875,12 @@
         <v>139</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
       <c t="s" r="M358" s="7">
-        <v>513</v>
+        <v>520</v>
       </c>
     </row>
     <row r="359" ht="14.25" customHeight="1">
@@ -13877,7 +13910,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
@@ -13886,7 +13919,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H360" s="8">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c t="s" r="I360" s="7">
         <v>105</v>
@@ -13897,7 +13930,7 @@
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
       <c t="s" r="M360" s="7">
-        <v>515</v>
+        <v>522</v>
       </c>
     </row>
     <row r="361" ht="14.25" customHeight="1">
@@ -13912,13 +13945,13 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G361" s="8">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c t="s" r="H361" s="8">
         <v>16</v>
@@ -13932,7 +13965,7 @@
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
       <c t="s" r="M361" s="7">
-        <v>516</v>
+        <v>523</v>
       </c>
     </row>
     <row r="362" ht="14.25" customHeight="1">
@@ -13947,7 +13980,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
@@ -13962,7 +13995,7 @@
         <v>145</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
@@ -13982,7 +14015,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
@@ -14002,7 +14035,7 @@
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
       <c t="s" r="M363" s="7">
-        <v>517</v>
+        <v>524</v>
       </c>
     </row>
     <row r="364" ht="14.25" customHeight="1">
@@ -14017,7 +14050,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="F364" s="7">
         <v>321</v>
@@ -14037,7 +14070,7 @@
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
       <c t="s" r="M364" s="7">
-        <v>518</v>
+        <v>525</v>
       </c>
     </row>
     <row r="365" ht="15" customHeight="1">
@@ -14052,7 +14085,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="F365" s="7">
         <v>321</v>
@@ -14067,7 +14100,7 @@
         <v>128</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c t="s" r="K365" s="7">
         <v>208</v>
@@ -14104,7 +14137,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="F367" s="7">
         <v>320</v>
@@ -14139,7 +14172,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="F368" s="7">
         <v>320</v>
@@ -14174,7 +14207,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="F369" s="7">
         <v>320</v>
@@ -14183,7 +14216,7 @@
         <v>68</v>
       </c>
       <c t="s" r="H369" s="8">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c t="s" r="I369" s="7">
         <v>261</v>
@@ -14192,7 +14225,7 @@
         <v>217</v>
       </c>
       <c t="s" r="K369" s="7">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="L369" s="7"/>
       <c t="s" r="M369" s="7">
@@ -14211,13 +14244,13 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="F370" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G370" s="8">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c t="s" r="H370" s="8">
         <v>68</v>
@@ -14226,14 +14259,14 @@
         <v>219</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c t="s" r="K370" s="7">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="L370" s="7"/>
       <c t="s" r="M370" s="7">
-        <v>520</v>
+        <v>527</v>
       </c>
     </row>
     <row r="371" ht="14.25" customHeight="1">
@@ -14248,7 +14281,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="F371" s="7">
         <v>320</v>
@@ -14257,7 +14290,7 @@
         <v>68</v>
       </c>
       <c t="s" r="H371" s="8">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c t="s" r="I371" s="7">
         <v>263</v>
@@ -14270,7 +14303,7 @@
       </c>
       <c r="L371" s="7"/>
       <c t="s" r="M371" s="7">
-        <v>521</v>
+        <v>528</v>
       </c>
     </row>
     <row r="372" ht="14.25" customHeight="1">
@@ -14285,13 +14318,13 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="F372" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G372" s="8">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c t="s" r="H372" s="8">
         <v>68</v>
@@ -14300,14 +14333,14 @@
         <v>265</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c t="s" r="K372" s="7">
         <v>224</v>
       </c>
       <c r="L372" s="7"/>
       <c t="s" r="M372" s="7">
-        <v>522</v>
+        <v>529</v>
       </c>
     </row>
     <row r="373" ht="14.25" customHeight="1">
@@ -14337,7 +14370,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="F374" s="7">
         <v>321</v>
@@ -14346,7 +14379,7 @@
         <v>56</v>
       </c>
       <c t="s" r="H374" s="8">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c t="s" r="I374" s="7">
         <v>217</v>
@@ -14357,7 +14390,7 @@
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
       <c t="s" r="M374" s="7">
-        <v>524</v>
+        <v>531</v>
       </c>
     </row>
     <row r="375" ht="15" customHeight="1">
@@ -14372,13 +14405,13 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="F375" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G375" s="8">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c t="s" r="H375" s="8">
         <v>56</v>
@@ -14387,12 +14420,12 @@
         <v>28</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
       <c t="s" r="M375" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="376" ht="14.25" customHeight="1">
@@ -14407,7 +14440,7 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="F376" s="7">
         <v>321</v>
@@ -14416,13 +14449,13 @@
         <v>56</v>
       </c>
       <c t="s" r="H376" s="8">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c t="s" r="I376" s="7">
         <v>201</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>525</v>
+        <v>532</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
@@ -14442,22 +14475,22 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="F377" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G377" s="8">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c t="s" r="H377" s="8">
         <v>56</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
@@ -14492,7 +14525,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>526</v>
+        <v>533</v>
       </c>
       <c r="F379" s="7">
         <v>320</v>
@@ -14507,12 +14540,12 @@
         <v>57</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
       <c t="s" r="M379" s="7">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="380" ht="15" customHeight="1">
@@ -14527,7 +14560,7 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>526</v>
+        <v>533</v>
       </c>
       <c r="F380" s="7">
         <v>320</v>
@@ -14562,7 +14595,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>526</v>
+        <v>533</v>
       </c>
       <c r="F381" s="7">
         <v>320</v>
@@ -14580,11 +14613,11 @@
         <v>71</v>
       </c>
       <c t="s" r="K381" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L381" s="7"/>
       <c t="s" r="M381" s="7">
-        <v>527</v>
+        <v>534</v>
       </c>
     </row>
     <row r="382" ht="14.25" customHeight="1">
@@ -14599,7 +14632,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>526</v>
+        <v>533</v>
       </c>
       <c r="F382" s="7">
         <v>320</v>
@@ -14608,20 +14641,20 @@
         <v>16</v>
       </c>
       <c t="s" r="H382" s="8">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c t="s" r="I382" s="7">
         <v>49</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c t="s" r="K382" s="7">
         <v>199</v>
       </c>
       <c r="L382" s="7"/>
       <c t="s" r="M382" s="7">
-        <v>529</v>
+        <v>536</v>
       </c>
     </row>
     <row r="383" ht="14.25" customHeight="1">
@@ -14636,13 +14669,13 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>526</v>
+        <v>533</v>
       </c>
       <c r="F383" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G383" s="8">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c t="s" r="H383" s="8">
         <v>16</v>
@@ -14654,11 +14687,11 @@
         <v>234</v>
       </c>
       <c t="s" r="K383" s="7">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="L383" s="7"/>
       <c t="s" r="M383" s="7">
-        <v>530</v>
+        <v>537</v>
       </c>
     </row>
     <row r="384" ht="14.25" customHeight="1">
@@ -14673,7 +14706,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>526</v>
+        <v>533</v>
       </c>
       <c r="F384" s="7">
         <v>320</v>
@@ -14693,7 +14726,7 @@
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
       <c t="s" r="M384" s="7">
-        <v>531</v>
+        <v>538</v>
       </c>
     </row>
     <row r="385" ht="15" customHeight="1">
@@ -14723,13 +14756,13 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="F386" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G386" s="8">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c t="s" r="H386" s="8">
         <v>68</v>
@@ -14743,7 +14776,7 @@
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
       <c t="s" r="M386" s="7">
-        <v>534</v>
+        <v>541</v>
       </c>
     </row>
     <row r="387" ht="14.25" customHeight="1">
@@ -14758,7 +14791,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="F387" s="7">
         <v>320</v>
@@ -14767,7 +14800,7 @@
         <v>68</v>
       </c>
       <c t="s" r="H387" s="8">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c t="s" r="I387" s="7">
         <v>46</v>
@@ -14793,13 +14826,13 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="F388" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G388" s="8">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c t="s" r="H388" s="8">
         <v>68</v>
@@ -14828,7 +14861,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="F389" s="7">
         <v>320</v>
@@ -14843,12 +14876,12 @@
         <v>224</v>
       </c>
       <c t="s" r="J389" s="7">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
       <c t="s" r="M389" s="7">
-        <v>535</v>
+        <v>542</v>
       </c>
     </row>
     <row r="390" ht="15" customHeight="1">
@@ -14863,7 +14896,7 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="F390" s="7">
         <v>320</v>
@@ -14875,7 +14908,7 @@
         <v>68</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c t="s" r="J390" s="7">
         <v>155</v>
@@ -14883,7 +14916,7 @@
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
       <c t="s" r="M390" s="7">
-        <v>275</v>
+        <v>208</v>
       </c>
     </row>
     <row r="391" ht="14.25" customHeight="1">
@@ -14913,7 +14946,7 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="F392" s="7">
         <v>320</v>
@@ -14948,7 +14981,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="F393" s="7">
         <v>320</v>
@@ -14963,12 +14996,12 @@
         <v>278</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
       <c t="s" r="M393" s="7">
-        <v>537</v>
+        <v>544</v>
       </c>
     </row>
     <row r="394" ht="14.25" customHeight="1">
@@ -14983,7 +15016,7 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="F394" s="7">
         <v>320</v>
@@ -14992,10 +15025,10 @@
         <v>68</v>
       </c>
       <c t="s" r="H394" s="8">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c t="s" r="J394" s="7">
         <v>145</v>
@@ -15003,7 +15036,7 @@
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
       <c t="s" r="M394" s="7">
-        <v>539</v>
+        <v>546</v>
       </c>
     </row>
     <row r="395" ht="15" customHeight="1">
@@ -15018,19 +15051,19 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="F395" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G395" s="8">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c t="s" r="H395" s="8">
         <v>68</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c t="s" r="J395" s="7">
         <v>256</v>
@@ -15038,7 +15071,7 @@
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
       <c t="s" r="M395" s="7">
-        <v>540</v>
+        <v>547</v>
       </c>
     </row>
     <row r="396" ht="14.25" customHeight="1">
@@ -15053,7 +15086,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="F396" s="7">
         <v>320</v>
@@ -15062,7 +15095,7 @@
         <v>68</v>
       </c>
       <c t="s" r="H396" s="8">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c t="s" r="I396" s="7">
         <v>171</v>
@@ -15073,7 +15106,7 @@
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
       <c t="s" r="M396" s="7">
-        <v>541</v>
+        <v>548</v>
       </c>
     </row>
     <row r="397" ht="14.25" customHeight="1">
@@ -15088,13 +15121,13 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="F397" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G397" s="8">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c t="s" r="H397" s="8">
         <v>68</v>
@@ -15103,7 +15136,7 @@
         <v>129</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>542</v>
+        <v>549</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
@@ -15136,7 +15169,7 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="F399" s="7">
         <v>321</v>
@@ -15156,7 +15189,7 @@
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
       <c t="s" r="M399" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="400" ht="15" customHeight="1">
@@ -15171,7 +15204,7 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="F400" s="7">
         <v>321</v>
@@ -15191,7 +15224,7 @@
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
       <c t="s" r="M400" s="7">
-        <v>544</v>
+        <v>551</v>
       </c>
     </row>
     <row r="401" ht="14.25" customHeight="1">
@@ -15206,7 +15239,7 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="F401" s="7">
         <v>321</v>
@@ -15221,12 +15254,12 @@
         <v>60</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
       <c t="s" r="M401" s="7">
-        <v>545</v>
+        <v>552</v>
       </c>
     </row>
     <row r="402" ht="14.25" customHeight="1">
@@ -15241,7 +15274,7 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="F402" s="7">
         <v>321</v>
@@ -15276,7 +15309,7 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="F403" s="7">
         <v>321</v>
@@ -15296,7 +15329,7 @@
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
       <c t="s" r="M403" s="7">
-        <v>546</v>
+        <v>553</v>
       </c>
     </row>
     <row r="404" ht="14.25" customHeight="1">
@@ -15311,7 +15344,7 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="F404" s="7">
         <v>321</v>
@@ -15348,7 +15381,7 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="F405" s="7">
         <v>321</v>
@@ -15370,7 +15403,7 @@
       </c>
       <c r="L405" s="7"/>
       <c t="s" r="M405" s="7">
-        <v>547</v>
+        <v>554</v>
       </c>
     </row>
     <row r="406" ht="14.25" customHeight="1">
@@ -15385,7 +15418,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="F406" s="7">
         <v>321</v>
@@ -15407,7 +15440,7 @@
       </c>
       <c r="L406" s="7"/>
       <c t="s" r="M406" s="7">
-        <v>548</v>
+        <v>555</v>
       </c>
     </row>
     <row r="407" ht="14.25" customHeight="1">
@@ -15437,7 +15470,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>549</v>
+        <v>556</v>
       </c>
       <c r="F408" s="7">
         <v>320</v>
@@ -15446,10 +15479,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H408" s="8">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c t="s" r="J408" s="7">
         <v>250</v>
@@ -15457,7 +15490,7 @@
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
       <c t="s" r="M408" s="7">
-        <v>551</v>
+        <v>558</v>
       </c>
     </row>
     <row r="409" ht="14.25" customHeight="1">
@@ -15472,19 +15505,19 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>549</v>
+        <v>556</v>
       </c>
       <c r="F409" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G409" s="8">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c t="s" r="H409" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I409" s="7">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c t="s" r="J409" s="7">
         <v>45</v>
@@ -15492,7 +15525,7 @@
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
       <c t="s" r="M409" s="7">
-        <v>552</v>
+        <v>559</v>
       </c>
     </row>
     <row r="410" ht="15" customHeight="1">
@@ -15507,7 +15540,7 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>549</v>
+        <v>556</v>
       </c>
       <c r="F410" s="7">
         <v>320</v>
@@ -15522,12 +15555,12 @@
         <v>197</v>
       </c>
       <c t="s" r="J410" s="7">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
       <c t="s" r="M410" s="7">
-        <v>553</v>
+        <v>560</v>
       </c>
     </row>
     <row r="411" ht="14.25" customHeight="1">
@@ -15542,7 +15575,7 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>549</v>
+        <v>556</v>
       </c>
       <c r="F411" s="7">
         <v>320</v>
@@ -15562,7 +15595,7 @@
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
       <c t="s" r="M411" s="7">
-        <v>554</v>
+        <v>561</v>
       </c>
     </row>
     <row r="412" ht="14.25" customHeight="1">
@@ -15577,7 +15610,7 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>549</v>
+        <v>556</v>
       </c>
       <c r="F412" s="7">
         <v>320</v>
@@ -15589,7 +15622,7 @@
         <v>215</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c t="s" r="J412" s="7">
         <v>256</v>
@@ -15597,7 +15630,7 @@
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
       <c t="s" r="M412" s="7">
-        <v>555</v>
+        <v>562</v>
       </c>
     </row>
     <row r="413" ht="14.25" customHeight="1">
@@ -15612,7 +15645,7 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>549</v>
+        <v>556</v>
       </c>
       <c r="F413" s="7">
         <v>320</v>
@@ -15627,14 +15660,14 @@
         <v>115</v>
       </c>
       <c t="s" r="J413" s="7">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c t="s" r="K413" s="7">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="L413" s="7"/>
       <c t="s" r="M413" s="7">
-        <v>556</v>
+        <v>563</v>
       </c>
     </row>
     <row r="414" ht="14.25" customHeight="1">
@@ -15649,7 +15682,7 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>549</v>
+        <v>556</v>
       </c>
       <c r="F414" s="7">
         <v>320</v>
@@ -15664,14 +15697,14 @@
         <v>315</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c t="s" r="K414" s="7">
         <v>90</v>
       </c>
       <c r="L414" s="7"/>
       <c t="s" r="M414" s="7">
-        <v>80</v>
+        <v>492</v>
       </c>
     </row>
     <row r="415" ht="15" customHeight="1">
@@ -15686,7 +15719,7 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>549</v>
+        <v>556</v>
       </c>
       <c r="F415" s="7">
         <v>320</v>
@@ -15698,17 +15731,17 @@
         <v>16</v>
       </c>
       <c t="s" r="I415" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c t="s" r="J415" s="7">
-        <v>558</v>
+        <v>565</v>
       </c>
       <c t="s" r="K415" s="7">
         <v>158</v>
       </c>
       <c r="L415" s="7"/>
       <c t="s" r="M415" s="7">
-        <v>559</v>
+        <v>566</v>
       </c>
     </row>
     <row r="416" ht="14.25" customHeight="1">
@@ -15738,7 +15771,7 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="F417" s="7">
         <v>320</v>
@@ -15750,7 +15783,7 @@
         <v>56</v>
       </c>
       <c t="s" r="I417" s="7">
-        <v>561</v>
+        <v>568</v>
       </c>
       <c t="s" r="J417" s="7">
         <v>59</v>
@@ -15773,7 +15806,7 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="F418" s="7">
         <v>320</v>
@@ -15788,12 +15821,12 @@
         <v>306</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>562</v>
+        <v>569</v>
       </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
       <c t="s" r="M418" s="7">
-        <v>563</v>
+        <v>570</v>
       </c>
     </row>
     <row r="419" ht="14.25" customHeight="1">
@@ -15808,7 +15841,7 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="F419" s="7">
         <v>320</v>
@@ -15820,7 +15853,7 @@
         <v>164</v>
       </c>
       <c t="s" r="I419" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c t="s" r="J419" s="7">
         <v>83</v>
@@ -15843,7 +15876,7 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="F420" s="7">
         <v>320</v>
@@ -15865,7 +15898,7 @@
       </c>
       <c r="L420" s="7"/>
       <c t="s" r="M420" s="7">
-        <v>564</v>
+        <v>571</v>
       </c>
     </row>
     <row r="421" ht="14.25" customHeight="1">
@@ -15880,7 +15913,7 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="F421" s="7">
         <v>320</v>
@@ -15900,7 +15933,7 @@
       <c r="K421" s="7"/>
       <c r="L421" s="7"/>
       <c t="s" r="M421" s="7">
-        <v>565</v>
+        <v>572</v>
       </c>
     </row>
     <row r="422" ht="14.25" customHeight="1">
@@ -15915,7 +15948,7 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="F422" s="7">
         <v>320</v>
@@ -15930,12 +15963,12 @@
         <v>76</v>
       </c>
       <c t="s" r="J422" s="7">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="K422" s="7"/>
       <c r="L422" s="7"/>
       <c t="s" r="M422" s="7">
-        <v>566</v>
+        <v>573</v>
       </c>
     </row>
     <row r="423" ht="14.25" customHeight="1">
@@ -15965,7 +15998,7 @@
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>567</v>
+        <v>574</v>
       </c>
       <c r="F424" s="7">
         <v>320</v>
@@ -15980,12 +16013,12 @@
         <v>306</v>
       </c>
       <c t="s" r="J424" s="7">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="K424" s="7"/>
       <c r="L424" s="7"/>
       <c t="s" r="M424" s="7">
-        <v>568</v>
+        <v>575</v>
       </c>
     </row>
     <row r="425" ht="15" customHeight="1">
@@ -16000,7 +16033,7 @@
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>567</v>
+        <v>574</v>
       </c>
       <c r="F425" s="7">
         <v>320</v>
@@ -16037,7 +16070,7 @@
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>567</v>
+        <v>574</v>
       </c>
       <c r="F426" s="7">
         <v>320</v>
@@ -16052,10 +16085,10 @@
         <v>251</v>
       </c>
       <c t="s" r="J426" s="7">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c t="s" r="K426" s="7">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="L426" s="7"/>
       <c t="s" r="M426" s="7">
@@ -16074,7 +16107,7 @@
       </c>
       <c r="D427" s="7"/>
       <c t="s" r="E427" s="7">
-        <v>567</v>
+        <v>574</v>
       </c>
       <c r="F427" s="7">
         <v>320</v>
@@ -16086,17 +16119,17 @@
         <v>16</v>
       </c>
       <c t="s" r="I427" s="7">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c t="s" r="J427" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c t="s" r="K427" s="7">
         <v>190</v>
       </c>
       <c r="L427" s="7"/>
       <c t="s" r="M427" s="7">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="428" ht="14.25" customHeight="1">
@@ -16111,7 +16144,7 @@
       </c>
       <c r="D428" s="7"/>
       <c t="s" r="E428" s="7">
-        <v>567</v>
+        <v>574</v>
       </c>
       <c r="F428" s="7">
         <v>320</v>
@@ -16120,7 +16153,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H428" s="8">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c t="s" r="I428" s="7">
         <v>113</v>
@@ -16133,7 +16166,7 @@
       </c>
       <c r="L428" s="7"/>
       <c t="s" r="M428" s="7">
-        <v>569</v>
+        <v>576</v>
       </c>
     </row>
     <row r="429" ht="14.25" customHeight="1">
@@ -16148,13 +16181,13 @@
       </c>
       <c r="D429" s="7"/>
       <c t="s" r="E429" s="7">
-        <v>567</v>
+        <v>574</v>
       </c>
       <c r="F429" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G429" s="8">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c t="s" r="H429" s="8">
         <v>16</v>
@@ -16163,14 +16196,14 @@
         <v>243</v>
       </c>
       <c t="s" r="J429" s="7">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c t="s" r="K429" s="7">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L429" s="7"/>
       <c t="s" r="M429" s="7">
-        <v>570</v>
+        <v>577</v>
       </c>
     </row>
     <row r="430" ht="15" customHeight="1">
@@ -16200,7 +16233,7 @@
       </c>
       <c r="D431" s="7"/>
       <c t="s" r="E431" s="7">
-        <v>571</v>
+        <v>578</v>
       </c>
       <c r="F431" s="7">
         <v>320</v>
@@ -16209,10 +16242,10 @@
         <v>68</v>
       </c>
       <c t="s" r="H431" s="8">
-        <v>572</v>
+        <v>579</v>
       </c>
       <c t="s" r="I431" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c t="s" r="J431" s="7">
         <v>83</v>
@@ -16220,7 +16253,7 @@
       <c r="K431" s="7"/>
       <c r="L431" s="7"/>
       <c t="s" r="M431" s="7">
-        <v>573</v>
+        <v>580</v>
       </c>
     </row>
     <row r="432" ht="14.25" customHeight="1">
@@ -16235,13 +16268,13 @@
       </c>
       <c r="D432" s="7"/>
       <c t="s" r="E432" s="7">
-        <v>571</v>
+        <v>578</v>
       </c>
       <c r="F432" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G432" s="8">
-        <v>572</v>
+        <v>579</v>
       </c>
       <c t="s" r="H432" s="8">
         <v>68</v>
@@ -16255,7 +16288,7 @@
       <c r="K432" s="7"/>
       <c r="L432" s="7"/>
       <c t="s" r="M432" s="7">
-        <v>574</v>
+        <v>581</v>
       </c>
     </row>
     <row r="433" ht="14.25" customHeight="1">
@@ -16270,7 +16303,7 @@
       </c>
       <c r="D433" s="7"/>
       <c t="s" r="E433" s="7">
-        <v>571</v>
+        <v>578</v>
       </c>
       <c r="F433" s="7">
         <v>320</v>
@@ -16279,7 +16312,7 @@
         <v>68</v>
       </c>
       <c t="s" r="H433" s="8">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c t="s" r="I433" s="7">
         <v>146</v>
@@ -16290,7 +16323,7 @@
       <c r="K433" s="7"/>
       <c r="L433" s="7"/>
       <c t="s" r="M433" s="7">
-        <v>576</v>
+        <v>583</v>
       </c>
     </row>
     <row r="434" ht="14.25" customHeight="1">
@@ -16305,13 +16338,13 @@
       </c>
       <c r="D434" s="7"/>
       <c t="s" r="E434" s="7">
-        <v>571</v>
+        <v>578</v>
       </c>
       <c r="F434" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G434" s="8">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c t="s" r="H434" s="8">
         <v>68</v>
@@ -16325,7 +16358,7 @@
       <c r="K434" s="7"/>
       <c r="L434" s="7"/>
       <c t="s" r="M434" s="7">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="435" ht="15" customHeight="1">
@@ -16355,7 +16388,7 @@
       </c>
       <c r="D436" s="7"/>
       <c t="s" r="E436" s="7">
-        <v>577</v>
+        <v>584</v>
       </c>
       <c r="F436" s="7">
         <v>321</v>
@@ -16367,7 +16400,7 @@
         <v>56</v>
       </c>
       <c t="s" r="I436" s="7">
-        <v>578</v>
+        <v>585</v>
       </c>
       <c t="s" r="J436" s="7">
         <v>93</v>
@@ -16375,7 +16408,7 @@
       <c r="K436" s="7"/>
       <c r="L436" s="7"/>
       <c t="s" r="M436" s="7">
-        <v>579</v>
+        <v>586</v>
       </c>
     </row>
     <row r="437" ht="14.25" customHeight="1">
@@ -16390,7 +16423,7 @@
       </c>
       <c r="D437" s="7"/>
       <c t="s" r="E437" s="7">
-        <v>577</v>
+        <v>584</v>
       </c>
       <c r="F437" s="7">
         <v>321</v>
@@ -16402,7 +16435,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I437" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c t="s" r="J437" s="7">
         <v>174</v>
@@ -16410,7 +16443,7 @@
       <c r="K437" s="7"/>
       <c r="L437" s="7"/>
       <c t="s" r="M437" s="7">
-        <v>580</v>
+        <v>587</v>
       </c>
     </row>
     <row r="438" ht="14.25" customHeight="1">
@@ -16425,7 +16458,7 @@
       </c>
       <c r="D438" s="7"/>
       <c t="s" r="E438" s="7">
-        <v>577</v>
+        <v>584</v>
       </c>
       <c r="F438" s="7">
         <v>321</v>
@@ -16440,14 +16473,14 @@
         <v>240</v>
       </c>
       <c t="s" r="J438" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c t="s" r="K438" s="7">
         <v>20</v>
       </c>
       <c r="L438" s="7"/>
       <c t="s" r="M438" s="7">
-        <v>581</v>
+        <v>588</v>
       </c>
     </row>
     <row r="439" ht="14.25" customHeight="1">
@@ -16462,7 +16495,7 @@
       </c>
       <c r="D439" s="7"/>
       <c t="s" r="E439" s="7">
-        <v>577</v>
+        <v>584</v>
       </c>
       <c r="F439" s="7">
         <v>321</v>
@@ -16484,7 +16517,7 @@
       </c>
       <c r="L439" s="7"/>
       <c t="s" r="M439" s="7">
-        <v>498</v>
+        <v>505</v>
       </c>
     </row>
     <row r="440" ht="15" customHeight="1">
@@ -16499,7 +16532,7 @@
       </c>
       <c r="D440" s="7"/>
       <c t="s" r="E440" s="7">
-        <v>577</v>
+        <v>584</v>
       </c>
       <c r="F440" s="7">
         <v>321</v>
@@ -16517,11 +16550,11 @@
         <v>272</v>
       </c>
       <c t="s" r="K440" s="7">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="L440" s="7"/>
       <c t="s" r="M440" s="7">
-        <v>511</v>
+        <v>518</v>
       </c>
     </row>
     <row r="441" ht="14.25" customHeight="1">
@@ -16536,7 +16569,7 @@
       </c>
       <c r="D441" s="7"/>
       <c t="s" r="E441" s="7">
-        <v>577</v>
+        <v>584</v>
       </c>
       <c r="F441" s="7">
         <v>321</v>
@@ -16551,7 +16584,7 @@
         <v>225</v>
       </c>
       <c t="s" r="J441" s="7">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c t="s" r="K441" s="7">
         <v>266</v>
@@ -16573,7 +16606,7 @@
       </c>
       <c r="D442" s="7"/>
       <c t="s" r="E442" s="7">
-        <v>577</v>
+        <v>584</v>
       </c>
       <c r="F442" s="7">
         <v>321</v>
@@ -16595,7 +16628,7 @@
       </c>
       <c r="L442" s="7"/>
       <c t="s" r="M442" s="7">
-        <v>558</v>
+        <v>565</v>
       </c>
     </row>
     <row r="443" ht="14.25" customHeight="1">
@@ -16610,7 +16643,7 @@
       </c>
       <c r="D443" s="7"/>
       <c t="s" r="E443" s="7">
-        <v>577</v>
+        <v>584</v>
       </c>
       <c r="F443" s="7">
         <v>321</v>
@@ -16628,7 +16661,7 @@
         <v>33</v>
       </c>
       <c t="s" r="K443" s="7">
-        <v>582</v>
+        <v>589</v>
       </c>
       <c r="L443" s="7"/>
       <c t="s" r="M443" s="7">
@@ -16662,7 +16695,7 @@
       </c>
       <c r="D445" s="7"/>
       <c t="s" r="E445" s="7">
-        <v>583</v>
+        <v>590</v>
       </c>
       <c r="F445" s="7">
         <v>321</v>
@@ -16674,15 +16707,15 @@
         <v>104</v>
       </c>
       <c t="s" r="I445" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c t="s" r="J445" s="7">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="K445" s="7"/>
       <c r="L445" s="7"/>
       <c t="s" r="M445" s="7">
-        <v>584</v>
+        <v>591</v>
       </c>
     </row>
     <row r="446" ht="14.25" customHeight="1">
@@ -16697,7 +16730,7 @@
       </c>
       <c r="D446" s="7"/>
       <c t="s" r="E446" s="7">
-        <v>583</v>
+        <v>590</v>
       </c>
       <c r="F446" s="7">
         <v>321</v>
@@ -16712,12 +16745,12 @@
         <v>108</v>
       </c>
       <c t="s" r="J446" s="7">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="K446" s="7"/>
       <c r="L446" s="7"/>
       <c t="s" r="M446" s="7">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="447" ht="14.25" customHeight="1">
@@ -16732,7 +16765,7 @@
       </c>
       <c r="D447" s="7"/>
       <c t="s" r="E447" s="7">
-        <v>583</v>
+        <v>590</v>
       </c>
       <c r="F447" s="7">
         <v>321</v>
@@ -16752,7 +16785,7 @@
       <c r="K447" s="7"/>
       <c r="L447" s="7"/>
       <c t="s" r="M447" s="7">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="448" ht="14.25" customHeight="1">
@@ -16767,7 +16800,7 @@
       </c>
       <c r="D448" s="7"/>
       <c t="s" r="E448" s="7">
-        <v>583</v>
+        <v>590</v>
       </c>
       <c r="F448" s="7">
         <v>321</v>
@@ -16782,12 +16815,12 @@
         <v>128</v>
       </c>
       <c t="s" r="J448" s="7">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="K448" s="7"/>
       <c r="L448" s="7"/>
       <c t="s" r="M448" s="7">
-        <v>586</v>
+        <v>593</v>
       </c>
     </row>
     <row r="449" ht="14.25" customHeight="1">
@@ -16817,7 +16850,7 @@
       </c>
       <c r="D450" s="7"/>
       <c t="s" r="E450" s="7">
-        <v>587</v>
+        <v>594</v>
       </c>
       <c r="F450" s="7">
         <v>320</v>
@@ -16832,12 +16865,12 @@
         <v>296</v>
       </c>
       <c t="s" r="J450" s="7">
-        <v>588</v>
+        <v>595</v>
       </c>
       <c r="K450" s="7"/>
       <c r="L450" s="7"/>
       <c t="s" r="M450" s="7">
-        <v>589</v>
+        <v>596</v>
       </c>
     </row>
     <row r="451" ht="14.25" customHeight="1">
@@ -16852,7 +16885,7 @@
       </c>
       <c r="D451" s="7"/>
       <c t="s" r="E451" s="7">
-        <v>587</v>
+        <v>594</v>
       </c>
       <c r="F451" s="7">
         <v>320</v>
@@ -16872,7 +16905,7 @@
       <c r="K451" s="7"/>
       <c r="L451" s="7"/>
       <c t="s" r="M451" s="7">
-        <v>590</v>
+        <v>597</v>
       </c>
     </row>
     <row r="452" ht="14.25" customHeight="1">
@@ -16887,7 +16920,7 @@
       </c>
       <c r="D452" s="7"/>
       <c t="s" r="E452" s="7">
-        <v>587</v>
+        <v>594</v>
       </c>
       <c r="F452" s="7">
         <v>320</v>
@@ -16907,7 +16940,7 @@
       <c r="K452" s="7"/>
       <c r="L452" s="7"/>
       <c t="s" r="M452" s="7">
-        <v>591</v>
+        <v>598</v>
       </c>
     </row>
     <row r="453" ht="14.25" customHeight="1">
@@ -16922,7 +16955,7 @@
       </c>
       <c r="D453" s="7"/>
       <c t="s" r="E453" s="7">
-        <v>587</v>
+        <v>594</v>
       </c>
       <c r="F453" s="7">
         <v>320</v>
@@ -16942,7 +16975,7 @@
       <c r="K453" s="7"/>
       <c r="L453" s="7"/>
       <c t="s" r="M453" s="7">
-        <v>469</v>
+        <v>474</v>
       </c>
     </row>
     <row r="454" ht="14.25" customHeight="1">
@@ -16957,7 +16990,7 @@
       </c>
       <c r="D454" s="7"/>
       <c t="s" r="E454" s="7">
-        <v>587</v>
+        <v>594</v>
       </c>
       <c r="F454" s="7">
         <v>320</v>
@@ -16992,7 +17025,7 @@
       </c>
       <c r="D455" s="7"/>
       <c t="s" r="E455" s="7">
-        <v>587</v>
+        <v>594</v>
       </c>
       <c r="F455" s="7">
         <v>320</v>
@@ -17012,7 +17045,7 @@
       <c r="K455" s="7"/>
       <c r="L455" s="7"/>
       <c t="s" r="M455" s="7">
-        <v>547</v>
+        <v>554</v>
       </c>
     </row>
     <row r="456" ht="14.25" customHeight="1">
@@ -17042,7 +17075,7 @@
       </c>
       <c r="D457" s="7"/>
       <c t="s" r="E457" s="7">
-        <v>592</v>
+        <v>599</v>
       </c>
       <c r="F457" s="7">
         <v>320</v>
@@ -17051,7 +17084,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H457" s="8">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c t="s" r="I457" s="7">
         <v>37</v>
@@ -17062,7 +17095,7 @@
       <c r="K457" s="7"/>
       <c r="L457" s="7"/>
       <c t="s" r="M457" s="7">
-        <v>593</v>
+        <v>600</v>
       </c>
     </row>
     <row r="458" ht="14.25" customHeight="1">
@@ -17077,13 +17110,13 @@
       </c>
       <c r="D458" s="7"/>
       <c t="s" r="E458" s="7">
-        <v>592</v>
+        <v>599</v>
       </c>
       <c r="F458" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G458" s="8">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c t="s" r="H458" s="8">
         <v>16</v>
@@ -17097,7 +17130,7 @@
       <c r="K458" s="7"/>
       <c r="L458" s="7"/>
       <c t="s" r="M458" s="7">
-        <v>594</v>
+        <v>601</v>
       </c>
     </row>
     <row r="459" ht="14.25" customHeight="1">
@@ -17112,7 +17145,7 @@
       </c>
       <c r="D459" s="7"/>
       <c t="s" r="E459" s="7">
-        <v>592</v>
+        <v>599</v>
       </c>
       <c r="F459" s="7">
         <v>320</v>
@@ -17121,13 +17154,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H459" s="8">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c t="s" r="I459" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c t="s" r="J459" s="7">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="K459" s="7"/>
       <c r="L459" s="7"/>
@@ -17147,19 +17180,19 @@
       </c>
       <c r="D460" s="7"/>
       <c t="s" r="E460" s="7">
-        <v>592</v>
+        <v>599</v>
       </c>
       <c r="F460" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G460" s="8">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c t="s" r="H460" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I460" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c t="s" r="J460" s="7">
         <v>126</v>
@@ -17184,7 +17217,7 @@
       </c>
       <c r="D461" s="7"/>
       <c t="s" r="E461" s="7">
-        <v>592</v>
+        <v>599</v>
       </c>
       <c r="F461" s="7">
         <v>320</v>
@@ -17196,7 +17229,7 @@
         <v>112</v>
       </c>
       <c t="s" r="I461" s="7">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c t="s" r="J461" s="7">
         <v>32</v>
@@ -17221,7 +17254,7 @@
       </c>
       <c r="D462" s="7"/>
       <c t="s" r="E462" s="7">
-        <v>592</v>
+        <v>599</v>
       </c>
       <c r="F462" s="7">
         <v>320</v>
@@ -17258,7 +17291,7 @@
       </c>
       <c r="D463" s="7"/>
       <c t="s" r="E463" s="7">
-        <v>592</v>
+        <v>599</v>
       </c>
       <c r="F463" s="7">
         <v>320</v>
@@ -17273,14 +17306,14 @@
         <v>171</v>
       </c>
       <c t="s" r="J463" s="7">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c t="s" r="K463" s="7">
         <v>258</v>
       </c>
       <c r="L463" s="7"/>
       <c t="s" r="M463" s="7">
-        <v>275</v>
+        <v>332</v>
       </c>
     </row>
     <row r="464" ht="14.25" customHeight="1">
@@ -17295,7 +17328,7 @@
       </c>
       <c r="D464" s="7"/>
       <c t="s" r="E464" s="7">
-        <v>592</v>
+        <v>599</v>
       </c>
       <c r="F464" s="7">
         <v>320</v>
@@ -17307,10 +17340,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I464" s="7">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c t="s" r="J464" s="7">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c t="s" r="K464" s="7">
         <v>141</v>
@@ -17347,7 +17380,7 @@
       </c>
       <c r="D466" s="7"/>
       <c t="s" r="E466" s="7">
-        <v>595</v>
+        <v>602</v>
       </c>
       <c r="F466" s="7">
         <v>321</v>
@@ -17356,10 +17389,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H466" s="8">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c t="s" r="I466" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c t="s" r="J466" s="7">
         <v>102</v>
@@ -17382,27 +17415,27 @@
       </c>
       <c r="D467" s="7"/>
       <c t="s" r="E467" s="7">
-        <v>595</v>
+        <v>602</v>
       </c>
       <c r="F467" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G467" s="8">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c t="s" r="H467" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I467" s="7">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c t="s" r="J467" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="K467" s="7"/>
       <c r="L467" s="7"/>
       <c t="s" r="M467" s="7">
-        <v>596</v>
+        <v>603</v>
       </c>
     </row>
     <row r="468" ht="14.25" customHeight="1">
@@ -17417,7 +17450,7 @@
       </c>
       <c r="D468" s="7"/>
       <c t="s" r="E468" s="7">
-        <v>595</v>
+        <v>602</v>
       </c>
       <c r="F468" s="7">
         <v>321</v>
@@ -17432,7 +17465,7 @@
         <v>60</v>
       </c>
       <c t="s" r="J468" s="7">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="K468" s="7"/>
       <c r="L468" s="7"/>
@@ -17452,7 +17485,7 @@
       </c>
       <c r="D469" s="7"/>
       <c t="s" r="E469" s="7">
-        <v>595</v>
+        <v>602</v>
       </c>
       <c r="F469" s="7">
         <v>321</v>
@@ -17470,11 +17503,11 @@
         <v>197</v>
       </c>
       <c t="s" r="K469" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L469" s="7"/>
       <c t="s" r="M469" s="7">
-        <v>597</v>
+        <v>604</v>
       </c>
     </row>
     <row r="470" ht="15" customHeight="1">
@@ -17489,7 +17522,7 @@
       </c>
       <c r="D470" s="7"/>
       <c t="s" r="E470" s="7">
-        <v>595</v>
+        <v>602</v>
       </c>
       <c r="F470" s="7">
         <v>321</v>
@@ -17511,7 +17544,7 @@
       </c>
       <c r="L470" s="7"/>
       <c t="s" r="M470" s="7">
-        <v>598</v>
+        <v>605</v>
       </c>
     </row>
     <row r="471" ht="14.25" customHeight="1">
@@ -17526,7 +17559,7 @@
       </c>
       <c r="D471" s="7"/>
       <c t="s" r="E471" s="7">
-        <v>595</v>
+        <v>602</v>
       </c>
       <c r="F471" s="7">
         <v>321</v>
@@ -17574,7 +17607,7 @@
       </c>
       <c r="D473" s="7"/>
       <c t="s" r="E473" s="7">
-        <v>599</v>
+        <v>606</v>
       </c>
       <c r="F473" s="7">
         <v>321</v>
@@ -17583,18 +17616,18 @@
         <v>68</v>
       </c>
       <c t="s" r="H473" s="8">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c t="s" r="I473" s="7">
         <v>179</v>
       </c>
       <c t="s" r="J473" s="7">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="K473" s="7"/>
       <c r="L473" s="7"/>
       <c t="s" r="M473" s="7">
-        <v>490</v>
+        <v>497</v>
       </c>
     </row>
     <row r="474" ht="14.25" customHeight="1">
@@ -17609,13 +17642,13 @@
       </c>
       <c r="D474" s="7"/>
       <c t="s" r="E474" s="7">
-        <v>599</v>
+        <v>606</v>
       </c>
       <c r="F474" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G474" s="8">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c t="s" r="H474" s="8">
         <v>68</v>
@@ -17644,7 +17677,7 @@
       </c>
       <c r="D475" s="7"/>
       <c t="s" r="E475" s="7">
-        <v>599</v>
+        <v>606</v>
       </c>
       <c r="F475" s="7">
         <v>321</v>
@@ -17653,7 +17686,7 @@
         <v>68</v>
       </c>
       <c t="s" r="H475" s="8">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c t="s" r="I475" s="7">
         <v>311</v>
@@ -17666,7 +17699,7 @@
       </c>
       <c r="L475" s="7"/>
       <c t="s" r="M475" s="7">
-        <v>600</v>
+        <v>607</v>
       </c>
     </row>
     <row r="476" ht="14.25" customHeight="1">
@@ -17681,13 +17714,13 @@
       </c>
       <c r="D476" s="7"/>
       <c t="s" r="E476" s="7">
-        <v>599</v>
+        <v>606</v>
       </c>
       <c r="F476" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G476" s="8">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c t="s" r="H476" s="8">
         <v>68</v>
@@ -17733,7 +17766,7 @@
       </c>
       <c r="D478" s="7"/>
       <c t="s" r="E478" s="7">
-        <v>601</v>
+        <v>608</v>
       </c>
       <c r="F478" s="7">
         <v>321</v>
@@ -17748,12 +17781,12 @@
         <v>177</v>
       </c>
       <c t="s" r="J478" s="7">
-        <v>588</v>
+        <v>595</v>
       </c>
       <c r="K478" s="7"/>
       <c r="L478" s="7"/>
       <c t="s" r="M478" s="7">
-        <v>602</v>
+        <v>609</v>
       </c>
     </row>
     <row r="479" ht="14.25" customHeight="1">
@@ -17768,7 +17801,7 @@
       </c>
       <c r="D479" s="7"/>
       <c t="s" r="E479" s="7">
-        <v>601</v>
+        <v>608</v>
       </c>
       <c r="F479" s="7">
         <v>321</v>
@@ -17780,7 +17813,7 @@
         <v>68</v>
       </c>
       <c t="s" r="I479" s="7">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c t="s" r="J479" s="7">
         <v>39</v>
@@ -17788,7 +17821,7 @@
       <c r="K479" s="7"/>
       <c r="L479" s="7"/>
       <c t="s" r="M479" s="7">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="480" ht="15" customHeight="1">
@@ -17803,7 +17836,7 @@
       </c>
       <c r="D480" s="7"/>
       <c t="s" r="E480" s="7">
-        <v>601</v>
+        <v>608</v>
       </c>
       <c r="F480" s="7">
         <v>321</v>
@@ -17823,7 +17856,7 @@
       <c r="K480" s="7"/>
       <c r="L480" s="7"/>
       <c t="s" r="M480" s="7">
-        <v>459</v>
+        <v>464</v>
       </c>
     </row>
     <row r="481" ht="14.25" customHeight="1">
@@ -17838,7 +17871,7 @@
       </c>
       <c r="D481" s="7"/>
       <c t="s" r="E481" s="7">
-        <v>601</v>
+        <v>608</v>
       </c>
       <c r="F481" s="7">
         <v>321</v>
@@ -17850,7 +17883,7 @@
         <v>68</v>
       </c>
       <c t="s" r="I481" s="7">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c t="s" r="J481" s="7">
         <v>97</v>
@@ -17858,7 +17891,7 @@
       <c r="K481" s="7"/>
       <c r="L481" s="7"/>
       <c t="s" r="M481" s="7">
-        <v>603</v>
+        <v>610</v>
       </c>
     </row>
     <row r="482" ht="14.25" customHeight="1">
@@ -17873,7 +17906,7 @@
       </c>
       <c r="D482" s="7"/>
       <c t="s" r="E482" s="7">
-        <v>601</v>
+        <v>608</v>
       </c>
       <c r="F482" s="7">
         <v>321</v>
@@ -17885,7 +17918,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I482" s="7">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c t="s" r="J482" s="7">
         <v>283</v>
@@ -17893,7 +17926,7 @@
       <c r="K482" s="7"/>
       <c r="L482" s="7"/>
       <c t="s" r="M482" s="7">
-        <v>604</v>
+        <v>611</v>
       </c>
     </row>
     <row r="483" ht="14.25" customHeight="1">
@@ -17908,7 +17941,7 @@
       </c>
       <c r="D483" s="7"/>
       <c t="s" r="E483" s="7">
-        <v>601</v>
+        <v>608</v>
       </c>
       <c r="F483" s="7">
         <v>321</v>
@@ -17917,17 +17950,19 @@
         <v>16</v>
       </c>
       <c t="s" r="H483" s="8">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c t="s" r="I483" s="7">
         <v>62</v>
       </c>
       <c t="s" r="J483" s="7">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="K483" s="7"/>
       <c r="L483" s="7"/>
-      <c r="M483" s="7"/>
+      <c t="s" r="M483" s="7">
+        <v>565</v>
+      </c>
     </row>
     <row r="484" ht="14.25" customHeight="1">
       <c t="s" r="A484" s="6">
@@ -17941,22 +17976,22 @@
       </c>
       <c r="D484" s="7"/>
       <c t="s" r="E484" s="7">
-        <v>601</v>
+        <v>608</v>
       </c>
       <c r="F484" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G484" s="8">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c t="s" r="H484" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I484" s="7">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c t="s" r="J484" s="7">
-        <v>605</v>
+        <v>612</v>
       </c>
       <c r="K484" s="7"/>
       <c r="L484" s="7"/>
@@ -17989,7 +18024,7 @@
       </c>
       <c r="D486" s="7"/>
       <c t="s" r="E486" s="7">
-        <v>606</v>
+        <v>613</v>
       </c>
       <c r="F486" s="7">
         <v>321</v>
@@ -18001,7 +18036,7 @@
         <v>215</v>
       </c>
       <c t="s" r="I486" s="7">
-        <v>561</v>
+        <v>568</v>
       </c>
       <c t="s" r="J486" s="7">
         <v>297</v>
@@ -18009,7 +18044,7 @@
       <c r="K486" s="7"/>
       <c r="L486" s="7"/>
       <c t="s" r="M486" s="7">
-        <v>607</v>
+        <v>614</v>
       </c>
     </row>
     <row r="487" ht="14.25" customHeight="1">
@@ -18024,7 +18059,7 @@
       </c>
       <c r="D487" s="7"/>
       <c t="s" r="E487" s="7">
-        <v>606</v>
+        <v>613</v>
       </c>
       <c r="F487" s="7">
         <v>321</v>
@@ -18044,7 +18079,7 @@
       <c r="K487" s="7"/>
       <c r="L487" s="7"/>
       <c t="s" r="M487" s="7">
-        <v>608</v>
+        <v>615</v>
       </c>
     </row>
     <row r="488" ht="14.25" customHeight="1">
@@ -18059,7 +18094,7 @@
       </c>
       <c r="D488" s="7"/>
       <c t="s" r="E488" s="7">
-        <v>606</v>
+        <v>613</v>
       </c>
       <c r="F488" s="7">
         <v>321</v>
@@ -18079,7 +18114,7 @@
       <c r="K488" s="7"/>
       <c r="L488" s="7"/>
       <c t="s" r="M488" s="7">
-        <v>609</v>
+        <v>616</v>
       </c>
     </row>
     <row r="489" ht="14.25" customHeight="1">
@@ -18094,7 +18129,7 @@
       </c>
       <c r="D489" s="7"/>
       <c t="s" r="E489" s="7">
-        <v>606</v>
+        <v>613</v>
       </c>
       <c r="F489" s="7">
         <v>321</v>
@@ -18109,12 +18144,12 @@
         <v>106</v>
       </c>
       <c t="s" r="J489" s="7">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="K489" s="7"/>
       <c r="L489" s="7"/>
       <c t="s" r="M489" s="7">
-        <v>453</v>
+        <v>458</v>
       </c>
     </row>
     <row r="490" ht="15" customHeight="1">
@@ -18129,7 +18164,7 @@
       </c>
       <c r="D490" s="7"/>
       <c t="s" r="E490" s="7">
-        <v>606</v>
+        <v>613</v>
       </c>
       <c r="F490" s="7">
         <v>321</v>
@@ -18138,13 +18173,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H490" s="8">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c t="s" r="I490" s="7">
         <v>230</v>
       </c>
       <c t="s" r="J490" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K490" s="7"/>
       <c r="L490" s="7"/>
@@ -18164,13 +18199,13 @@
       </c>
       <c r="D491" s="7"/>
       <c t="s" r="E491" s="7">
-        <v>606</v>
+        <v>613</v>
       </c>
       <c r="F491" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G491" s="8">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c t="s" r="H491" s="8">
         <v>16</v>
@@ -18184,7 +18219,7 @@
       <c r="K491" s="7"/>
       <c r="L491" s="7"/>
       <c t="s" r="M491" s="7">
-        <v>610</v>
+        <v>617</v>
       </c>
     </row>
     <row r="492" ht="14.25" customHeight="1">
@@ -18199,7 +18234,7 @@
       </c>
       <c r="D492" s="7"/>
       <c t="s" r="E492" s="7">
-        <v>606</v>
+        <v>613</v>
       </c>
       <c r="F492" s="7">
         <v>321</v>
@@ -18208,7 +18243,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H492" s="8">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c t="s" r="I492" s="7">
         <v>50</v>
@@ -18221,7 +18256,7 @@
       </c>
       <c r="L492" s="7"/>
       <c t="s" r="M492" s="7">
-        <v>611</v>
+        <v>618</v>
       </c>
     </row>
     <row r="493" ht="14.25" customHeight="1">
@@ -18236,25 +18271,25 @@
       </c>
       <c r="D493" s="7"/>
       <c t="s" r="E493" s="7">
-        <v>606</v>
+        <v>613</v>
       </c>
       <c r="F493" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G493" s="8">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c t="s" r="H493" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I493" s="7">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c t="s" r="J493" s="7">
         <v>169</v>
       </c>
       <c t="s" r="K493" s="7">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L493" s="7"/>
       <c t="s" r="M493" s="7">
@@ -18273,7 +18308,7 @@
       </c>
       <c r="D494" s="7"/>
       <c t="s" r="E494" s="7">
-        <v>606</v>
+        <v>613</v>
       </c>
       <c r="F494" s="7">
         <v>321</v>
@@ -18285,10 +18320,10 @@
         <v>56</v>
       </c>
       <c t="s" r="I494" s="7">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c t="s" r="J494" s="7">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c t="s" r="K494" s="7">
         <v>64</v>
@@ -18325,7 +18360,7 @@
       </c>
       <c r="D496" s="7"/>
       <c t="s" r="E496" s="7">
-        <v>612</v>
+        <v>619</v>
       </c>
       <c r="F496" s="7">
         <v>320</v>
@@ -18337,15 +18372,15 @@
         <v>112</v>
       </c>
       <c t="s" r="I496" s="7">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c t="s" r="J496" s="7">
-        <v>588</v>
+        <v>595</v>
       </c>
       <c r="K496" s="7"/>
       <c r="L496" s="7"/>
       <c t="s" r="M496" s="7">
-        <v>613</v>
+        <v>620</v>
       </c>
     </row>
     <row r="497" ht="14.25" customHeight="1">
@@ -18360,7 +18395,7 @@
       </c>
       <c r="D497" s="7"/>
       <c t="s" r="E497" s="7">
-        <v>612</v>
+        <v>619</v>
       </c>
       <c r="F497" s="7">
         <v>320</v>
@@ -18380,7 +18415,7 @@
       <c r="K497" s="7"/>
       <c r="L497" s="7"/>
       <c t="s" r="M497" s="7">
-        <v>462</v>
+        <v>467</v>
       </c>
     </row>
     <row r="498" ht="14.25" customHeight="1">
@@ -18395,7 +18430,7 @@
       </c>
       <c r="D498" s="7"/>
       <c t="s" r="E498" s="7">
-        <v>612</v>
+        <v>619</v>
       </c>
       <c r="F498" s="7">
         <v>320</v>
@@ -18410,12 +18445,12 @@
         <v>124</v>
       </c>
       <c t="s" r="J498" s="7">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="K498" s="7"/>
       <c r="L498" s="7"/>
       <c t="s" r="M498" s="7">
-        <v>614</v>
+        <v>621</v>
       </c>
     </row>
     <row r="499" ht="14.25" customHeight="1">
@@ -18430,7 +18465,7 @@
       </c>
       <c r="D499" s="7"/>
       <c t="s" r="E499" s="7">
-        <v>612</v>
+        <v>619</v>
       </c>
       <c r="F499" s="7">
         <v>320</v>
@@ -18445,12 +18480,12 @@
         <v>83</v>
       </c>
       <c t="s" r="J499" s="7">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="K499" s="7"/>
       <c r="L499" s="7"/>
       <c t="s" r="M499" s="7">
-        <v>615</v>
+        <v>622</v>
       </c>
     </row>
     <row r="500" ht="15" customHeight="1">
@@ -18465,7 +18500,7 @@
       </c>
       <c r="D500" s="7"/>
       <c t="s" r="E500" s="7">
-        <v>612</v>
+        <v>619</v>
       </c>
       <c r="F500" s="7">
         <v>320</v>
@@ -18485,7 +18520,7 @@
       <c r="K500" s="7"/>
       <c r="L500" s="7"/>
       <c t="s" r="M500" s="7">
-        <v>616</v>
+        <v>623</v>
       </c>
     </row>
     <row r="501" ht="14.25" customHeight="1">
@@ -18500,7 +18535,7 @@
       </c>
       <c r="D501" s="7"/>
       <c t="s" r="E501" s="7">
-        <v>612</v>
+        <v>619</v>
       </c>
       <c r="F501" s="7">
         <v>320</v>
@@ -18535,7 +18570,7 @@
       </c>
       <c r="D502" s="7"/>
       <c t="s" r="E502" s="7">
-        <v>612</v>
+        <v>619</v>
       </c>
       <c r="F502" s="7">
         <v>320</v>
@@ -18547,7 +18582,7 @@
         <v>104</v>
       </c>
       <c t="s" r="I502" s="7">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c t="s" r="J502" s="7">
         <v>155</v>
@@ -18555,7 +18590,7 @@
       <c r="K502" s="7"/>
       <c r="L502" s="7"/>
       <c t="s" r="M502" s="7">
-        <v>617</v>
+        <v>624</v>
       </c>
     </row>
     <row r="503" ht="14.25" customHeight="1">
@@ -18570,7 +18605,7 @@
       </c>
       <c r="D503" s="7"/>
       <c t="s" r="E503" s="7">
-        <v>612</v>
+        <v>619</v>
       </c>
       <c r="F503" s="7">
         <v>320</v>
@@ -18582,10 +18617,10 @@
         <v>68</v>
       </c>
       <c t="s" r="I503" s="7">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c t="s" r="J503" s="7">
-        <v>618</v>
+        <v>625</v>
       </c>
       <c r="K503" s="7"/>
       <c r="L503" s="7"/>
@@ -18618,7 +18653,7 @@
       </c>
       <c r="D505" s="7"/>
       <c t="s" r="E505" s="7">
-        <v>619</v>
+        <v>626</v>
       </c>
       <c r="F505" s="7">
         <v>321</v>
@@ -18630,13 +18665,13 @@
         <v>123</v>
       </c>
       <c t="s" r="I505" s="7">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c t="s" r="J505" s="7">
         <v>195</v>
       </c>
       <c t="s" r="K505" s="7">
-        <v>562</v>
+        <v>569</v>
       </c>
       <c r="L505" s="7"/>
       <c t="s" r="M505" s="7">
@@ -18655,7 +18690,7 @@
       </c>
       <c r="D506" s="7"/>
       <c t="s" r="E506" s="7">
-        <v>619</v>
+        <v>626</v>
       </c>
       <c r="F506" s="7">
         <v>321</v>
@@ -18675,7 +18710,7 @@
       <c r="K506" s="7"/>
       <c r="L506" s="7"/>
       <c t="s" r="M506" s="7">
-        <v>620</v>
+        <v>627</v>
       </c>
     </row>
     <row r="507" ht="14.25" customHeight="1">
@@ -18690,7 +18725,7 @@
       </c>
       <c r="D507" s="7"/>
       <c t="s" r="E507" s="7">
-        <v>619</v>
+        <v>626</v>
       </c>
       <c r="F507" s="7">
         <v>321</v>
@@ -18699,20 +18734,20 @@
         <v>16</v>
       </c>
       <c t="s" r="H507" s="8">
-        <v>621</v>
+        <v>628</v>
       </c>
       <c t="s" r="I507" s="7">
         <v>137</v>
       </c>
       <c t="s" r="J507" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c t="s" r="K507" s="7">
         <v>139</v>
       </c>
       <c r="L507" s="7"/>
       <c t="s" r="M507" s="7">
-        <v>622</v>
+        <v>629</v>
       </c>
     </row>
     <row r="508" ht="14.25" customHeight="1">
@@ -18727,13 +18762,13 @@
       </c>
       <c r="D508" s="7"/>
       <c t="s" r="E508" s="7">
-        <v>619</v>
+        <v>626</v>
       </c>
       <c r="F508" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G508" s="8">
-        <v>621</v>
+        <v>628</v>
       </c>
       <c t="s" r="H508" s="8">
         <v>16</v>
@@ -18775,7 +18810,7 @@
       </c>
       <c r="D510" s="7"/>
       <c t="s" r="E510" s="7">
-        <v>623</v>
+        <v>630</v>
       </c>
       <c r="F510" s="7">
         <v>321</v>
@@ -18787,7 +18822,7 @@
         <v>164</v>
       </c>
       <c t="s" r="I510" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c t="s" r="J510" s="7">
         <v>213</v>
@@ -18810,7 +18845,7 @@
       </c>
       <c r="D511" s="7"/>
       <c t="s" r="E511" s="7">
-        <v>623</v>
+        <v>630</v>
       </c>
       <c r="F511" s="7">
         <v>321</v>
@@ -18830,7 +18865,7 @@
       <c r="K511" s="7"/>
       <c r="L511" s="7"/>
       <c t="s" r="M511" s="7">
-        <v>624</v>
+        <v>631</v>
       </c>
     </row>
     <row r="512" ht="14.25" customHeight="1">
@@ -18845,7 +18880,7 @@
       </c>
       <c r="D512" s="7"/>
       <c t="s" r="E512" s="7">
-        <v>623</v>
+        <v>630</v>
       </c>
       <c r="F512" s="7">
         <v>321</v>
@@ -18860,7 +18895,7 @@
         <v>253</v>
       </c>
       <c t="s" r="J512" s="7">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="K512" s="7"/>
       <c r="L512" s="7"/>
@@ -18880,7 +18915,7 @@
       </c>
       <c r="D513" s="7"/>
       <c t="s" r="E513" s="7">
-        <v>623</v>
+        <v>630</v>
       </c>
       <c r="F513" s="7">
         <v>321</v>
@@ -18900,7 +18935,7 @@
       <c r="K513" s="7"/>
       <c r="L513" s="7"/>
       <c t="s" r="M513" s="7">
-        <v>625</v>
+        <v>632</v>
       </c>
     </row>
     <row r="514" ht="14.25" customHeight="1">
@@ -18915,7 +18950,7 @@
       </c>
       <c r="D514" s="7"/>
       <c t="s" r="E514" s="7">
-        <v>623</v>
+        <v>630</v>
       </c>
       <c r="F514" s="7">
         <v>321</v>
@@ -18927,7 +18962,7 @@
         <v>56</v>
       </c>
       <c t="s" r="I514" s="7">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c t="s" r="J514" s="7">
         <v>64</v>
@@ -18935,7 +18970,7 @@
       <c r="K514" s="7"/>
       <c r="L514" s="7"/>
       <c t="s" r="M514" s="7">
-        <v>617</v>
+        <v>577</v>
       </c>
     </row>
     <row r="515" ht="15" customHeight="1">
@@ -18965,7 +19000,7 @@
       </c>
       <c r="D516" s="7"/>
       <c t="s" r="E516" s="7">
-        <v>626</v>
+        <v>633</v>
       </c>
       <c r="F516" s="7">
         <v>320</v>
@@ -18974,18 +19009,18 @@
         <v>68</v>
       </c>
       <c t="s" r="H516" s="8">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c t="s" r="I516" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c t="s" r="J516" s="7">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="K516" s="7"/>
       <c r="L516" s="7"/>
       <c t="s" r="M516" s="7">
-        <v>608</v>
+        <v>615</v>
       </c>
     </row>
     <row r="517" ht="14.25" customHeight="1">
@@ -19000,19 +19035,19 @@
       </c>
       <c r="D517" s="7"/>
       <c t="s" r="E517" s="7">
-        <v>626</v>
+        <v>633</v>
       </c>
       <c r="F517" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G517" s="8">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c t="s" r="H517" s="8">
         <v>68</v>
       </c>
       <c t="s" r="I517" s="7">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c t="s" r="J517" s="7">
         <v>39</v>
@@ -19020,7 +19055,7 @@
       <c r="K517" s="7"/>
       <c r="L517" s="7"/>
       <c t="s" r="M517" s="7">
-        <v>627</v>
+        <v>634</v>
       </c>
     </row>
     <row r="518" ht="14.25" customHeight="1">
@@ -19035,7 +19070,7 @@
       </c>
       <c r="D518" s="7"/>
       <c t="s" r="E518" s="7">
-        <v>626</v>
+        <v>633</v>
       </c>
       <c r="F518" s="7">
         <v>320</v>
@@ -19055,7 +19090,7 @@
       <c r="K518" s="7"/>
       <c r="L518" s="7"/>
       <c t="s" r="M518" s="7">
-        <v>628</v>
+        <v>635</v>
       </c>
     </row>
     <row r="519" ht="14.25" customHeight="1">
@@ -19070,7 +19105,7 @@
       </c>
       <c r="D519" s="7"/>
       <c t="s" r="E519" s="7">
-        <v>626</v>
+        <v>633</v>
       </c>
       <c r="F519" s="7">
         <v>320</v>
@@ -19090,7 +19125,7 @@
       <c r="K519" s="7"/>
       <c r="L519" s="7"/>
       <c t="s" r="M519" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="520" ht="15" customHeight="1">
@@ -19105,7 +19140,7 @@
       </c>
       <c r="D520" s="7"/>
       <c t="s" r="E520" s="7">
-        <v>626</v>
+        <v>633</v>
       </c>
       <c r="F520" s="7">
         <v>320</v>
@@ -19125,7 +19160,7 @@
       <c r="K520" s="7"/>
       <c r="L520" s="7"/>
       <c t="s" r="M520" s="7">
-        <v>629</v>
+        <v>636</v>
       </c>
     </row>
     <row r="521" ht="14.25" customHeight="1">
@@ -19140,7 +19175,7 @@
       </c>
       <c r="D521" s="7"/>
       <c t="s" r="E521" s="7">
-        <v>626</v>
+        <v>633</v>
       </c>
       <c r="F521" s="7">
         <v>320</v>
@@ -19160,7 +19195,7 @@
       <c r="K521" s="7"/>
       <c r="L521" s="7"/>
       <c t="s" r="M521" s="7">
-        <v>566</v>
+        <v>573</v>
       </c>
     </row>
     <row r="522" ht="14.25" customHeight="1">
@@ -19190,7 +19225,7 @@
       </c>
       <c r="D523" s="7"/>
       <c t="s" r="E523" s="7">
-        <v>630</v>
+        <v>637</v>
       </c>
       <c r="F523" s="7">
         <v>330</v>
@@ -19202,7 +19237,7 @@
         <v>104</v>
       </c>
       <c t="s" r="I523" s="7">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c t="s" r="J523" s="7">
         <v>83</v>
@@ -19225,7 +19260,7 @@
       </c>
       <c r="D524" s="7"/>
       <c t="s" r="E524" s="7">
-        <v>630</v>
+        <v>637</v>
       </c>
       <c r="F524" s="7">
         <v>330</v>
@@ -19234,7 +19269,7 @@
         <v>104</v>
       </c>
       <c t="s" r="H524" s="8">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c t="s" r="I524" s="7">
         <v>195</v>
@@ -19260,13 +19295,13 @@
       </c>
       <c r="D525" s="7"/>
       <c t="s" r="E525" s="7">
-        <v>630</v>
+        <v>637</v>
       </c>
       <c r="F525" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G525" s="8">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c t="s" r="H525" s="8">
         <v>104</v>
@@ -19301,14 +19336,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B527" s="7">
-        <v>632</v>
+        <v>639</v>
       </c>
       <c t="s" r="C527" s="7">
         <v>14</v>
       </c>
       <c r="D527" s="7"/>
       <c t="s" r="E527" s="7">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="F527" s="7">
         <v>330</v>
@@ -19320,17 +19355,17 @@
         <v>16</v>
       </c>
       <c t="s" r="I527" s="7">
-        <v>588</v>
+        <v>595</v>
       </c>
       <c t="s" r="J527" s="7">
         <v>213</v>
       </c>
       <c t="s" r="K527" s="7">
-        <v>588</v>
+        <v>595</v>
       </c>
       <c r="L527" s="7"/>
       <c t="s" r="M527" s="7">
-        <v>634</v>
+        <v>641</v>
       </c>
     </row>
     <row r="528" ht="14.25" customHeight="1">
@@ -19345,7 +19380,7 @@
       </c>
       <c r="D528" s="7"/>
       <c t="s" r="E528" s="7">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="F528" s="7">
         <v>330</v>
@@ -19354,18 +19389,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H528" s="8">
-        <v>635</v>
+        <v>642</v>
       </c>
       <c t="s" r="I528" s="7">
         <v>243</v>
       </c>
       <c t="s" r="J528" s="7">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="K528" s="7"/>
       <c r="L528" s="7"/>
       <c t="s" r="M528" s="7">
-        <v>636</v>
+        <v>643</v>
       </c>
     </row>
     <row r="529" ht="14.25" customHeight="1">
@@ -19395,7 +19430,7 @@
       </c>
       <c r="D530" s="7"/>
       <c t="s" r="E530" s="7">
-        <v>637</v>
+        <v>644</v>
       </c>
       <c r="F530" s="7">
         <v>330</v>
@@ -19410,12 +19445,12 @@
         <v>39</v>
       </c>
       <c t="s" r="J530" s="7">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="K530" s="7"/>
       <c r="L530" s="7"/>
       <c t="s" r="M530" s="7">
-        <v>614</v>
+        <v>621</v>
       </c>
     </row>
     <row r="531" ht="14.25" customHeight="1">
@@ -19430,7 +19465,7 @@
       </c>
       <c r="D531" s="7"/>
       <c t="s" r="E531" s="7">
-        <v>637</v>
+        <v>644</v>
       </c>
       <c r="F531" s="7">
         <v>330</v>
@@ -19439,7 +19474,7 @@
         <v>104</v>
       </c>
       <c t="s" r="H531" s="8">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c t="s" r="I531" s="7">
         <v>230</v>
@@ -19450,7 +19485,7 @@
       <c r="K531" s="7"/>
       <c r="L531" s="7"/>
       <c t="s" r="M531" s="7">
-        <v>639</v>
+        <v>646</v>
       </c>
     </row>
     <row r="532" ht="14.25" customHeight="1">
@@ -19465,13 +19500,13 @@
       </c>
       <c r="D532" s="7"/>
       <c t="s" r="E532" s="7">
-        <v>637</v>
+        <v>644</v>
       </c>
       <c r="F532" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G532" s="8">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c t="s" r="H532" s="8">
         <v>104</v>
@@ -19480,7 +19515,7 @@
         <v>204</v>
       </c>
       <c t="s" r="J532" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K532" s="7"/>
       <c r="L532" s="7"/>
@@ -19513,19 +19548,19 @@
       </c>
       <c r="D534" s="7"/>
       <c t="s" r="E534" s="7">
-        <v>640</v>
+        <v>647</v>
       </c>
       <c r="F534" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G534" s="8">
-        <v>635</v>
+        <v>642</v>
       </c>
       <c t="s" r="H534" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I534" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c t="s" r="J534" s="7">
         <v>312</v>
@@ -19563,7 +19598,7 @@
       </c>
       <c r="D536" s="7"/>
       <c t="s" r="E536" s="7">
-        <v>641</v>
+        <v>648</v>
       </c>
       <c r="F536" s="7">
         <v>330</v>
@@ -19578,12 +19613,12 @@
         <v>306</v>
       </c>
       <c t="s" r="J536" s="7">
-        <v>562</v>
+        <v>569</v>
       </c>
       <c r="K536" s="7"/>
       <c r="L536" s="7"/>
       <c t="s" r="M536" s="7">
-        <v>642</v>
+        <v>649</v>
       </c>
     </row>
     <row r="537" ht="14.25" customHeight="1">
@@ -19613,7 +19648,7 @@
       </c>
       <c r="D538" s="7"/>
       <c t="s" r="E538" s="7">
-        <v>643</v>
+        <v>650</v>
       </c>
       <c r="F538" s="7">
         <v>330</v>
@@ -19622,18 +19657,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H538" s="8">
-        <v>644</v>
+        <v>651</v>
       </c>
       <c t="s" r="I538" s="7">
         <v>299</v>
       </c>
       <c t="s" r="J538" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K538" s="7"/>
       <c r="L538" s="7"/>
       <c t="s" r="M538" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="539" ht="14.25" customHeight="1">
@@ -19648,13 +19683,13 @@
       </c>
       <c r="D539" s="7"/>
       <c t="s" r="E539" s="7">
-        <v>643</v>
+        <v>650</v>
       </c>
       <c r="F539" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G539" s="8">
-        <v>644</v>
+        <v>651</v>
       </c>
       <c t="s" r="H539" s="8">
         <v>16</v>
@@ -19663,7 +19698,7 @@
         <v>99</v>
       </c>
       <c t="s" r="J539" s="7">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="K539" s="7"/>
       <c r="L539" s="7"/>
@@ -19671,7 +19706,7 @@
     </row>
     <row r="540" ht="16.5" customHeight="1">
       <c t="s" r="A540" s="9">
-        <v>645</v>
+        <v>652</v>
       </c>
       <c r="B540" s="9"/>
       <c r="C540" s="9"/>
@@ -19691,7 +19726,7 @@
     <row r="541" ht="65.25" customHeight="1"/>
     <row r="542" ht="16.5" customHeight="1">
       <c t="s" r="A542" s="10">
-        <v>646</v>
+        <v>653</v>
       </c>
       <c r="B542" s="10"/>
       <c r="C542" s="10"/>
@@ -19704,7 +19739,7 @@
       <c r="J542" s="10"/>
       <c r="K542" s="10"/>
       <c t="s" r="L542" s="11">
-        <v>647</v>
+        <v>654</v>
       </c>
       <c r="M542" s="11"/>
       <c r="N542" s="11"/>
